--- a/reports/subagent_chat/report.xlsx
+++ b/reports/subagent_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="170">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc59-b4bd-7922-9106-8f95660c53fd</t>
+    <t>01a0cce3-0d9c-7b70-86d0-3dd59612ee78</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc59-b4c7-75c1-a3dc-22ab9b512aa9</t>
+    <t>01a0cce3-0da5-7a50-834d-622dd2173e09</t>
+  </si>
+  <si>
+    <t>Conversation history · cache read</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -318,7 +321,7 @@
     <t xml:space="preserve">    System prompt</t>
   </si>
   <si>
-    <t>Delegate echoing the supplied text to workflow-specialist using task. Provide a self-contained assignment. After its summary returns, answer the user concisely. The specialist uses an echo tool, which supplies no independent factual evidence.</t>
+    <t>Delegate echoing the supplied text to isolated-subagent using task. Provide a self-contained assignment. After its summary returns, answer the user concisely. The specialist uses an echo tool, which supplies no independent factual evidence.</t>
   </si>
   <si>
     <t xml:space="preserve">    User prompt</t>
@@ -345,8 +348,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0bfebbbb3ce44274006ab34a2b0d0887d2a21ef40210b6e1be", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0orePOs-S0r2ZGIM8qAbvduXhuS6HcS0PJr9kYsEA8TMnl0nxfd8Hqfol3Fzo5MPP5HUHjZzADENYNUYwqvNcuaTyhhd9D6XXbOtpKZouNAVSlROsng8nA9olfq7nZIP5KKEZpg62zGs2_yL55oh_oHsNjLyglgpSHPD8QvWGs7ubUtHakTsowB-943vWyDuiko8yAzt8weY10RGcRpUgOvTYC2jksrCP3izkzVS7yeN2GEgUrHSbG9tS0VCKjTNQJJAU3JiFnlvDDq8ENS9McFuyk5JUvto85dQogksQceKLE5iMbsTyuYYshP8yJOrKeTSKpBJWJoo5t4oXvd6E5xPKTF78qipvC619zwlOtnmWs3oIT2GoXP93DuK-zFMzxGe0JIlH-PpjOyyf8mBIhxCqapVriWN22OyaYeT3JTQ1agSDsAUxLfUu0z-HUb7VKiNaca_194sM3tauPUr4jjqCI45X_oxiYwMpVrK9JCrqp8vEWGLyGPF5LtgZyVgzd7TP-7GLEsduQszeNm0Ms6wMiC4A43JOXOmf0OGu-zCvI7SzNSi4UP5no_1HLachpTtQCBknbBz3x2WZ7JC9vq-HadNWjmIWzO2QkFtg7JXbqkJionPiVgufJvKvtgVY7PlVoM99YwFpRjyO6x6_aCcoKiImSf9XfTzb9Y10MKI1Gu2ig8EsWYZGT-0n8VlCuATKv6eCHMnduI7_Ct9pwUneVlDE275poaADl6O06C1H_QA88i2PIiOzrHG7IX8aYCTq-dY4MDvU2d_FWYibVSi_ipR9Wphb2n2F1LeueWs1ffBXSw3eyQtlBL-cFx1DqurX2D_33VfQoK4o0uWYyUC9-CAbZzt5V0jHpQjseiv_Yh_wRKY6A3vksxhRahMV9WdPoeu-paGwGXGBPqtpyjhGvsJFZSHJG1Lg8kGBGB5Hey7PiV9h1FMHWyJFqqjzMOKIjI9NEgUpKdgmxVh7xQW5OiG6ja7EWRgbvC8XpLBxxkLmzxNSRnF1h-EBMVjUWdpJkT5ylKHOa05tGqH-FS9nCykTOYWPmJzQxwDfZtvU5CLvkVAMmtCcqu9zHqj10JrXNOOhlmF58DtV_pTOS0tsXUt9KPEVSdgGYq8-qyYDiBXSQafTfQzmXGuJ9V1cUy77SVFMA34MY7GzOQuCCCfa0LDSQWHXDZu9sYwVNj-IA3yh3vJqs9HVCwAJI1rGts--ElouTX2DsUulhjte45PEKwOX-O44bS0CqXEaZCUuLi0WDUq9TyZfFlyrg6p4beapBLcSZGrjHcnsZWdD-B5NQtHZr6H920_ZrY0Sf_KtmCEDThEKtSMipL13Ya9LrYbGJlapehb-B1JIJS0WNAmg=="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then briefly explain how the result from that tool is returned to the parent agent: state that the tool output is delivered to you, you summarize/report it in your final response, and the parent receives that summary. Do not add independent factual claims beyond this process description.\",\"subagent_type\":\"workflow-specialist\"}", "call_id": "call_9JHEYFbgDSkh97uIcwJTEbmA", "id": "fc_0bfebbbb3ce44274006ab34a2b62d487d2a913de2731c5a246", "index": 1}]
-{"name": "task", "args": {"description": "Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then briefly explain how the result from that tool is returned to the parent agent: state that the tool output is delivered to you, you summarize/report it in your final response, and the parent receives that summary. Do not add independent factual claims beyond this process description.", "subagent_type": "workflow-specialist"}, "id": "call_9JHEYFbgDSkh97uIcwJTEbmA", "type": "tool_call"}</t>
+    <t>[{"id": "rs_02356a6adfa3262b006ab36d545a0887d2a6efeb552fef21db", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21UhmGF_evNgNySwNWT3cv80iSB8gIH9tgYVoXADn7z_t-cNNvPxdJZaAScctN-X4I6-ZMmVsj5v7C8gfEnw1QN4Qvae5pbeO93SMSwo_KHscPnM03UH-KDMw4WL1EdlMltY0ZJ1LOb0xBpDD_1ByAc1RPP5a-xUMiavi4Rg8HKwAYHD5OA4kWQSCIHJl2UiZ4kXr-tf7aqIdNYlr1l5lo9MjrdaxD1cwZ5AAZpzLDL7zGPiVHOz2L3fQpcyPk176JawLHtepeq0vUgWgIUqPXMwY9OfmXrX_0u02fE8D8l11Oe_UuM7-6Ywe0LiYYVxslSsen2DYli5INYnCDPqUJGO38F_0JSdX-Ln1NanyNN2TotaFInFayUDM6-IG3RYugXt59Jt3_P-4qNbgOP0lncMWgSHxctjIjx89vaYz3hjz2WBSBGCndPvOtq5uN8cmMrcJKkjTiRjHCnV3SEtR2kG-QZfNkyi5d2Crgsxr4qXd3zTi-0qudQsgreJshvtcIvg0fjs9xrORUIXdcGCwXgnksdSgHjvhrCiWiEeXxLtyWR0FQjNRyEQpvkzm3Q32rzLO1SVyuDMJczrNhoxOrGpEV5z66mI1au4iTMA3JSt2DchmrmCfVIupMoq8mneUWjF1umBH8jtbJHIAD9uwL-WcwY4ihkiyaoyWfO-plJS2EWmDvdgsZqCkgBOe5HaDLB7IZND7pYK078Tgd7WaG5761vEaeAAj30JD5bXzvV4IeJEYp1Xt5Tico4mujjTnOAvJgVhKXri8Gxb4ypMQr59_n-z26epV8h9aqisFY3j-gEGM6NLPESvJcu4gHF3Rswszs3qsh68Wk_7whd0QeG3zZS71bSii3vcJD28uMNEXV6AE3U33oifUE4dveZt7eNxbNGN4QHx7G3FqaLr81mBssnAfgmm0aIFoI-vGK58oXKg_kSANnvwdiVqYS-VPbA-V9JB_kfYHzQ58il62TgiPPgyHpLZ0n3KIQlO7DqcS3wc2V3o0FDnV8l7VnneDpD_1f9HW2IBy80Qld1vTCXpDRryFT_hvT4kNO-m82O-bdZANS6hdjiuf9UVgJbY_gg1DODBgxXjmc8n1T0nE3ms-2EDILmGbGMAHp5oUROHkAh8av1LD8wFSceTYMCkRRgYxlK1fPDh5KPSt8VO1TVZl8fleknHB41-4DbtyfBAy2wOhDBJEkpV7u0aHcuO4VJeo63s307AwV93EfukQm6mdEMMJxS48DdYuVojm_OTF7Ovfgm5qwhu7cN2Djd_ieXGauYZ2mcnT1tvYAHDAXmXQtD0AapNcnZobo7S3XJsA_ceLOkCp5lXnFQZdgrSTO4WSDodeeJws3SIn0pZH4Kww=="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Echo the exact supplied text: \\\"ReAct\\\". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.\",\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_GvpxgR5ep2QOYbL19IiPbs5S", "id": "fc_02356a6adfa3262b006ab36d54e44087d2bde1e47362f66de5", "index": 1}]
+{"name": "task", "args": {"description": "Echo the exact supplied text: \"ReAct\". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.", "subagent_type": "isolated-subagent"}, "id": "call_GvpxgR5ep2QOYbL19IiPbs5S", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -358,38 +361,38 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0cc59-bed0-7943-8c70-10c12303efa6</t>
+    <t>01a0cce3-1afe-7ec0-bb7c-537b7d189ad9</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': 'Use your echo tool to echo exactly the supplied text: “ReAct”. Then briefly explain how the result from that tool is returned to the parent agent: state that the tool output is delivered to you, you summarize/report it in your final response, and the parent receives that summary. Do not add independent factual claims beyond this process description.', 'subagent_type': 'workflow-specialist'}</t>
+    <t>{'description': 'Echo the exact supplied text: "ReAct". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.', 'subagent_type': 'isolated-subagent'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='The tool output is delivered to me. I summarize/report it in my final response, and the parent receives that summary: “Your input was: ReAct”.', tool_call_id='call_9JHEYFbgDSkh97uIcwJTEbmA')]})</t>
+    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='The tool returned: “Your input was: ReAct”. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.', tool_call_id='call_GvpxgR5ep2QOYbL19IiPbs5S')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc59-bedb-7b32-8f5a-20fb1aeaffe3</t>
+    <t>01a0cce3-1b09-7dc1-9c13-d7ac69a85691</t>
   </si>
   <si>
     <t>You are a workflow teaching specialist. Call echo_tool with the assigned text, then summarize the returned echo for the parent. The echo repeats supplied input and provides no independent factual evidence. Do not delegate further.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0ee20727aa7aac92006ab34a2d603c87d2958b3bb4d33a3c7a", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0otxddo7f5Z--EqiX0qYRMSCuOGgHjHJ_VylMUvPis5126zgjFt76F3Ar_ZFgHMqMlla0DusPS0XLgMnJ_i_IrQJus243mxLT81do9sFLAR7EtRhROle_4ddQenAXGNWNXQWoSZICf3YJDwWJdbGWUQeY2rNzdXsFEpRA9WOJ2oLqN4pToXB4VEnqls1hjn47SCxhgEXRJ4XhcgdmqMNtvo1iyOW_Go6BYvuWAEiULsk0E_sgrWwxTzdtaLkrqxOQtoPHh55660VQiyf4yyDuQGVx-TkDrYk1MBsYPFWg4sTzKI7pv67rgBateZC_2f5B7qfZIa15yfpRkiTcmFHysjjbYikPpRgTFdIY5yHY62scR_R0_Ba22fH1yZLiq14MzxWhovpZ-eZmTwCbWQtAvcX_jyqh-XlOevlyxoyTqQmta-SGoSdnDs38FjVk9hgVoYXXg7A7b2t5aQNOWdQFIwzD50qNAnXYzQut9Fxo7xt7qzS96Wtw-FeGIV4ca5PhU2TQB6YNFlyyT0MD3VvAZvov2VAWCuhQAtEQeW1cs1pfTSIsSO2GKrB-xNWjzl94UwfIJjIJpe0emEL0RV_Nkg-tpByeMN5lM_MAxQUB0de0_hKC8td_zm3WcI1UDCBUWvDVTxneNlNE5jkn-XbFu4MiIzUwihz890jtqLwJwBc4qDPO_uyCjh-m3I_fCyoD-ibJDI_J0iQbDcXPWm4D3jTOl_EB-fS8VggeAlIHowUDl-m60cJvVagbl4saKet7M_ab8UZTJoTGqBFQImvmSErRPRDFcQ_50lkp6YlHJkxlKi-qkENIqIxwKu-VQsjvUZVplrvB1J17Jqk4VqbijFwkR5TXT2CP7z1WM802fHYT8_Ha6kq2lMcNcuiaywM6ibs8J31xsWajMGovbpY3NIWVlmNi3t0oS8IrOjzU1ZRZTZxhm1swpHoDLcVXJZAC7Pw7n_BTOssOzYEe7U8HQKBMX2rFYCtpz0XReWaaJpf0Vm1Z23LNDp7s2j3JMYaOBYBhLuqu_yZh-mg-r-eGw3x6aaM6-fZwglhUginHaz4pncGZPH7UKI_qmn91Te9iW4NifFkFqJY8SGQQLJQXnDriTXj54AXlF_uypwXe9dJ_MQvI5RHEmA7NfBKsRXC6GlMHD2nUDrJcdOIE9ncMISVZkO3kRlrVs0-0ZmpNTyfqu8-yFy5mQhtpm6Zfpeo12A6nqO0gY2VImS2Hmk8aj4Srr5o6dRJKhgZ9YMCGQS8uOYgABGSWVawmqDnAYCoQW1MyZzdPuW7M4b9a4y0dYuKNOxQcNgNKydhsfImWq7Z8beCS40eI0KlIrsp5Yl2w5uJhxJU5k4uUXr_-URmrty8QBrX_M2q5M6v5SzrVt0HjA="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_wjzZczTAGuZxDZSqA0DnGMdK", "id": "fc_0ee20727aa7aac92006ab34a2dbed487d297c264128d3a200f", "index": 1}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_wjzZczTAGuZxDZSqA0DnGMdK", "type": "tool_call"}</t>
+    <t>[{"id": "rs_09300af7f4472580006ab36d57636487d288881c928d0de5f9", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21XfU0YomilKv-MqloXyKMUrLz0PLAnkuxs2S3eiw3fUwBG8tyiHVBmThWqi6SEDFzAgBMdkhC3nSH8FSi_8yj6O2V3ZyKlSFW2GjJLy8kX7tdAtV4dJ3vxP0f-V1Yppk7yYTWqqdsNfNfIGngbZkicwcMfHNlsHZ5DicWHaTvmBSdxq3SzceWSdyPw2qWYeae7KsHTFMlBaRPxoSIQYDMuUL0-0IQ5y8g9yx_hy2UcW6N9bhgOOg3KSP1yM3on9vd3zGSCxTrHHqytNrFn7VLFj9L7oJkWMIkyOaJtNsUgN85tmOiWk1hyhVrka8Gyskwv-6V7kCQroq00ghAI1XU5ntI89aVO6hgx8xGa2y-WErw-2NdSpNjFQNFC0fS0GMNWJRaaFuiYpWGZufoReibA72NvZKlelKKzcCQK8epnThhutNG1wMUC9ZRV0g_vn4Z-GjtitNJ8laa7Fn5f08iEpQVkocuSIGIxp6TmGJpp7j2B1QANrGiRFonan5344sKYJoav-fTlbbw1WsBFC7aseDsvYrq6y949XGhaYZRFfPgVAC5sewCsD3jdSB3TMV5EOUNB1nieTv7nFouh3lXJHOQZ9p02Nl1pSmBOFQVdXtJj6CzAnTfwsQfBeNHEdTByc0MbjPssuCHPfaaf6r8uIaY5j5Eq7PRmL3YMRfzS52TpDWm5psdN1TiNGDxUbxjw0UPiVahCGApovU-7QuJA5sZuaDFV8Ey6NISRkny5jOg_mmX4Avu_AN3GxvpdT-0zegSqBDhUvMseACxiON09p4agxT8ALeB2GO6E7ejVQ9l7BkSV6lJJ2hMRI3UxbQ9PM-T-HAKWxKX4j2qluuEw6OCS_MIeUg4mFwl1zOHmc22D5c3Z5HtSX3qwpbLs92kU0kMENFpyljaBU5r0Qa7mLG6B0OPRureLxBt6qneiLCoyj9MY9ioA6vhYvuT1Hsjy6fLQLov_BwG5BK6_EHNpIE-z6Iqt5_h4DFp7mDSQ0LIIW-N55SDSeG63EojZHlpTEb96QntkYc1XWAMudhQ3rr5iixXxdKBlI95P5k6lUpCAFJ9Hf8CfyKgUWwjDGGGJqby-_iLEcrA54Uii_mf4w2JPNTcgMbQ8HUByn9bMyrVJBk4Gd7BGOS63uNBrwKf8oxw11NZiZBN6wE7_GycYN5RjBaSdiH7eDs54MLzNGrtg2HyxUU9O0vgndwrryqWc0JexCAWOW3c1UV9l5NIDs8C83EbcKsBmLvcBjQjhB9RdYRpuchxjtYRbgualkgqdxieBO_pSySPJSaXyp8tkTA=="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_3xW3L97jhorBQsp82zzndopP", "id": "fc_09300af7f4472580006ab36d57d1f087d29dab905fbfe61298", "index": 1}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_3xW3L97jhorBQsp82zzndopP", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0cc59-c3c9-7ef2-8456-ee8dc6450acc</t>
+    <t>01a0cce3-200e-7061-a841-7c3f88238d8f</t>
   </si>
   <si>
     <t>{'text': 'ReAct'}</t>
@@ -401,28 +404,25 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cc59-c3cf-7bb0-bf7a-cb79056d5932</t>
-  </si>
-  <si>
-    <t>Conversation history · cache read</t>
+    <t>01a0cce3-2013-71d3-a69f-0435e63e9c0a</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The tool output is delivered to me. I summarize/report it in my final response, and the parent receives that summary: \u201cYour input was: ReAct\u201d.", "phase": "final_answer", "index": 0, "id": "msg_0ee20727aa7aac92006ab34a2eaa4c87d295d02c40dbb74373"}]</t>
+    <t>[{"type": "text", "text": "The tool returned: \u201cYour input was: ReAct\u201d. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.", "phase": "final_answer", "index": 0, "id": "msg_09300af7f4472580006ab36d58d6dc87d2b56059e0173862c6"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cc59-c80c-79b3-b060-b43fbfc70873</t>
-  </si>
-  <si>
-    <t>The tool output is delivered to me. I summarize/report it in my final response, and the parent receives that summary: “Your input was: ReAct”.</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The specialist echoed: **\u201cReAct\u201d**.\n\nIts tool result was delivered to the specialist, which summarized it in its final response; that summary was then returned to me, the parent agent.", "phase": "final_answer", "index": 0, "id": "msg_0bfebbbb3ce44274006ab34a2fef7087d2b31d450da099dc5f"}]</t>
+    <t>01a0cce3-25de-7380-bafd-de3809be4210</t>
+  </si>
+  <si>
+    <t>The tool returned: “Your input was: ReAct”. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The specialist echoed: **\u201cReAct.\u201d**\n\nIts tool result returns to the parent agent as a tool response/summary. The parent can then incorporate that result into its final answer.", "phase": "final_answer", "index": 0, "id": "msg_02356a6adfa3262b006ab36d5a251487d2879a79d5c7a84ffa"}]</t>
   </si>
   <si>
     <t>delegating_parent</t>
@@ -443,7 +443,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cc59-b4c0-7622-b132-83ec0300e42d</t>
+    <t>01a0cce3-0d9f-76b3-b4e3-3ecec2bcc9ba</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -455,7 +455,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc59-b4c1-7860-8319-bbfec26373fb</t>
+    <t>01a0cce3-0da0-7452-830a-a8f457830cb9</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -476,7 +476,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc59-bece-7743-8ffb-cb07f698075a</t>
+    <t>01a0cce3-1afd-7ea0-b6ce-0756d2a9edb4</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -488,7 +488,7 @@
     <t>Launch an ephemeral subagent to handle a complex, multi-step task.
 Available agent types and the tools they have access to:
 - general-purpose: General-purpose agent for researching complex questions, searching for files and content, and executing multi-step tasks. When you are searching for a keyword or file and are not confident that you will find the right match in the first few tries use this agent to perform the search for you. This agent has access to all tools as the main agent.
-- workflow-specialist: Echoes assigned text with a local tool and summarizes its result.
+- isolated-subagent: Echoes assigned text with a local tool and summarizes its result.
 Specify subagent_type to select the agent. Usage notes:
 - Launch multiple agents concurrently when their tasks are independent, using a single message with multiple tool calls.
 - Each invocation is stateless by default: the agent sees only the prompt you give it and returns a single final report. Put full detail in the prompt and state exactly what it should return — unless an agent type below says it inherits your conversation instead.
@@ -498,25 +498,25 @@
 - When only general-purpose is available, use it for any complex, context-heavy task; it has the same capabilities as the main agent.</t>
   </si>
   <si>
-    <t xml:space="preserve">            workflow-specialist</t>
-  </si>
-  <si>
-    <t>Execute the workflow-specialist workflow operation and pass its result to the next graph step.</t>
-  </si>
-  <si>
-    <t>01a0cc59-bed1-7822-b919-8a8a6e71c2b9</t>
+    <t xml:space="preserve">            isolated-subagent</t>
+  </si>
+  <si>
+    <t>Execute the isolated-subagent workflow operation and pass its result to the next graph step.</t>
+  </si>
+  <si>
+    <t>01a0cce3-1aff-7cd1-9b61-cfb541f61ffe</t>
   </si>
   <si>
     <t xml:space="preserve">                PatchToolCallsMiddleware.before_agent</t>
   </si>
   <si>
-    <t>01a0cc59-bed2-7d52-bd18-4cb44897700e</t>
+    <t>01a0cce3-1b00-7b32-bac1-abcf104178f2</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cc59-bed4-73f3-bde4-e966bf220e73</t>
+    <t>01a0cce3-1b03-7c21-8473-8bd7f8a447f4</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -525,7 +525,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0cc59-c3c8-79f0-ba79-fe5472e5bac4</t>
+    <t>01a0cce3-200c-7d63-b35e-cf59862af41b</t>
   </si>
   <si>
     <t xml:space="preserve">                    echo_tool</t>
@@ -534,10 +534,10 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0cc59-c3cc-7f12-acf6-052b3bfa275d</t>
-  </si>
-  <si>
-    <t>01a0cc59-c809-7d41-af6f-0be05fb7cae5</t>
+    <t>01a0cce3-2010-7142-8124-2e5578174a35</t>
+  </si>
+  <si>
+    <t>01a0cce3-25db-7ee1-bec9-c17131f78393</t>
   </si>
 </sst>
 </file>
@@ -944,7 +944,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1004,20 +1004,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60)=4,SUM('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60),"Unknown")</f>
-        <v>0.001222539318</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004463219394</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60)=4,SUM('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60),"Unknown")</f>
-        <v>0.0014014</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00051162</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>122.0</v>
+        <v>45.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>140.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1028,20 +1028,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60)=4,SUM('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60),"Unknown")</f>
-        <v>0.001222539318</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004463219394</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60)=4,SUM('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60),"Unknown")</f>
-        <v>0.0014014</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00051162</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>122.0</v>
+        <v>45.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>140.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1075,23 +1075,23 @@
         <v>97</v>
       </c>
       <c r="D5" s="5">
-        <v>3</v>
+        <v>2046</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>3.56973804e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.092e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
@@ -1104,8 +1104,27 @@
       <c r="C6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="47" customHeight="1">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="F6" s="2">
+        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G6" s="5">
+        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1115,11 +1134,8 @@
       <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
+    </row>
+    <row r="8" spans="1:13" ht="47" customHeight="1">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -1127,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
@@ -1141,26 +1157,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2046</v>
-      </c>
-      <c r="E9" s="2">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER('Reference data'!$B$3)),F9*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000446217255</v>
-      </c>
-      <c r="F9" s="2">
-        <f>IF(D9=0,0,IF(ISNUMBER('Reference data'!D17),D9*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.0005115</v>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(ISNUMBER(E9),ROUND(E9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
-      </c>
-      <c r="H9" s="5">
-        <f>IF(ISNUMBER(F9),ROUND(F9*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
@@ -1174,48 +1174,29 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:13" ht="24" customHeight="1">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="4">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" t="s">
+    </row>
+    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="5">
-        <v>29</v>
-      </c>
-      <c r="E12" s="2">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="F12" s="2">
-        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H12" s="5">
-        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+      <c r="D12" s="4">
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1229,26 +1210,26 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.7356492e-05</v>
+        <v>3.3499008e-05</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001116</v>
+        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>3.84e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="409" customHeight="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1258,11 +1239,27 @@
       <c r="C14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24" customHeight="1">
+      <c r="D14" s="5">
+        <v>83</v>
+      </c>
+      <c r="E14" s="2">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.6888052e-05</v>
+      </c>
+      <c r="F14" s="2">
+        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>9.96e-05</v>
+      </c>
+      <c r="G14" s="5">
+        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H14" s="5">
+        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="385" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1270,7 +1267,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="24" customHeight="1">
@@ -1284,690 +1284,671 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:13" ht="24" customHeight="1">
+      <c r="A17" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13)=4,SUM('Turns'!E5,'Turns'!E9,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>0.000574455645</v>
-      </c>
-      <c r="F17" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13)=4,SUM('Turns'!F5,'Turns'!F9,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>0.0006585</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
-      </c>
-      <c r="H17" s="5">
-        <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
-      </c>
-      <c r="K17" s="4" t="s">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="E18" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
+        <v>0.0001566078624</v>
+      </c>
+      <c r="F18" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
+        <v>0.00017952</v>
+      </c>
+      <c r="G18" s="5">
+        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="73" customHeight="1">
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="K19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:13" ht="60" customHeight="1">
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="47" customHeight="1">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="I20" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:13" ht="60" customHeight="1">
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="I21" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    </row>
+    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="4">
-        <v>1767</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="D22" s="4">
+        <v>1755</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="24" customHeight="1">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="5">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER('Reference data'!$B$3)),F22*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F22" s="2">
-        <f>IF(D22=0,0,IF(ISNUMBER('Reference data'!B17),D22*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G22" s="5">
-        <f>IF(ISNUMBER(E22),ROUND(E22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="5">
-        <f>IF(ISNUMBER(F22),ROUND(F22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+      <c r="M22" s="4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="24" customHeight="1">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1692</v>
+      </c>
+      <c r="E23" s="2">
+        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.95210008e-05</v>
+      </c>
+      <c r="F23" s="2">
+        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.384e-05</v>
+      </c>
+      <c r="G23" s="5">
+        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="24" customHeight="1">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="47" customHeight="1">
-      <c r="A24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>120</v>
+      <c r="D24" s="5">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2">
+        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="F24" s="2">
+        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G24" s="5">
+        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="5">
+        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1764</v>
-      </c>
-      <c r="E25" s="2">
-        <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00038471517</v>
-      </c>
-      <c r="F25" s="2">
-        <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.000441</v>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
-      </c>
-      <c r="H25" s="5">
-        <f>IF(ISNUMBER(F25),ROUND(F25*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="24" customHeight="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="47" customHeight="1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="24" customHeight="1">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A27" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="4">
-        <v>57</v>
+      <c r="D27" s="5">
+        <v>60</v>
+      </c>
+      <c r="E27" s="2">
+        <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.308555e-05</v>
+      </c>
+      <c r="F27" s="2">
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!D17),D27*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>1.5e-05</v>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="4">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="5">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2">
-        <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.7686384e-05</v>
-      </c>
-      <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!F17),D28*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>4.32e-05</v>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H28" s="5">
-        <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
-      <c r="A29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D29" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="5">
-        <v>21</v>
-      </c>
-      <c r="E29" s="2">
-        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
-      </c>
-      <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="D30" s="5">
+        <v>23</v>
+      </c>
+      <c r="E30" s="2">
+        <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.4077412e-05</v>
+      </c>
+      <c r="F30" s="2">
+        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!F17),D30*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>2.76e-05</v>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
         <v>2.0</v>
       </c>
-      <c r="H29" s="5">
-        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H30" s="5">
+        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
         <v>3.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="294" customHeight="1">
-      <c r="A30" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="D31" s="5">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.1983724e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!E17),D31*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.52e-05</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="294" customHeight="1">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1">
+      <c r="A33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E33" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E25,'Turns'!E28,'Turns'!E29)=4,SUM('Turns'!E22,'Turns'!E25,'Turns'!E28,'Turns'!E29),"Unknown")</f>
-        <v>0.0004449087</v>
-      </c>
-      <c r="F33" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F25,'Turns'!F28,'Turns'!F29)=4,SUM('Turns'!F22,'Turns'!F25,'Turns'!F28,'Turns'!F29),"Unknown")</f>
-        <v>0.00051</v>
-      </c>
-      <c r="G33" s="5">
-        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
-      </c>
-      <c r="H33" s="5">
-        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
-      </c>
-      <c r="K33" s="4" t="s">
+    <row r="34" spans="1:13" ht="24" customHeight="1">
+      <c r="A34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M34" s="4" t="s">
+      <c r="E35" s="2">
+        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30,'Turns'!E31)=5,SUM('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30,'Turns'!E31),"Unknown")</f>
+        <v>8.91911088e-05</v>
+      </c>
+      <c r="F35" s="2">
+        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30,'Turns'!F31)=5,SUM('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30,'Turns'!F31),"Unknown")</f>
+        <v>0.00010224</v>
+      </c>
+      <c r="G35" s="5">
+        <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H35" s="5">
+        <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B36" s="4">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="24" customHeight="1">
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="K36" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="M36" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="24" customHeight="1">
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="I36" s="6" t="s">
+    <row r="37" spans="1:13" ht="24" customHeight="1">
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>115</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A37" s="4" t="s">
+    <row r="38" spans="1:13" ht="24" customHeight="1">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>117</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="s">
+    </row>
+    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="4">
-        <v>1841</v>
-      </c>
-      <c r="J37" s="4" t="s">
+      <c r="D39" s="4">
+        <v>1816</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="24" customHeight="1">
-      <c r="A38" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="M39" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="D38" s="5">
-        <v>1764</v>
-      </c>
-      <c r="E38" s="2">
-        <f>IF(AND(ISNUMBER(F38),ISNUMBER('Reference data'!$B$3)),F38*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.07772136e-05</v>
-      </c>
-      <c r="F38" s="2">
-        <f>IF(D38=0,0,IF(ISNUMBER('Reference data'!C17),D38*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.528e-05</v>
-      </c>
-      <c r="G38" s="5">
-        <f>IF(ISNUMBER(E38),ROUND(E38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H38" s="5">
-        <f>IF(ISNUMBER(F38),ROUND(F38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="24" customHeight="1">
-      <c r="A39" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="5">
-        <v>3</v>
-      </c>
-      <c r="E39" s="2">
-        <f>IF(AND(ISNUMBER(F39),ISNUMBER('Reference data'!$B$3)),F39*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F39" s="2">
-        <f>IF(D39=0,0,IF(ISNUMBER('Reference data'!B17),D39*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G39" s="5">
-        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="5">
-        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>125</v>
+        <v>97</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1752</v>
+      </c>
+      <c r="E40" s="2">
+        <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.05678448e-05</v>
+      </c>
+      <c r="F40" s="2">
+        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!C17),D40*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.504e-05</v>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H40" s="5">
+        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="24" customHeight="1">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D41" s="5">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2">
         <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.6138845e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F41" s="2">
-        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!D17),D41*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.85e-05</v>
+        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!B17),D41*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G41" s="5">
         <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H41" s="5">
         <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>129</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="1:13" ht="24" customHeight="1">
+      <c r="A43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A43" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B43" s="4">
-        <v>1</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" s="4">
-        <v>36</v>
+      <c r="D43" s="5">
+        <v>61</v>
+      </c>
+      <c r="E43" s="2">
+        <f>IF(AND(ISNUMBER(F43),ISNUMBER('Reference data'!$B$3)),F43*'Reference data'!$B$3,"Unknown")</f>
+        <v>1.33036425e-05</v>
+      </c>
+      <c r="F43" s="2">
+        <f>IF(D43=0,0,IF(ISNUMBER('Reference data'!D17),D43*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>1.525e-05</v>
+      </c>
+      <c r="G43" s="5">
+        <f>IF(ISNUMBER(E43),ROUND(E43*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H43" s="5">
+        <f>IF(ISNUMBER(F43),ROUND(F43*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>2.0</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="24" customHeight="1">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" s="5">
-        <v>36</v>
-      </c>
-      <c r="E44" s="2">
-        <f>IF(AND(ISNUMBER(F44),ISNUMBER('Reference data'!$B$3)),F44*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.7686384e-05</v>
-      </c>
-      <c r="F44" s="2">
-        <f>IF(D44=0,0,IF(ISNUMBER('Reference data'!E17),D44*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.32e-05</v>
-      </c>
-      <c r="G44" s="5">
-        <f>IF(ISNUMBER(E44),ROUND(E44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H44" s="5">
-        <f>IF(ISNUMBER(F44),ROUND(F44*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="60" customHeight="1">
-      <c r="A45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>108</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>130</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="24" customHeight="1">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="D46" s="5">
+        <v>40</v>
+      </c>
+      <c r="E46" s="2">
+        <f>IF(AND(ISNUMBER(F46),ISNUMBER('Reference data'!$B$3)),F46*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.187376e-05</v>
+      </c>
+      <c r="F46" s="2">
+        <f>IF(D46=0,0,IF(ISNUMBER('Reference data'!E17),D46*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.8e-05</v>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="60" customHeight="1">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="24" customHeight="1">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A48" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="4">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E48" s="2">
-        <f>IF(COUNT('Turns'!E38,'Turns'!E39,'Turns'!E41,'Turns'!E44)=4,SUM('Turns'!E38,'Turns'!E39,'Turns'!E41,'Turns'!E44),"Unknown")</f>
-        <v>8.51258646e-05</v>
-      </c>
-      <c r="F48" s="2">
-        <f>IF(COUNT('Turns'!F38,'Turns'!F39,'Turns'!F41,'Turns'!F44)=4,SUM('Turns'!F38,'Turns'!F39,'Turns'!F41,'Turns'!F44),"Unknown")</f>
-        <v>9.758e-05</v>
-      </c>
-      <c r="G48" s="5">
-        <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H48" s="5">
-        <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="K48" s="4" t="s">
+    <row r="49" spans="1:13" ht="24" customHeight="1">
+      <c r="A49" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D49" s="4">
-        <v>2213</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24" customHeight="1">
-      <c r="A50" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" s="5">
-        <v>2046</v>
-      </c>
       <c r="E50" s="2">
-        <f>IF(AND(ISNUMBER(F50),ISNUMBER('Reference data'!$B$3)),F50*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <f>IF(COUNT('Turns'!E40,'Turns'!E41,'Turns'!E43,'Turns'!E46)=4,SUM('Turns'!E40,'Turns'!E41,'Turns'!E43,'Turns'!E46),"Unknown")</f>
+        <v>8.62686693e-05</v>
       </c>
       <c r="F50" s="2">
-        <f>IF(D50=0,0,IF(ISNUMBER('Reference data'!C17),D50*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.092e-05</v>
+        <f>IF(COUNT('Turns'!F40,'Turns'!F41,'Turns'!F43,'Turns'!F46)=4,SUM('Turns'!F40,'Turns'!F41,'Turns'!F43,'Turns'!F46),"Unknown")</f>
+        <v>9.889e-05</v>
       </c>
       <c r="G50" s="5">
         <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="H50" s="5">
         <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="24" customHeight="1">
-      <c r="A51" t="s">
+        <v>10.0</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A51" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="5">
-        <v>3</v>
-      </c>
-      <c r="E51" s="2">
-        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!B17),D51*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G51" s="5">
-        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="5">
-        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="34" customHeight="1">
+      <c r="B51" s="4">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="4">
+        <v>2210</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="24" customHeight="1">
       <c r="A52" t="s">
         <v>131</v>
       </c>
@@ -1975,10 +1956,26 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>133</v>
+        <v>97</v>
+      </c>
+      <c r="D52" s="5">
+        <v>2046</v>
+      </c>
+      <c r="E52" s="2">
+        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.56973804e-05</v>
+      </c>
+      <c r="F52" s="2">
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!C17),D52*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.092e-05</v>
+      </c>
+      <c r="G52" s="5">
+        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H52" s="5">
+        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="24" customHeight="1">
@@ -1989,29 +1986,29 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D53" s="5">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="E53" s="2">
         <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.576717e-05</v>
+        <v>5.23422e-07</v>
       </c>
       <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!D17),D53*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.1e-05</v>
+        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!B17),D53*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G53" s="5">
         <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H53" s="5">
         <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="24" customHeight="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="34" customHeight="1">
       <c r="A54" t="s">
         <v>131</v>
       </c>
@@ -2019,21 +2016,40 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
+        <v>129</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="24" customHeight="1">
+      <c r="A55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="4">
-        <v>1</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="4">
-        <v>44</v>
+      <c r="D55" s="5">
+        <v>161</v>
+      </c>
+      <c r="E55" s="2">
+        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.51128925e-05</v>
+      </c>
+      <c r="F55" s="2">
+        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!D17),D55*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>4.025e-05</v>
+      </c>
+      <c r="G55" s="5">
+        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H55" s="5">
+        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="24" customHeight="1">
@@ -2044,40 +2060,21 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" s="5">
-        <v>44</v>
-      </c>
-      <c r="E56" s="2">
-        <f>IF(AND(ISNUMBER(F56),ISNUMBER('Reference data'!$B$3)),F56*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.6061136e-05</v>
-      </c>
-      <c r="F56" s="2">
-        <f>IF(D56=0,0,IF(ISNUMBER('Reference data'!E17),D56*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>5.28e-05</v>
-      </c>
-      <c r="G56" s="5">
-        <f>IF(ISNUMBER(E56),ROUND(E56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-      <c r="H56" s="5">
-        <f>IF(ISNUMBER(F56),ROUND(F56*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="60" customHeight="1">
-      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A57" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>134</v>
+      <c r="B57" s="4">
+        <v>1</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="4">
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="24" customHeight="1">
@@ -2088,10 +2085,29 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="D58" s="5">
+        <v>41</v>
+      </c>
+      <c r="E58" s="2">
+        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.2920604e-05</v>
+      </c>
+      <c r="F58" s="2">
+        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.92e-05</v>
+      </c>
+      <c r="G58" s="5">
+        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="60" customHeight="1">
       <c r="A59" t="s">
         <v>131</v>
       </c>
@@ -2099,41 +2115,66 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
+        <v>109</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="24" customHeight="1">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A60" s="4" t="s">
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E60" s="2">
-        <f>IF(COUNT('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56)=4,SUM('Turns'!E50,'Turns'!E51,'Turns'!E53,'Turns'!E56),"Unknown")</f>
-        <v>0.0001180491084</v>
-      </c>
-      <c r="F60" s="2">
-        <f>IF(COUNT('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56)=4,SUM('Turns'!F50,'Turns'!F51,'Turns'!F53,'Turns'!F56),"Unknown")</f>
-        <v>0.00013532</v>
-      </c>
-      <c r="G60" s="5">
-        <f>IF(ISNUMBER(E60),ROUND(E60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="H60" s="5">
-        <f>IF(ISNUMBER(F60),ROUND(F60*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
-      </c>
-      <c r="K60" s="4" t="s">
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="4">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>111</v>
       </c>
+      <c r="E62" s="2">
+        <f>IF(COUNT('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58)=4,SUM('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58),"Unknown")</f>
+        <v>0.0001142542989</v>
+      </c>
+      <c r="F62" s="2">
+        <f>IF(COUNT('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58)=4,SUM('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58),"Unknown")</f>
+        <v>0.00013097</v>
+      </c>
+      <c r="G62" s="5">
+        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>11.0</v>
+      </c>
+      <c r="H62" s="5">
+        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>13.0</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE60">
+  <conditionalFormatting sqref="A2:AE62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2266,7 +2307,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>137</v>
@@ -2275,83 +2316,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D22,'Turns'!D39,'Turns'!D51)=4,SUM('Turns'!D5,'Turns'!D22,'Turns'!D39,'Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D41,'Turns'!D53)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D41,'Turns'!D53),"Unknown")</f>
         <v>12.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E22,'Turns'!E39,'Turns'!E51)=4,SUM('Turns'!E5,'Turns'!E22,'Turns'!E39,'Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E41,'Turns'!E53)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E41,'Turns'!E53),"Unknown")</f>
         <v>2.093688e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F22,'Turns'!F39,'Turns'!F51)=4,SUM('Turns'!F5,'Turns'!F22,'Turns'!F39,'Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F41,'Turns'!F53)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F41,'Turns'!F53),"Unknown")</f>
         <v>2.4e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D38,'Turns'!D50)=2,SUM('Turns'!D38,'Turns'!D50),"Unknown")</f>
-        <v>3810.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D40,'Turns'!D52)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D40,'Turns'!D52),"Unknown")</f>
+        <v>7536.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E38,'Turns'!E50)=2,SUM('Turns'!E38,'Turns'!E50),"Unknown")</f>
-        <v>6.6474594e-05</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E40,'Turns'!E52)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E40,'Turns'!E52),"Unknown")</f>
+        <v>0.0001314836064</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F38,'Turns'!F50)=2,SUM('Turns'!F38,'Turns'!F50),"Unknown")</f>
-        <v>7.62e-05</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F40,'Turns'!F52)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F40,'Turns'!F52),"Unknown")</f>
+        <v>0.00015072</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D9,'Turns'!D25,'Turns'!D41,'Turns'!D53)=4,SUM('Turns'!D9,'Turns'!D25,'Turns'!D41,'Turns'!D53),"Unknown")</f>
-        <v>4048.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D43,'Turns'!D55)=3,SUM('Turns'!D27,'Turns'!D43,'Turns'!D55),"Unknown")</f>
+        <v>282.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E9,'Turns'!E25,'Turns'!E41,'Turns'!E53)=4,SUM('Turns'!E9,'Turns'!E25,'Turns'!E41,'Turns'!E53),"Unknown")</f>
-        <v>0.00088283844</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E43,'Turns'!E55)=3,SUM('Turns'!E27,'Turns'!E43,'Turns'!E55),"Unknown")</f>
+        <v>6.1502085e-05</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F9,'Turns'!F25,'Turns'!F41,'Turns'!F53)=4,SUM('Turns'!F9,'Turns'!F25,'Turns'!F41,'Turns'!F53),"Unknown")</f>
-        <v>0.001012</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F43,'Turns'!F55)=3,SUM('Turns'!F27,'Turns'!F43,'Turns'!F55),"Unknown")</f>
+        <v>7.05e-05</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D29,'Turns'!D44,'Turns'!D56)=4,SUM('Turns'!D13,'Turns'!D29,'Turns'!D44,'Turns'!D56),"Unknown")</f>
-        <v>194.0</v>
+        <f>IF(COUNT('Turns'!D14,'Turns'!D31,'Turns'!D46,'Turns'!D58)=4,SUM('Turns'!D14,'Turns'!D31,'Turns'!D46,'Turns'!D58),"Unknown")</f>
+        <v>185.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E29,'Turns'!E44,'Turns'!E56)=4,SUM('Turns'!E13,'Turns'!E29,'Turns'!E44,'Turns'!E56),"Unknown")</f>
-        <v>0.000203087736</v>
+        <f>IF(COUNT('Turns'!E14,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E14,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.00019366614</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F29,'Turns'!F44,'Turns'!F56)=4,SUM('Turns'!F13,'Turns'!F29,'Turns'!F44,'Turns'!F56),"Unknown")</f>
-        <v>0.0002328</v>
+        <f>IF(COUNT('Turns'!F14,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F14,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.000222</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D28)=2,SUM('Turns'!D12,'Turns'!D28),"Unknown")</f>
-        <v>65.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D30)=2,SUM('Turns'!D13,'Turns'!D30),"Unknown")</f>
+        <v>55.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E28)=2,SUM('Turns'!E12,'Turns'!E28),"Unknown")</f>
-        <v>6.804486e-05</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E30)=2,SUM('Turns'!E13,'Turns'!E30),"Unknown")</f>
+        <v>5.757642e-05</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F28)=2,SUM('Turns'!F12,'Turns'!F28),"Unknown")</f>
-        <v>7.8e-05</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F30)=2,SUM('Turns'!F13,'Turns'!F30),"Unknown")</f>
+        <v>6.6e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60)=4,SUM('Turns'!E17,'Turns'!E33,'Turns'!E48,'Turns'!E60),"Unknown")</f>
-        <v>0.001222539318</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004463219394</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60)=4,SUM('Turns'!F17,'Turns'!F33,'Turns'!F48,'Turns'!F60),"Unknown")</f>
-        <v>0.0014014</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00051162</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>122.0</v>
+        <v>45.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>140.0</v>
+        <v>51.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>6523.83</v>
+        <v>7492.497</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>138</v>
@@ -2371,7 +2412,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>140</v>
@@ -2383,7 +2424,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.415</v>
+        <v>0.422</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>142</v>
@@ -2403,7 +2444,7 @@
         <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>144</v>
@@ -2415,80 +2456,80 @@
         <v>49</v>
       </c>
       <c r="J4" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K4" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L4" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K4" s="2">
+        <v>2046.0</v>
+      </c>
+      <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L4" s="2">
+        <v>3.56973804e-05</v>
+      </c>
+      <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M4" s="2">
+        <v>4.092e-05</v>
+      </c>
+      <c r="P4" s="2">
         <v>0</v>
       </c>
-      <c r="N4" s="2">
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
+      <c r="R4" s="2">
         <v>0</v>
       </c>
-      <c r="P4" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="Q4" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000446217255</v>
-      </c>
-      <c r="R4" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.0005115</v>
-      </c>
       <c r="S4" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>83.0</v>
+      </c>
+      <c r="T4" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>8.6888052e-05</v>
+      </c>
+      <c r="U4" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>9.96e-05</v>
+      </c>
+      <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>93.0</v>
-      </c>
-      <c r="T4" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>9.7356492e-05</v>
-      </c>
-      <c r="U4" s="2">
+        <v>3.3499008e-05</v>
+      </c>
+      <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001116</v>
-      </c>
-      <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>3.84e-05</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000574455645</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>0.0001566078624</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0006585</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>0.00017952</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>18.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2566.468</v>
+        <v>3419.856</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>138</v>
@@ -2508,7 +2549,7 @@
         <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1">
         <v>2049</v>
@@ -2523,83 +2564,83 @@
         <v>145</v>
       </c>
       <c r="J5" s="2">
+        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K5" s="2">
+        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
+        <v>5.23422e-07</v>
+      </c>
+      <c r="L5" s="2">
+        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M5" s="2">
         <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K5" s="2">
+        <v>2046.0</v>
+      </c>
+      <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="L5" s="2">
+        <v>3.56973804e-05</v>
+      </c>
+      <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M5" s="2">
+        <v>4.092e-05</v>
+      </c>
+      <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="N5" s="2">
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="O5" s="2">
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="P5" s="2">
-        <f>IF(COUNT('Turns'!D9)=1,SUM('Turns'!D9),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <f>IF(COUNT('Turns'!E9)=1,SUM('Turns'!E9),"Unknown")</f>
-        <v>0.000446217255</v>
-      </c>
-      <c r="R5" s="2">
-        <f>IF(COUNT('Turns'!F9)=1,SUM('Turns'!F9),"Unknown")</f>
-        <v>0.0005115</v>
-      </c>
       <c r="S5" s="2">
+        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
+        <v>83.0</v>
+      </c>
+      <c r="T5" s="2">
+        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
+        <v>8.6888052e-05</v>
+      </c>
+      <c r="U5" s="2">
+        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
+        <v>9.96e-05</v>
+      </c>
+      <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>93.0</v>
-      </c>
-      <c r="T5" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>9.7356492e-05</v>
-      </c>
-      <c r="U5" s="2">
+        <v>3.3499008e-05</v>
+      </c>
+      <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>0.0001116</v>
-      </c>
-      <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>29.0</v>
-      </c>
-      <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>3.0358476e-05</v>
-      </c>
-      <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>3.84e-05</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>0.000574455645</v>
+        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
+        <v>0.0001566078624</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>0.0006585</v>
+        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
+        <v>0.00017952</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>18.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2555.741</v>
+        <v>3413.269</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>149</v>
@@ -2619,7 +2660,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>151</v>
@@ -2631,83 +2672,83 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D22,'Turns'!D39)=2,SUM('Turns'!D22,'Turns'!D39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E39)=2,SUM('Turns'!E22,'Turns'!E39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
         <v>1.046844e-06</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F39)=2,SUM('Turns'!F22,'Turns'!F39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
+        <v>3444.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>3.07772136e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
+        <v>6.00888456e-05</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>3.528e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
+        <v>6.888e-05</v>
       </c>
       <c r="P6" s="2">
-        <f>IF(COUNT('Turns'!D25,'Turns'!D41)=2,SUM('Turns'!D25,'Turns'!D41),"Unknown")</f>
-        <v>1838.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
+        <v>121.0</v>
       </c>
       <c r="Q6" s="2">
-        <f>IF(COUNT('Turns'!E25,'Turns'!E41)=2,SUM('Turns'!E25,'Turns'!E41),"Unknown")</f>
-        <v>0.000400854015</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
+        <v>2.63891925e-05</v>
       </c>
       <c r="R6" s="2">
-        <f>IF(COUNT('Turns'!F25,'Turns'!F41)=2,SUM('Turns'!F25,'Turns'!F41),"Unknown")</f>
-        <v>0.0004595</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
+        <v>3.025e-05</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D29,'Turns'!D44)=2,SUM('Turns'!D29,'Turns'!D44),"Unknown")</f>
-        <v>57.0</v>
+        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E29,'Turns'!E44)=2,SUM('Turns'!E29,'Turns'!E44),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>6.3857484e-05</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F29,'Turns'!F44)=2,SUM('Turns'!F29,'Turns'!F44),"Unknown")</f>
-        <v>6.84e-05</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>7.32e-05</v>
       </c>
       <c r="V6" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>23.0</v>
       </c>
       <c r="W6" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>2.4077412e-05</v>
       </c>
       <c r="X6" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.76e-05</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E33,'Turns'!E48)=2,SUM('Turns'!E33,'Turns'!E48),"Unknown")</f>
-        <v>0.0005300345646</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
+        <v>0.0001754597781</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F33,'Turns'!F48)=2,SUM('Turns'!F33,'Turns'!F48),"Unknown")</f>
-        <v>0.00060758</v>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
+        <v>0.00020113</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>61.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>2361.954</v>
+        <v>2781.037</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>138</v>
@@ -2727,95 +2768,95 @@
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>155</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I7" t="s">
         <v>152</v>
       </c>
       <c r="J7" s="2">
-        <f>IF(COUNT('Turns'!D22,'Turns'!D39)=2,SUM('Turns'!D22,'Turns'!D39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K7" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E39)=2,SUM('Turns'!E22,'Turns'!E39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
         <v>1.046844e-06</v>
       </c>
       <c r="L7" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F39)=2,SUM('Turns'!F22,'Turns'!F39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M7" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
+        <v>3444.0</v>
       </c>
       <c r="N7" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>3.07772136e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
+        <v>6.00888456e-05</v>
       </c>
       <c r="O7" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>3.528e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
+        <v>6.888e-05</v>
       </c>
       <c r="P7" s="2">
-        <f>IF(COUNT('Turns'!D25,'Turns'!D41)=2,SUM('Turns'!D25,'Turns'!D41),"Unknown")</f>
-        <v>1838.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
+        <v>121.0</v>
       </c>
       <c r="Q7" s="2">
-        <f>IF(COUNT('Turns'!E25,'Turns'!E41)=2,SUM('Turns'!E25,'Turns'!E41),"Unknown")</f>
-        <v>0.000400854015</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
+        <v>2.63891925e-05</v>
       </c>
       <c r="R7" s="2">
-        <f>IF(COUNT('Turns'!F25,'Turns'!F41)=2,SUM('Turns'!F25,'Turns'!F41),"Unknown")</f>
-        <v>0.0004595</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
+        <v>3.025e-05</v>
       </c>
       <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D29,'Turns'!D44)=2,SUM('Turns'!D29,'Turns'!D44),"Unknown")</f>
-        <v>57.0</v>
+        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E29,'Turns'!E44)=2,SUM('Turns'!E29,'Turns'!E44),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>6.3857484e-05</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F29,'Turns'!F44)=2,SUM('Turns'!F29,'Turns'!F44),"Unknown")</f>
-        <v>6.84e-05</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>7.32e-05</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>23.0</v>
       </c>
       <c r="W7" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>2.4077412e-05</v>
       </c>
       <c r="X7" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.76e-05</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E33,'Turns'!E48)=2,SUM('Turns'!E33,'Turns'!E48),"Unknown")</f>
-        <v>0.0005300345646</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
+        <v>0.0001754597781</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F33,'Turns'!F48)=2,SUM('Turns'!F33,'Turns'!F48),"Unknown")</f>
-        <v>0.00060758</v>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
+        <v>0.00020113</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>61.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>2359.774</v>
+        <v>2778.92</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>138</v>
@@ -2835,7 +2876,7 @@
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>157</v>
@@ -2844,86 +2885,86 @@
         <v>158</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D22,'Turns'!D39)=2,SUM('Turns'!D22,'Turns'!D39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E39)=2,SUM('Turns'!E22,'Turns'!E39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
         <v>1.046844e-06</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F39)=2,SUM('Turns'!F22,'Turns'!F39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
+        <v>3444.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>3.07772136e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
+        <v>6.00888456e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>3.528e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
+        <v>6.888e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D25,'Turns'!D41)=2,SUM('Turns'!D25,'Turns'!D41),"Unknown")</f>
-        <v>1838.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
+        <v>121.0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E25,'Turns'!E41)=2,SUM('Turns'!E25,'Turns'!E41),"Unknown")</f>
-        <v>0.000400854015</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
+        <v>2.63891925e-05</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F25,'Turns'!F41)=2,SUM('Turns'!F25,'Turns'!F41),"Unknown")</f>
-        <v>0.0004595</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
+        <v>3.025e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D29,'Turns'!D44)=2,SUM('Turns'!D29,'Turns'!D44),"Unknown")</f>
-        <v>57.0</v>
+        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E29,'Turns'!E44)=2,SUM('Turns'!E29,'Turns'!E44),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>6.3857484e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F29,'Turns'!F44)=2,SUM('Turns'!F29,'Turns'!F44),"Unknown")</f>
-        <v>6.84e-05</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>7.32e-05</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>23.0</v>
       </c>
       <c r="W8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>2.4077412e-05</v>
       </c>
       <c r="X8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.76e-05</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E33,'Turns'!E48)=2,SUM('Turns'!E33,'Turns'!E48),"Unknown")</f>
-        <v>0.0005300345646</v>
+        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
+        <v>0.0001754597781</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F33,'Turns'!F48)=2,SUM('Turns'!F33,'Turns'!F48),"Unknown")</f>
-        <v>0.00060758</v>
+        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
+        <v>0.00020113</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>53.0</v>
+        <v>18.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>61.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>2358.488</v>
+        <v>2777.493</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>138</v>
@@ -2943,7 +2984,7 @@
         <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>140</v>
@@ -2955,7 +2996,7 @@
         <v>158</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.627</v>
+        <v>1.968</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>142</v>
@@ -2975,7 +3016,7 @@
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>144</v>
@@ -2987,80 +3028,83 @@
         <v>158</v>
       </c>
       <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>1692.0</v>
       </c>
       <c r="N10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>2.95210008e-05</v>
       </c>
       <c r="O10" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>3.384e-05</v>
       </c>
       <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>60.0</v>
       </c>
       <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00038471517</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>1.308555e-05</v>
       </c>
       <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000441</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>1.5e-05</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
         <v>21.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
         <v>2.1983724e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
         <v>2.52e-05</v>
       </c>
       <c r="V10" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>23.0</v>
       </c>
       <c r="W10" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>2.4077412e-05</v>
       </c>
       <c r="X10" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.76e-05</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.0004449087</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>8.91911088e-05</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.00051</v>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
+        <v>0.00010224</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>1267.331</v>
+        <v>1288.434</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>138</v>
@@ -3080,98 +3124,101 @@
         <v>95</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11" s="1">
-        <v>1767</v>
+        <v>1755</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>148</v>
       </c>
       <c r="H11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I11" t="s">
         <v>162</v>
       </c>
       <c r="J11" s="2">
-        <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K11" s="2">
-        <f>IF(COUNT('Turns'!E22)=1,SUM('Turns'!E22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L11" s="2">
-        <f>IF(COUNT('Turns'!F22)=1,SUM('Turns'!F22),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M11" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
+        <v>1692.0</v>
       </c>
       <c r="N11" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
+        <v>2.95210008e-05</v>
       </c>
       <c r="O11" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
+        <v>3.384e-05</v>
       </c>
       <c r="P11" s="2">
-        <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>60.0</v>
       </c>
       <c r="Q11" s="2">
-        <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.00038471517</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>1.308555e-05</v>
       </c>
       <c r="R11" s="2">
-        <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.000441</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>1.5e-05</v>
       </c>
       <c r="S11" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
         <v>21.0</v>
       </c>
       <c r="T11" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
         <v>2.1983724e-05</v>
       </c>
       <c r="U11" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
         <v>2.52e-05</v>
       </c>
       <c r="V11" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>23.0</v>
       </c>
       <c r="W11" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>2.4077412e-05</v>
       </c>
       <c r="X11" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.76e-05</v>
       </c>
       <c r="Y11" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.0004449087</v>
+        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
+        <v>8.91911088e-05</v>
       </c>
       <c r="Z11" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.00051</v>
+        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
+        <v>0.00010224</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>10.0</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AD11" s="1">
-        <v>1259.495</v>
+        <v>1279.812</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>149</v>
@@ -3191,7 +3238,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>151</v>
@@ -3203,7 +3250,7 @@
         <v>158</v>
       </c>
       <c r="AD12" s="1">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>142</v>
@@ -3223,19 +3270,19 @@
         <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>167</v>
       </c>
       <c r="H13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
         <v>165</v>
       </c>
       <c r="AD13" s="1">
-        <v>1.473</v>
+        <v>0.723</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>142</v>
@@ -3255,7 +3302,7 @@
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>144</v>
@@ -3267,52 +3314,52 @@
         <v>158</v>
       </c>
       <c r="J14" s="2">
-        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K14" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L14" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M14" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>1752.0</v>
       </c>
       <c r="N14" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>3.07772136e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>3.05678448e-05</v>
       </c>
       <c r="O14" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>3.528e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>3.504e-05</v>
       </c>
       <c r="P14" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>74.0</v>
+        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="Q14" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.6138845e-05</v>
+        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
+        <v>1.33036425e-05</v>
       </c>
       <c r="R14" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>1.85e-05</v>
+        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
+        <v>1.525e-05</v>
       </c>
       <c r="S14" s="2">
-        <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T14" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>4.187376e-05</v>
       </c>
       <c r="U14" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V14" s="2">
         <v>0</v>
@@ -3324,12 +3371,12 @@
         <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>8.51258646e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>8.62686693e-05</v>
       </c>
       <c r="Z14" s="2">
-        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>9.758e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>9.889e-05</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3340,7 +3387,7 @@
         <v>10.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1082.201</v>
+        <v>1478.562</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>138</v>
@@ -3360,67 +3407,67 @@
         <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F15" s="1">
-        <v>1841</v>
+        <v>1816</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>148</v>
       </c>
       <c r="H15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I15" t="s">
         <v>168</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D38)=1,SUM('Turns'!D38),"Unknown")</f>
-        <v>1764.0</v>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
+        <v>1752.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E38)=1,SUM('Turns'!E38),"Unknown")</f>
-        <v>3.07772136e-05</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>3.05678448e-05</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F38)=1,SUM('Turns'!F38),"Unknown")</f>
-        <v>3.528e-05</v>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
+        <v>3.504e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
-        <v>74.0</v>
+        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
+        <v>61.0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>1.6138845e-05</v>
+        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
+        <v>1.33036425e-05</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
-        <v>1.85e-05</v>
+        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
+        <v>1.525e-05</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D44)=1,SUM('Turns'!D44),"Unknown")</f>
-        <v>36.0</v>
+        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E44)=1,SUM('Turns'!E44),"Unknown")</f>
-        <v>3.7686384e-05</v>
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>4.187376e-05</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F44)=1,SUM('Turns'!F44),"Unknown")</f>
-        <v>4.32e-05</v>
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V15" s="2">
         <v>0</v>
@@ -3432,12 +3479,12 @@
         <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
-        <v>8.51258646e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>8.62686693e-05</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
-        <v>9.758e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>9.889e-05</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3448,10 +3495,10 @@
         <v>10.0</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AD15" s="1">
-        <v>1076.156</v>
+        <v>1474.575</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>149</v>
@@ -3471,7 +3518,7 @@
         <v>47</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>144</v>
@@ -3483,52 +3530,52 @@
         <v>49</v>
       </c>
       <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>2046.0</v>
       </c>
       <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
         <v>3.56973804e-05</v>
       </c>
       <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>164.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>161.0</v>
       </c>
       <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>3.576717e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>3.51128925e-05</v>
       </c>
       <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.1e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>4.025e-05</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>44.0</v>
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>41.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>4.6061136e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>4.2920604e-05</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>5.28e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>4.92e-05</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
@@ -3540,23 +3587,23 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0001180491084</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.0001142542989</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00013532</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00013097</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>1583.925</v>
+        <v>1285.334</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>138</v>
@@ -3576,10 +3623,10 @@
         <v>95</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F17" s="1">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>148</v>
@@ -3591,52 +3638,52 @@
         <v>169</v>
       </c>
       <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
         <v>5.23422e-07</v>
       </c>
       <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D50)=1,SUM('Turns'!D50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>2046.0</v>
       </c>
       <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
         <v>3.56973804e-05</v>
       </c>
       <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>164.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>161.0</v>
       </c>
       <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>3.576717e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>3.51128925e-05</v>
       </c>
       <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>4.1e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>4.025e-05</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D56)=1,SUM('Turns'!D56),"Unknown")</f>
-        <v>44.0</v>
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>41.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E56)=1,SUM('Turns'!E56),"Unknown")</f>
-        <v>4.6061136e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>4.2920604e-05</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F56)=1,SUM('Turns'!F56),"Unknown")</f>
-        <v>5.28e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>4.92e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -3648,26 +3695,26 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E60)=1,SUM('Turns'!E60),"Unknown")</f>
-        <v>0.0001180491084</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.0001142542989</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F60)=1,SUM('Turns'!F60),"Unknown")</f>
-        <v>0.00013532</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00013097</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="AC17" s="1" t="s">
         <v>131</v>
       </c>
       <c r="AD17" s="1">
-        <v>1578.684</v>
+        <v>1280.525</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>149</v>

--- a/reports/subagent_chat/report.xlsx
+++ b/reports/subagent_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="170">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce3-0d9c-7b70-86d0-3dd59612ee78</t>
+    <t>01a0d142-b71b-72b0-beb4-02a590022f96</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,13 +306,13 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce3-0da5-7a50-834d-622dd2173e09</t>
+    <t>01a0d142-b724-75f2-acca-1970e25f6cbe</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>Fresh input</t>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -348,8 +348,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_02356a6adfa3262b006ab36d545a0887d2a6efeb552fef21db", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21UhmGF_evNgNySwNWT3cv80iSB8gIH9tgYVoXADn7z_t-cNNvPxdJZaAScctN-X4I6-ZMmVsj5v7C8gfEnw1QN4Qvae5pbeO93SMSwo_KHscPnM03UH-KDMw4WL1EdlMltY0ZJ1LOb0xBpDD_1ByAc1RPP5a-xUMiavi4Rg8HKwAYHD5OA4kWQSCIHJl2UiZ4kXr-tf7aqIdNYlr1l5lo9MjrdaxD1cwZ5AAZpzLDL7zGPiVHOz2L3fQpcyPk176JawLHtepeq0vUgWgIUqPXMwY9OfmXrX_0u02fE8D8l11Oe_UuM7-6Ywe0LiYYVxslSsen2DYli5INYnCDPqUJGO38F_0JSdX-Ln1NanyNN2TotaFInFayUDM6-IG3RYugXt59Jt3_P-4qNbgOP0lncMWgSHxctjIjx89vaYz3hjz2WBSBGCndPvOtq5uN8cmMrcJKkjTiRjHCnV3SEtR2kG-QZfNkyi5d2Crgsxr4qXd3zTi-0qudQsgreJshvtcIvg0fjs9xrORUIXdcGCwXgnksdSgHjvhrCiWiEeXxLtyWR0FQjNRyEQpvkzm3Q32rzLO1SVyuDMJczrNhoxOrGpEV5z66mI1au4iTMA3JSt2DchmrmCfVIupMoq8mneUWjF1umBH8jtbJHIAD9uwL-WcwY4ihkiyaoyWfO-plJS2EWmDvdgsZqCkgBOe5HaDLB7IZND7pYK078Tgd7WaG5761vEaeAAj30JD5bXzvV4IeJEYp1Xt5Tico4mujjTnOAvJgVhKXri8Gxb4ypMQr59_n-z26epV8h9aqisFY3j-gEGM6NLPESvJcu4gHF3Rswszs3qsh68Wk_7whd0QeG3zZS71bSii3vcJD28uMNEXV6AE3U33oifUE4dveZt7eNxbNGN4QHx7G3FqaLr81mBssnAfgmm0aIFoI-vGK58oXKg_kSANnvwdiVqYS-VPbA-V9JB_kfYHzQ58il62TgiPPgyHpLZ0n3KIQlO7DqcS3wc2V3o0FDnV8l7VnneDpD_1f9HW2IBy80Qld1vTCXpDRryFT_hvT4kNO-m82O-bdZANS6hdjiuf9UVgJbY_gg1DODBgxXjmc8n1T0nE3ms-2EDILmGbGMAHp5oUROHkAh8av1LD8wFSceTYMCkRRgYxlK1fPDh5KPSt8VO1TVZl8fleknHB41-4DbtyfBAy2wOhDBJEkpV7u0aHcuO4VJeo63s307AwV93EfukQm6mdEMMJxS48DdYuVojm_OTF7Ovfgm5qwhu7cN2Djd_ieXGauYZ2mcnT1tvYAHDAXmXQtD0AapNcnZobo7S3XJsA_ceLOkCp5lXnFQZdgrSTO4WSDodeeJws3SIn0pZH4Kww=="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Echo the exact supplied text: \\\"ReAct\\\". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.\",\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_GvpxgR5ep2QOYbL19IiPbs5S", "id": "fc_02356a6adfa3262b006ab36d54e44087d2bde1e47362f66de5", "index": 1}]
-{"name": "task", "args": {"description": "Echo the exact supplied text: \"ReAct\". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.", "subagent_type": "isolated-subagent"}, "id": "call_GvpxgR5ep2QOYbL19IiPbs5S", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0b0f4e337a0b72c1006ab48bf66d3087d2a421e4e726bcd8a1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIv25sVZByrJ-Z1P3JBd7ZG5d1EHcxU3cLqgJw2OVwVz_sUvMzXuQ54Dlf-Nc-CybCYivsJQqwSSYNWu3ZtF44YybnYXCP1yhXm-svXO7QBMsCEEr3biaYnqFPKgUs0INILl4s0GnN2lJUPcbAuJs8UTsk11mOFO3pDQZomzHkSCS4QA_JHH0pVVo291NidvDtwlGFO-lzVVRuhKWx1coEbG40eXiEYDmwO2sfDFuLloTLp_22eRk_YoWfPXc2Rq9GqREs79lLzUTpD3W2sWFTIP4HESBXY9BXj3q1b1RrXibmWe4VeuIGpfKKPcsL4vG2TsMUpUiTbi8o_K8t6kvvj2F8fDlUb63hg65NrNOuD7UTw7JIIKbzCM7uUS5e5Mv18ggZr7dgsvJZEtyyHjzohecCOdxOdUVECQKAnXIh1wlkJpsEkQ5XIm1xRKA_vY40U5NKSD2TCJx2RgS18-REeW35C5rsAtY4EJosEq59A0NbC8eaBZmuiJ-HSYZQWBzzBt-a7fNfOS6ZcLzfl9vY5O6qHg-knEQG1DFjfhRLfqx2s1ToNci2MeLmA-uSkcDNBrot0EYsZe_vRnGouaA63AT-3mHe8txI-mHlcfoki-hjr6O3s16BCkkNSVp7xZNhFouAUabriJS5wbhLgT-jMOU9pMYp7TbO3vTwz7KDSLjKRwU8PKFuAaDg-KFNNFAF6AS3793pV571CUG1zpV4DqWKQW7mjgENRNx08XKSqeJVCx_KYvvSSbw_Y6Bu89PLOdCLzLbCFSwQy14OfYmO9jtHwVjgU1GPAsVIUf24VtfCylS4TsX4ek7_bXyUAyLrFuqdwQD16o2QPBj5fJnMXv1ia47V2UqxPyV_LC_d5yjub2-n4NWTTlZ5zc5n9nD1fphDLDax3-PL_culI0z-8J90sCiccxK2N-PHlldf_c3YB3dkD-K-3DWrpmigW_jPxGxvLDn-CcAaJsshixbyYyB3FuTm8Avq_mG4qQFbkc9gy8RehGlVR5RiaWwCqESQZNoS51gBnpxL2ku194_eRtngi2v2ACyD3vs8F5SLyAgPIbKbcWTXoc90MnZ2j2Wt7YchL3yPbvtGMWyjjbqnNRkcMQTf78EWmOn1L2BHWUA7Td1b2zqHqCODJyRQORWx7M-K63sxD4rNJCUjk_lf1XvNOL11sBskrcpWsT55UijHjuwsXhPzjESsLLPYPEogMjKBBb_tHGGW885kJ17rcp4kqfW4G31XGx6Ra2UcvU8lChMdrQbGv09XhTvmkDOkCjeFOgnEqeYwp6Ti-h2jPXnl2AbPIFd4TfiIU3uFBHHrpl6rmYRrLid_RpEG5senAewTYoahEN11gOQnfW4Q-V4Q=="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.\" ,\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_2F51dvYjDannP4m8M1mgKlqk", "id": "fc_0b0f4e337a0b72c1006ab48bf6b2c087d290baa7c279eb01e3", "index": 1}]
+{"name": "task", "args": {"description": "Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.", "subagent_type": "isolated-subagent"}, "id": "call_2F51dvYjDannP4m8M1mgKlqk", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -361,38 +361,38 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0cce3-1afe-7ec0-bb7c-537b7d189ad9</t>
+    <t>01a0d142-bf27-7823-ad57-670a30c3a8f1</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': 'Echo the exact supplied text: "ReAct". Then briefly explain how your tool result is returned to the parent agent: state that your result is returned as a tool response/summary to the parent, which can then use it in its final answer. Do not add unrelated content.', 'subagent_type': 'isolated-subagent'}</t>
+    <t>{'description': 'Use your echo tool to echo exactly the supplied text: “ReAct”. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.', 'subagent_type': 'isolated-subagent'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='The tool returned: “Your input was: ReAct”. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.', tool_call_id='call_GvpxgR5ep2QOYbL19IiPbs5S')]})</t>
+    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='The echoed result is returned to the parent agent as the task result/summary: “ReAct”.', tool_call_id='call_2F51dvYjDannP4m8M1mgKlqk')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce3-1b09-7dc1-9c13-d7ac69a85691</t>
+    <t>01a0d142-bf30-7c72-93e6-527e44423b76</t>
   </si>
   <si>
     <t>You are a workflow teaching specialist. Call echo_tool with the assigned text, then summarize the returned echo for the parent. The echo repeats supplied input and provides no independent factual evidence. Do not delegate further.</t>
   </si>
   <si>
-    <t>[{"id": "rs_09300af7f4472580006ab36d57636487d288881c928d0de5f9", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs21XfU0YomilKv-MqloXyKMUrLz0PLAnkuxs2S3eiw3fUwBG8tyiHVBmThWqi6SEDFzAgBMdkhC3nSH8FSi_8yj6O2V3ZyKlSFW2GjJLy8kX7tdAtV4dJ3vxP0f-V1Yppk7yYTWqqdsNfNfIGngbZkicwcMfHNlsHZ5DicWHaTvmBSdxq3SzceWSdyPw2qWYeae7KsHTFMlBaRPxoSIQYDMuUL0-0IQ5y8g9yx_hy2UcW6N9bhgOOg3KSP1yM3on9vd3zGSCxTrHHqytNrFn7VLFj9L7oJkWMIkyOaJtNsUgN85tmOiWk1hyhVrka8Gyskwv-6V7kCQroq00ghAI1XU5ntI89aVO6hgx8xGa2y-WErw-2NdSpNjFQNFC0fS0GMNWJRaaFuiYpWGZufoReibA72NvZKlelKKzcCQK8epnThhutNG1wMUC9ZRV0g_vn4Z-GjtitNJ8laa7Fn5f08iEpQVkocuSIGIxp6TmGJpp7j2B1QANrGiRFonan5344sKYJoav-fTlbbw1WsBFC7aseDsvYrq6y949XGhaYZRFfPgVAC5sewCsD3jdSB3TMV5EOUNB1nieTv7nFouh3lXJHOQZ9p02Nl1pSmBOFQVdXtJj6CzAnTfwsQfBeNHEdTByc0MbjPssuCHPfaaf6r8uIaY5j5Eq7PRmL3YMRfzS52TpDWm5psdN1TiNGDxUbxjw0UPiVahCGApovU-7QuJA5sZuaDFV8Ey6NISRkny5jOg_mmX4Avu_AN3GxvpdT-0zegSqBDhUvMseACxiON09p4agxT8ALeB2GO6E7ejVQ9l7BkSV6lJJ2hMRI3UxbQ9PM-T-HAKWxKX4j2qluuEw6OCS_MIeUg4mFwl1zOHmc22D5c3Z5HtSX3qwpbLs92kU0kMENFpyljaBU5r0Qa7mLG6B0OPRureLxBt6qneiLCoyj9MY9ioA6vhYvuT1Hsjy6fLQLov_BwG5BK6_EHNpIE-z6Iqt5_h4DFp7mDSQ0LIIW-N55SDSeG63EojZHlpTEb96QntkYc1XWAMudhQ3rr5iixXxdKBlI95P5k6lUpCAFJ9Hf8CfyKgUWwjDGGGJqby-_iLEcrA54Uii_mf4w2JPNTcgMbQ8HUByn9bMyrVJBk4Gd7BGOS63uNBrwKf8oxw11NZiZBN6wE7_GycYN5RjBaSdiH7eDs54MLzNGrtg2HyxUU9O0vgndwrryqWc0JexCAWOW3c1UV9l5NIDs8C83EbcKsBmLvcBjQjhB9RdYRpuchxjtYRbgualkgqdxieBO_pSySPJSaXyp8tkTA=="}, {"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_3xW3L97jhorBQsp82zzndopP", "id": "fc_09300af7f4472580006ab36d57d1f087d29dab905fbfe61298", "index": 1}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_3xW3L97jhorBQsp82zzndopP", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_ZtmMfMRzgGQF48ppM5b3oeJj", "id": "fc_0c8eb20f1d11b30a006ab48bf8786087d29be9c77d997d91a8", "index": 0}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_ZtmMfMRzgGQF48ppM5b3oeJj", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0cce3-200e-7061-a841-7c3f88238d8f</t>
+    <t>01a0d142-c402-7003-97f2-f06a70c12f41</t>
   </si>
   <si>
     <t>{'text': 'ReAct'}</t>
@@ -404,25 +404,25 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cce3-2013-71d3-a69f-0435e63e9c0a</t>
+    <t>01a0d142-c40c-7212-be6f-e0524469d562</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The tool returned: \u201cYour input was: ReAct\u201d. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.", "phase": "final_answer", "index": 0, "id": "msg_09300af7f4472580006ab36d58d6dc87d2b56059e0173862c6"}]</t>
+    <t>[{"type": "text", "text": "The echoed result is returned to the parent agent as the task result/summary: \u201cReAct\u201d.", "phase": "final_answer", "index": 0, "id": "msg_0c8eb20f1d11b30a006ab48bf98f9087d286f37b9d43a2992a"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cce3-25de-7380-bafd-de3809be4210</t>
-  </si>
-  <si>
-    <t>The tool returned: “Your input was: ReAct”. This result is returned as a tool response/summary to the parent, which can then use it in its final answer.</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The specialist echoed: **\u201cReAct.\u201d**\n\nIts tool result returns to the parent agent as a tool response/summary. The parent can then incorporate that result into its final answer.", "phase": "final_answer", "index": 0, "id": "msg_02356a6adfa3262b006ab36d5a251487d2879a79d5c7a84ffa"}]</t>
+    <t>01a0d142-c812-7833-9af0-84a4704eb738</t>
+  </si>
+  <si>
+    <t>The echoed result is returned to the parent agent as the task result/summary: “ReAct”.</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The specialist echoed: **\u201cReAct\u201d**.\n\nIts tool result is returned to the parent through the specialist\u2019s task summary, which the parent can then incorporate into its response.", "phase": "final_answer", "index": 0, "id": "msg_0b0f4e337a0b72c1006ab48bfa80d087d2b1859aa25c26069c"}]</t>
   </si>
   <si>
     <t>delegating_parent</t>
@@ -443,7 +443,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0cce3-0d9f-76b3-b4e3-3ecec2bcc9ba</t>
+    <t>01a0d142-b71e-7ab0-b926-2b8b25bf1742</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -455,7 +455,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce3-0da0-7452-830a-a8f457830cb9</t>
+    <t>01a0d142-b71f-70e2-9e32-05658451738d</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -476,7 +476,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce3-1afd-7ea0-b6ce-0756d2a9edb4</t>
+    <t>01a0d142-bf26-7741-b420-f46b9e717e95</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -504,19 +504,19 @@
     <t>Execute the isolated-subagent workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cce3-1aff-7cd1-9b61-cfb541f61ffe</t>
+    <t>01a0d142-bf28-7271-86b3-1e331d71c795</t>
   </si>
   <si>
     <t xml:space="preserve">                PatchToolCallsMiddleware.before_agent</t>
   </si>
   <si>
-    <t>01a0cce3-1b00-7b32-bac1-abcf104178f2</t>
+    <t>01a0d142-bf29-7461-be33-f6953eb29004</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0cce3-1b03-7c21-8473-8bd7f8a447f4</t>
+    <t>01a0d142-bf2b-7952-b975-77f2aa546f40</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -525,7 +525,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0cce3-200c-7d63-b35e-cf59862af41b</t>
+    <t>01a0d142-c401-78f3-8dda-1148024ee64f</t>
   </si>
   <si>
     <t xml:space="preserve">                    echo_tool</t>
@@ -534,10 +534,10 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0cce3-2010-7142-8124-2e5578174a35</t>
-  </si>
-  <si>
-    <t>01a0cce3-25db-7ee1-bec9-c17131f78393</t>
+    <t>01a0d142-c406-72a1-8af6-1a63f774d36b</t>
+  </si>
+  <si>
+    <t>01a0d142-c80c-7be0-bd88-a2523a23fd5b</t>
   </si>
 </sst>
 </file>
@@ -944,7 +944,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1004,20 +1004,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004463219394</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
+        <v>0.0003896690275</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00051162</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
+        <v>0.00044465</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>39.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1028,20 +1028,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004463219394</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
+        <v>0.0003896690275</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00051162</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
+        <v>0.00044465</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>39.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <v>3.5860242e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E6" s="2">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F6" s="2">
         <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1196,7 +1196,7 @@
         <v>106</v>
       </c>
       <c r="D12" s="4">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1210,15 +1210,15 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.84e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1">
@@ -1240,15 +1240,15 @@
         <v>108</v>
       </c>
       <c r="D14" s="5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.6888052e-05</v>
+        <v>8.623284e-05</v>
       </c>
       <c r="F14" s="2">
         <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>9.96e-05</v>
+        <v>9.84e-05</v>
       </c>
       <c r="G14" s="5">
         <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="E18" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
-        <v>0.0001566078624</v>
+        <v>0.000153115872</v>
       </c>
       <c r="F18" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
-        <v>0.00017952</v>
+        <v>0.00017472</v>
       </c>
       <c r="G18" s="5">
         <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="H18" s="5">
         <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>112</v>
@@ -1350,7 +1350,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="60" customHeight="1">
+    <row r="21" spans="1:13" ht="47" customHeight="1">
       <c r="B21">
         <v>1</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>94</v>
       </c>
       <c r="D22" s="4">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>95</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.95210008e-05</v>
+        <v>2.9655684e-05</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E24" s="2">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F24" s="2">
         <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1477,15 +1477,15 @@
         <v>104</v>
       </c>
       <c r="D27" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.308555e-05</v>
+        <v>1.29261625e-05</v>
       </c>
       <c r="F27" s="2">
         <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!D17),D27*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.5e-05</v>
+        <v>1.475e-05</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H27" s="5">
         <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1518,7 +1518,7 @@
         <v>106</v>
       </c>
       <c r="D29" s="4">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
@@ -1529,18 +1529,18 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" s="5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2">
         <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="F30" s="2">
-        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!F17),D30*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.76e-05</v>
+        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!E17),D30*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.28e-05</v>
       </c>
       <c r="G30" s="5">
         <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1548,10 +1548,10 @@
       </c>
       <c r="H30" s="5">
         <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="24" customHeight="1">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="73" customHeight="1">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -1559,29 +1559,13 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="5">
-        <v>21</v>
-      </c>
-      <c r="E31" s="2">
-        <f>IF(AND(ISNUMBER(F31),ISNUMBER('Reference data'!$B$3)),F31*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
-      </c>
-      <c r="F31" s="2">
-        <f>IF(D31=0,0,IF(ISNUMBER('Reference data'!E17),D31*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H31" s="5">
-        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="294" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="24" customHeight="1">
       <c r="A32" t="s">
         <v>119</v>
       </c>
@@ -1589,10 +1573,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1">
@@ -1603,62 +1584,62 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="24" customHeight="1">
-      <c r="A34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>105</v>
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" s="2">
+        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30)=4,SUM('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30),"Unknown")</f>
+        <v>6.30884365e-05</v>
+      </c>
+      <c r="F34" s="2">
+        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30)=4,SUM('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30),"Unknown")</f>
+        <v>7.199e-05</v>
+      </c>
+      <c r="G34" s="5">
+        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H34" s="5">
+        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="B35" s="4">
         <v>1</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30,'Turns'!E31)=5,SUM('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30,'Turns'!E31),"Unknown")</f>
-        <v>8.91911088e-05</v>
-      </c>
-      <c r="F35" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30,'Turns'!F31)=5,SUM('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30,'Turns'!F31),"Unknown")</f>
-        <v>0.00010224</v>
-      </c>
-      <c r="G35" s="5">
-        <f>IF(ISNUMBER(E35),ROUND(E35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H35" s="5">
-        <f>IF(ISNUMBER(F35),ROUND(F35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>123</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B36" s="4">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M36" s="4" t="s">
+      <c r="M35" s="4" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>115</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
@@ -1666,41 +1647,60 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="24" customHeight="1">
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A39" s="4" t="s">
+    <row r="38" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="4">
-        <v>1816</v>
-      </c>
-      <c r="J39" s="4" t="s">
+      <c r="D38" s="4">
+        <v>1790</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M39" s="4" t="s">
+      <c r="M38" s="4" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1">
+      <c r="A39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="5">
+        <v>1751</v>
+      </c>
+      <c r="E39" s="2">
+        <f>IF(AND(ISNUMBER(F39),ISNUMBER('Reference data'!$B$3)),F39*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.0689777e-05</v>
+      </c>
+      <c r="F39" s="2">
+        <f>IF(D39=0,0,IF(ISNUMBER('Reference data'!C17),D39*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>3.502e-05</v>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H39" s="5">
+        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
@@ -1711,26 +1711,26 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D40" s="5">
-        <v>1752</v>
+        <v>3</v>
       </c>
       <c r="E40" s="2">
         <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.05678448e-05</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F40" s="2">
-        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!C17),D40*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.504e-05</v>
+        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!B17),D40*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G40" s="5">
         <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" s="5">
         <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="24" customHeight="1">
@@ -1741,26 +1741,10 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="5">
-        <v>3</v>
-      </c>
-      <c r="E41" s="2">
-        <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F41" s="2">
-        <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!B17),D41*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G41" s="5">
-        <f>IF(ISNUMBER(E41),ROUND(E41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H41" s="5">
-        <f>IF(ISNUMBER(F41),ROUND(F41*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>129</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
@@ -1771,10 +1755,26 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>126</v>
+        <v>104</v>
+      </c>
+      <c r="D42" s="5">
+        <v>36</v>
+      </c>
+      <c r="E42" s="2">
+        <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.88715e-06</v>
+      </c>
+      <c r="F42" s="2">
+        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!D17),D42*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>9e-06</v>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="24" customHeight="1">
@@ -1785,54 +1785,54 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="5">
-        <v>61</v>
-      </c>
-      <c r="E43" s="2">
-        <f>IF(AND(ISNUMBER(F43),ISNUMBER('Reference data'!$B$3)),F43*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.33036425e-05</v>
-      </c>
-      <c r="F43" s="2">
-        <f>IF(D43=0,0,IF(ISNUMBER('Reference data'!D17),D43*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.525e-05</v>
-      </c>
-      <c r="G43" s="5">
-        <f>IF(ISNUMBER(E43),ROUND(E43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-      <c r="H43" s="5">
-        <f>IF(ISNUMBER(F43),ROUND(F43*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="24" customHeight="1">
-      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A45" s="4" t="s">
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="24" customHeight="1">
+      <c r="A45" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="4">
-        <v>1</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="24" customHeight="1">
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" s="5">
+        <v>24</v>
+      </c>
+      <c r="E45" s="2">
+        <f>IF(AND(ISNUMBER(F45),ISNUMBER('Reference data'!$B$3)),F45*'Reference data'!$B$3,"Unknown")</f>
+        <v>2.523888e-05</v>
+      </c>
+      <c r="F45" s="2">
+        <f>IF(D45=0,0,IF(ISNUMBER('Reference data'!E17),D45*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>2.88e-05</v>
+      </c>
+      <c r="G45" s="5">
+        <f>IF(ISNUMBER(E45),ROUND(E45*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H45" s="5">
+        <f>IF(ISNUMBER(F45),ROUND(F45*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="47" customHeight="1">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -1840,29 +1840,13 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="5">
-        <v>40</v>
-      </c>
-      <c r="E46" s="2">
-        <f>IF(AND(ISNUMBER(F46),ISNUMBER('Reference data'!$B$3)),F46*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.187376e-05</v>
-      </c>
-      <c r="F46" s="2">
-        <f>IF(D46=0,0,IF(ISNUMBER('Reference data'!E17),D46*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.8e-05</v>
-      </c>
-      <c r="G46" s="5">
-        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H46" s="5">
-        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="60" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24" customHeight="1">
       <c r="A47" t="s">
         <v>127</v>
       </c>
@@ -1870,10 +1854,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
@@ -1884,68 +1865,87 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="24" customHeight="1">
-      <c r="A49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A49" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>105</v>
+      <c r="B49" s="4">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="2">
+        <f>IF(COUNT('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45)=4,SUM('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45),"Unknown")</f>
+        <v>6.4341617e-05</v>
+      </c>
+      <c r="F49" s="2">
+        <f>IF(COUNT('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45)=4,SUM('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45),"Unknown")</f>
+        <v>7.342e-05</v>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B50" s="4">
         <v>1</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(COUNT('Turns'!E40,'Turns'!E41,'Turns'!E43,'Turns'!E46)=4,SUM('Turns'!E40,'Turns'!E41,'Turns'!E43,'Turns'!E46),"Unknown")</f>
-        <v>8.62686693e-05</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(COUNT('Turns'!F40,'Turns'!F41,'Turns'!F43,'Turns'!F46)=4,SUM('Turns'!F40,'Turns'!F41,'Turns'!F43,'Turns'!F46),"Unknown")</f>
-        <v>9.889e-05</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="4">
+        <v>2189</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="24" customHeight="1">
+      <c r="A51" t="s">
         <v>131</v>
       </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" s="4">
-        <v>2210</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>132</v>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="5">
+        <v>2046</v>
+      </c>
+      <c r="E51" s="2">
+        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.5860242e-05</v>
+      </c>
+      <c r="F51" s="2">
+        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.092e-05</v>
+      </c>
+      <c r="G51" s="5">
+        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H51" s="5">
+        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="24" customHeight="1">
@@ -1956,26 +1956,26 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D52" s="5">
-        <v>2046</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2">
         <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!C17),D52*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.092e-05</v>
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="24" customHeight="1">
@@ -1986,29 +1986,13 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3</v>
-      </c>
-      <c r="E53" s="2">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
-      </c>
-      <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!B17),D53*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G53" s="5">
-        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H53" s="5">
-        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="34" customHeight="1">
+        <v>129</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="24" customHeight="1">
       <c r="A54" t="s">
         <v>131</v>
       </c>
@@ -2016,10 +2000,26 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>133</v>
+        <v>104</v>
+      </c>
+      <c r="D54" s="5">
+        <v>140</v>
+      </c>
+      <c r="E54" s="2">
+        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.067225e-05</v>
+      </c>
+      <c r="F54" s="2">
+        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>3.5e-05</v>
+      </c>
+      <c r="G54" s="5">
+        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="24" customHeight="1">
@@ -2030,54 +2030,54 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="5">
-        <v>161</v>
-      </c>
-      <c r="E55" s="2">
-        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.51128925e-05</v>
-      </c>
-      <c r="F55" s="2">
-        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!D17),D55*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>4.025e-05</v>
-      </c>
-      <c r="G55" s="5">
-        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="4">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="24" customHeight="1">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="5">
+        <v>40</v>
+      </c>
+      <c r="E57" s="2">
+        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.20648e-05</v>
+      </c>
+      <c r="F57" s="2">
+        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.8e-05</v>
+      </c>
+      <c r="G57" s="5">
+        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
         <v>4.0</v>
       </c>
-      <c r="H55" s="5">
-        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
-      <c r="A56" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="4">
-        <v>1</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" s="4">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
+      <c r="H57" s="5">
+        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="60" customHeight="1">
       <c r="A58" t="s">
         <v>131</v>
       </c>
@@ -2085,29 +2085,13 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="5">
-        <v>41</v>
-      </c>
-      <c r="E58" s="2">
-        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.2920604e-05</v>
-      </c>
-      <c r="F58" s="2">
-        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.92e-05</v>
-      </c>
-      <c r="G58" s="5">
-        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H58" s="5">
-        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="60" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="24" customHeight="1">
       <c r="A59" t="s">
         <v>131</v>
       </c>
@@ -2115,10 +2099,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
@@ -2129,52 +2110,41 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="24" customHeight="1">
-      <c r="A61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A61" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A62" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="s">
+      <c r="B61" s="4">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E62" s="2">
-        <f>IF(COUNT('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58)=4,SUM('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58),"Unknown")</f>
-        <v>0.0001142542989</v>
-      </c>
-      <c r="F62" s="2">
-        <f>IF(COUNT('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58)=4,SUM('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58),"Unknown")</f>
-        <v>0.00013097</v>
-      </c>
-      <c r="G62" s="5">
-        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E61" s="2">
+        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57)=4,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57),"Unknown")</f>
+        <v>0.000109123102</v>
+      </c>
+      <c r="F61" s="2">
+        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57)=4,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57),"Unknown")</f>
+        <v>0.00012452</v>
+      </c>
+      <c r="G61" s="5">
+        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
         <v>11.0</v>
       </c>
-      <c r="H62" s="5">
-        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
-      </c>
-      <c r="K62" s="4" t="s">
+      <c r="H61" s="5">
+        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>12.0</v>
+      </c>
+      <c r="K61" s="4" t="s">
         <v>112</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE62">
+  <conditionalFormatting sqref="A2:AE61">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2316,83 +2286,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D41,'Turns'!D53)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D41,'Turns'!D53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D52)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D52),"Unknown")</f>
         <v>12.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E41,'Turns'!E53)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E41,'Turns'!E53),"Unknown")</f>
-        <v>2.093688e-06</v>
+        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E52)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E52),"Unknown")</f>
+        <v>2.10324e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F41,'Turns'!F53)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F41,'Turns'!F53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F52)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F52),"Unknown")</f>
         <v>2.4e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D40,'Turns'!D52)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D40,'Turns'!D52),"Unknown")</f>
-        <v>7536.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D51)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D51),"Unknown")</f>
+        <v>7535.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E40,'Turns'!E52)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E40,'Turns'!E52),"Unknown")</f>
-        <v>0.0001314836064</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E51)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E51),"Unknown")</f>
+        <v>0.000132065945</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F40,'Turns'!F52)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F40,'Turns'!F52),"Unknown")</f>
-        <v>0.00015072</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F51)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F51),"Unknown")</f>
+        <v>0.0001507</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D43,'Turns'!D55)=3,SUM('Turns'!D27,'Turns'!D43,'Turns'!D55),"Unknown")</f>
-        <v>282.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42,'Turns'!D54)=3,SUM('Turns'!D27,'Turns'!D42,'Turns'!D54),"Unknown")</f>
+        <v>235.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E43,'Turns'!E55)=3,SUM('Turns'!E27,'Turns'!E43,'Turns'!E55),"Unknown")</f>
-        <v>6.1502085e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42,'Turns'!E54)=3,SUM('Turns'!E27,'Turns'!E42,'Turns'!E54),"Unknown")</f>
+        <v>5.14855625e-05</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F43,'Turns'!F55)=3,SUM('Turns'!F27,'Turns'!F43,'Turns'!F55),"Unknown")</f>
-        <v>7.05e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42,'Turns'!F54)=3,SUM('Turns'!F27,'Turns'!F42,'Turns'!F54),"Unknown")</f>
+        <v>5.875e-05</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D14,'Turns'!D31,'Turns'!D46,'Turns'!D58)=4,SUM('Turns'!D14,'Turns'!D31,'Turns'!D46,'Turns'!D58),"Unknown")</f>
-        <v>185.0</v>
+        <f>IF(COUNT('Turns'!D14,'Turns'!D30,'Turns'!D45,'Turns'!D57)=4,SUM('Turns'!D14,'Turns'!D30,'Turns'!D45,'Turns'!D57),"Unknown")</f>
+        <v>165.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E14,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E14,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
-        <v>0.00019366614</v>
+        <f>IF(COUNT('Turns'!E14,'Turns'!E30,'Turns'!E45,'Turns'!E57)=4,SUM('Turns'!E14,'Turns'!E30,'Turns'!E45,'Turns'!E57),"Unknown")</f>
+        <v>0.0001735173</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F14,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F14,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
-        <v>0.000222</v>
+        <f>IF(COUNT('Turns'!F14,'Turns'!F30,'Turns'!F45,'Turns'!F57)=4,SUM('Turns'!F14,'Turns'!F30,'Turns'!F45,'Turns'!F57),"Unknown")</f>
+        <v>0.000198</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D30)=2,SUM('Turns'!D13,'Turns'!D30),"Unknown")</f>
-        <v>55.0</v>
+        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
+        <v>29.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E30)=2,SUM('Turns'!E13,'Turns'!E30),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
+        <v>3.049698e-05</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F30)=2,SUM('Turns'!F13,'Turns'!F30),"Unknown")</f>
-        <v>6.6e-05</v>
+        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
+        <v>3.48e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E35,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004463219394</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
+        <v>0.0003896690275</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F35,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00051162</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
+        <v>0.00044465</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>45.0</v>
+        <v>39.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>51.0</v>
+        <v>44.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>7492.497</v>
+        <v>5359.855</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>138</v>
@@ -2424,7 +2394,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.422</v>
+        <v>0.343</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>142</v>
@@ -2461,7 +2431,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -2473,7 +2443,7 @@
       </c>
       <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <v>3.5860242e-05</v>
       </c>
       <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2490,46 +2460,46 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>8.6888052e-05</v>
+        <v>8.623284e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>9.96e-05</v>
+        <v>9.84e-05</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.84e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.0001566078624</v>
+        <v>0.000153115872</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017952</v>
+        <v>0.00017472</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>3419.856</v>
+        <v>2053.755</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>138</v>
@@ -2569,7 +2539,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -2581,7 +2551,7 @@
       </c>
       <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <v>3.5860242e-05</v>
       </c>
       <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2598,49 +2568,49 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>8.6888052e-05</v>
+        <v>8.623284e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>9.96e-05</v>
+        <v>9.84e-05</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>32.0</v>
+        <v>29.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.84e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.0001566078624</v>
+        <v>0.000153115872</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017952</v>
+        <v>0.00017472</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>3413.269</v>
+        <v>2046.721</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>149</v>
@@ -2672,83 +2642,80 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
+        <v>1.05162e-06</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
-        <v>3444.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
+        <v>3443.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
-        <v>6.00888456e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
+        <v>6.0345461e-05</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
-        <v>6.888e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
+        <v>6.886e-05</v>
       </c>
       <c r="P6" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
-        <v>121.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>95.0</v>
       </c>
       <c r="Q6" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
-        <v>2.63891925e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>2.08133125e-05</v>
       </c>
       <c r="R6" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
-        <v>3.025e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>2.375e-05</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
-        <v>61.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
+        <v>43.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
-        <v>6.3857484e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
+        <v>4.521966e-05</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
-        <v>7.32e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
+        <v>5.16e-05</v>
       </c>
       <c r="V6" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W6" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>0</v>
       </c>
       <c r="X6" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
-        <v>0.0001754597781</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>0.0001274300535</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
-        <v>0.00020113</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>0.00014541</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>2781.037</v>
+        <v>2276.116</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>138</v>
@@ -2780,83 +2747,80 @@
         <v>152</v>
       </c>
       <c r="J7" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K7" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
+        <v>1.05162e-06</v>
       </c>
       <c r="L7" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M7" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
-        <v>3444.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
+        <v>3443.0</v>
       </c>
       <c r="N7" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
-        <v>6.00888456e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
+        <v>6.0345461e-05</v>
       </c>
       <c r="O7" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
-        <v>6.888e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
+        <v>6.886e-05</v>
       </c>
       <c r="P7" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
-        <v>121.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>95.0</v>
       </c>
       <c r="Q7" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
-        <v>2.63891925e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>2.08133125e-05</v>
       </c>
       <c r="R7" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
-        <v>3.025e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>2.375e-05</v>
       </c>
       <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
-        <v>61.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
+        <v>43.0</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
-        <v>6.3857484e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
+        <v>4.521966e-05</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
-        <v>7.32e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
+        <v>5.16e-05</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W7" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>0</v>
       </c>
       <c r="X7" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
-        <v>0.0001754597781</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>0.0001274300535</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
-        <v>0.00020113</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>0.00014541</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>2778.92</v>
+        <v>2273.475</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>138</v>
@@ -2888,83 +2852,80 @@
         <v>114</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D41)=2,SUM('Turns'!D24,'Turns'!D41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
         <v>6.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E41)=2,SUM('Turns'!E24,'Turns'!E41),"Unknown")</f>
-        <v>1.046844e-06</v>
+        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
+        <v>1.05162e-06</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F41)=2,SUM('Turns'!F24,'Turns'!F41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
         <v>1.2e-06</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D40)=2,SUM('Turns'!D23,'Turns'!D40),"Unknown")</f>
-        <v>3444.0</v>
+        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
+        <v>3443.0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E40)=2,SUM('Turns'!E23,'Turns'!E40),"Unknown")</f>
-        <v>6.00888456e-05</v>
+        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
+        <v>6.0345461e-05</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F40)=2,SUM('Turns'!F23,'Turns'!F40),"Unknown")</f>
-        <v>6.888e-05</v>
+        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
+        <v>6.886e-05</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D43)=2,SUM('Turns'!D27,'Turns'!D43),"Unknown")</f>
-        <v>121.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>95.0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E43)=2,SUM('Turns'!E27,'Turns'!E43),"Unknown")</f>
-        <v>2.63891925e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>2.08133125e-05</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F43)=2,SUM('Turns'!F27,'Turns'!F43),"Unknown")</f>
-        <v>3.025e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>2.375e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D31,'Turns'!D46)=2,SUM('Turns'!D31,'Turns'!D46),"Unknown")</f>
-        <v>61.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
+        <v>43.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
-        <v>6.3857484e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
+        <v>4.521966e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
-        <v>7.32e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
+        <v>5.16e-05</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W8" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>0</v>
       </c>
       <c r="X8" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E35,'Turns'!E50)=2,SUM('Turns'!E35,'Turns'!E50),"Unknown")</f>
-        <v>0.0001754597781</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
+        <v>0.0001274300535</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F35,'Turns'!F50)=2,SUM('Turns'!F35,'Turns'!F50),"Unknown")</f>
-        <v>0.00020113</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
+        <v>0.00014541</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>2777.493</v>
+        <v>2271.449</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>138</v>
@@ -2996,7 +2957,7 @@
         <v>158</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.968</v>
+        <v>1.322</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>142</v>
@@ -3033,7 +2994,7 @@
       </c>
       <c r="K10" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L10" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
@@ -3045,7 +3006,7 @@
       </c>
       <c r="N10" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.95210008e-05</v>
+        <v>2.9655684e-05</v>
       </c>
       <c r="O10" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -3053,58 +3014,55 @@
       </c>
       <c r="P10" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="Q10" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.308555e-05</v>
+        <v>1.29261625e-05</v>
       </c>
       <c r="R10" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.5e-05</v>
+        <v>1.475e-05</v>
       </c>
       <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>1.998078e-05</v>
       </c>
       <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V10" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W10" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>0</v>
       </c>
       <c r="X10" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>8.91911088e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>6.30884365e-05</v>
       </c>
       <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>0.00010224</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>7.199e-05</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>1288.434</v>
+        <v>1236.572</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>138</v>
@@ -3127,7 +3085,7 @@
         <v>112</v>
       </c>
       <c r="F11" s="1">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>148</v>
@@ -3144,7 +3102,7 @@
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
@@ -3156,7 +3114,7 @@
       </c>
       <c r="N11" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.95210008e-05</v>
+        <v>2.9655684e-05</v>
       </c>
       <c r="O11" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -3164,61 +3122,58 @@
       </c>
       <c r="P11" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
       <c r="Q11" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.308555e-05</v>
+        <v>1.29261625e-05</v>
       </c>
       <c r="R11" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.5e-05</v>
+        <v>1.475e-05</v>
       </c>
       <c r="S11" s="2">
-        <f>IF(COUNT('Turns'!D31)=1,SUM('Turns'!D31),"Unknown")</f>
-        <v>21.0</v>
+        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
+        <v>19.0</v>
       </c>
       <c r="T11" s="2">
-        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
+        <v>1.998078e-05</v>
       </c>
       <c r="U11" s="2">
-        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
-        <v>2.52e-05</v>
+        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
+        <v>2.28e-05</v>
       </c>
       <c r="V11" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W11" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.4077412e-05</v>
+        <v>0</v>
       </c>
       <c r="X11" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="2">
-        <f>IF(COUNT('Turns'!E35)=1,SUM('Turns'!E35),"Unknown")</f>
-        <v>8.91911088e-05</v>
+        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
+        <v>6.30884365e-05</v>
       </c>
       <c r="Z11" s="2">
-        <f>IF(COUNT('Turns'!F35)=1,SUM('Turns'!F35),"Unknown")</f>
-        <v>0.00010224</v>
+        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
+        <v>7.199e-05</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC11" s="1" t="s">
         <v>119</v>
       </c>
       <c r="AD11" s="1">
-        <v>1279.812</v>
+        <v>1228.523</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>149</v>
@@ -3250,7 +3205,7 @@
         <v>158</v>
       </c>
       <c r="AD12" s="1">
-        <v>2.96</v>
+        <v>4.112</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>142</v>
@@ -3282,7 +3237,7 @@
         <v>165</v>
       </c>
       <c r="AD13" s="1">
-        <v>0.723</v>
+        <v>1.036</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>142</v>
@@ -3314,52 +3269,52 @@
         <v>158</v>
       </c>
       <c r="J14" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K14" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L14" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M14" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>1752.0</v>
+        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
+        <v>1751.0</v>
       </c>
       <c r="N14" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>3.05678448e-05</v>
+        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <v>3.0689777e-05</v>
       </c>
       <c r="O14" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>3.504e-05</v>
+        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <v>3.502e-05</v>
       </c>
       <c r="P14" s="2">
-        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>61.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q14" s="2">
-        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>1.33036425e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>7.88715e-06</v>
       </c>
       <c r="R14" s="2">
-        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>1.525e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S14" s="2">
-        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
+        <v>24.0</v>
       </c>
       <c r="T14" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>4.187376e-05</v>
+        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
+        <v>2.523888e-05</v>
       </c>
       <c r="U14" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
+        <v>2.88e-05</v>
       </c>
       <c r="V14" s="2">
         <v>0</v>
@@ -3371,23 +3326,23 @@
         <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>8.62686693e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.4341617e-05</v>
       </c>
       <c r="Z14" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>9.889e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.342e-05</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1478.562</v>
+        <v>1023.072</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>138</v>
@@ -3410,7 +3365,7 @@
         <v>112</v>
       </c>
       <c r="F15" s="1">
-        <v>1816</v>
+        <v>1790</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>148</v>
@@ -3422,52 +3377,52 @@
         <v>168</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D41)=1,SUM('Turns'!D41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>1752.0</v>
+        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
+        <v>1751.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>3.05678448e-05</v>
+        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
+        <v>3.0689777e-05</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>3.504e-05</v>
+        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
+        <v>3.502e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D43)=1,SUM('Turns'!D43),"Unknown")</f>
-        <v>61.0</v>
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>36.0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E43)=1,SUM('Turns'!E43),"Unknown")</f>
-        <v>1.33036425e-05</v>
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>7.88715e-06</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F43)=1,SUM('Turns'!F43),"Unknown")</f>
-        <v>1.525e-05</v>
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>9e-06</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
+        <v>24.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>4.187376e-05</v>
+        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
+        <v>2.523888e-05</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
+        <v>2.88e-05</v>
       </c>
       <c r="V15" s="2">
         <v>0</v>
@@ -3479,26 +3434,26 @@
         <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>8.62686693e-05</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>6.4341617e-05</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>9.889e-05</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>7.342e-05</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="AC15" s="1" t="s">
         <v>127</v>
       </c>
       <c r="AD15" s="1">
-        <v>1474.575</v>
+        <v>1015.023</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>149</v>
@@ -3530,52 +3485,52 @@
         <v>49</v>
       </c>
       <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>2046.0</v>
       </c>
       <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>3.5860242e-05</v>
       </c>
       <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>161.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>140.0</v>
       </c>
       <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>3.51128925e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>3.067225e-05</v>
       </c>
       <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>4.025e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>3.5e-05</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>41.0</v>
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>4.2920604e-05</v>
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>4.20648e-05</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>4.92e-05</v>
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
@@ -3587,12 +3542,12 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.0001142542989</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>0.000109123102</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00013097</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>0.00012452</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3600,10 +3555,10 @@
       </c>
       <c r="AB16" s="5">
         <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>1285.334</v>
+        <v>1023.474</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>138</v>
@@ -3626,7 +3581,7 @@
         <v>112</v>
       </c>
       <c r="F17" s="1">
-        <v>2210</v>
+        <v>2189</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>148</v>
@@ -3638,52 +3593,52 @@
         <v>169</v>
       </c>
       <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
         <v>3.0</v>
       </c>
       <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
+        <v>5.2581e-07</v>
       </c>
       <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
         <v>6e-07</v>
       </c>
       <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
         <v>2046.0</v>
       </c>
       <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>3.56973804e-05</v>
+        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
+        <v>3.5860242e-05</v>
       </c>
       <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>161.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>140.0</v>
       </c>
       <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>3.51128925e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>3.067225e-05</v>
       </c>
       <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>4.025e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>3.5e-05</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>41.0</v>
+        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
+        <v>40.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>4.2920604e-05</v>
+        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
+        <v>4.20648e-05</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>4.92e-05</v>
+        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
+        <v>4.8e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -3695,12 +3650,12 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.0001142542989</v>
+        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
+        <v>0.000109123102</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00013097</v>
+        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
+        <v>0.00012452</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3708,13 +3663,13 @@
       </c>
       <c r="AB17" s="5">
         <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="AC17" s="1" t="s">
         <v>131</v>
       </c>
       <c r="AD17" s="1">
-        <v>1280.525</v>
+        <v>1016.334</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>149</v>
@@ -3772,7 +3727,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/subagent_chat/report.xlsx
+++ b/reports/subagent_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="170">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d142-b71b-72b0-beb4-02a590022f96</t>
+    <t>01a0d587-81ab-7592-8676-94fee801eb4b</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d142-b724-75f2-acca-1970e25f6cbe</t>
+    <t>01a0d587-81b4-78a1-9a6c-fac8360c169a</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -348,8 +348,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0f4e337a0b72c1006ab48bf66d3087d2a421e4e726bcd8a1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIv25sVZByrJ-Z1P3JBd7ZG5d1EHcxU3cLqgJw2OVwVz_sUvMzXuQ54Dlf-Nc-CybCYivsJQqwSSYNWu3ZtF44YybnYXCP1yhXm-svXO7QBMsCEEr3biaYnqFPKgUs0INILl4s0GnN2lJUPcbAuJs8UTsk11mOFO3pDQZomzHkSCS4QA_JHH0pVVo291NidvDtwlGFO-lzVVRuhKWx1coEbG40eXiEYDmwO2sfDFuLloTLp_22eRk_YoWfPXc2Rq9GqREs79lLzUTpD3W2sWFTIP4HESBXY9BXj3q1b1RrXibmWe4VeuIGpfKKPcsL4vG2TsMUpUiTbi8o_K8t6kvvj2F8fDlUb63hg65NrNOuD7UTw7JIIKbzCM7uUS5e5Mv18ggZr7dgsvJZEtyyHjzohecCOdxOdUVECQKAnXIh1wlkJpsEkQ5XIm1xRKA_vY40U5NKSD2TCJx2RgS18-REeW35C5rsAtY4EJosEq59A0NbC8eaBZmuiJ-HSYZQWBzzBt-a7fNfOS6ZcLzfl9vY5O6qHg-knEQG1DFjfhRLfqx2s1ToNci2MeLmA-uSkcDNBrot0EYsZe_vRnGouaA63AT-3mHe8txI-mHlcfoki-hjr6O3s16BCkkNSVp7xZNhFouAUabriJS5wbhLgT-jMOU9pMYp7TbO3vTwz7KDSLjKRwU8PKFuAaDg-KFNNFAF6AS3793pV571CUG1zpV4DqWKQW7mjgENRNx08XKSqeJVCx_KYvvSSbw_Y6Bu89PLOdCLzLbCFSwQy14OfYmO9jtHwVjgU1GPAsVIUf24VtfCylS4TsX4ek7_bXyUAyLrFuqdwQD16o2QPBj5fJnMXv1ia47V2UqxPyV_LC_d5yjub2-n4NWTTlZ5zc5n9nD1fphDLDax3-PL_culI0z-8J90sCiccxK2N-PHlldf_c3YB3dkD-K-3DWrpmigW_jPxGxvLDn-CcAaJsshixbyYyB3FuTm8Avq_mG4qQFbkc9gy8RehGlVR5RiaWwCqESQZNoS51gBnpxL2ku194_eRtngi2v2ACyD3vs8F5SLyAgPIbKbcWTXoc90MnZ2j2Wt7YchL3yPbvtGMWyjjbqnNRkcMQTf78EWmOn1L2BHWUA7Td1b2zqHqCODJyRQORWx7M-K63sxD4rNJCUjk_lf1XvNOL11sBskrcpWsT55UijHjuwsXhPzjESsLLPYPEogMjKBBb_tHGGW885kJ17rcp4kqfW4G31XGx6Ra2UcvU8lChMdrQbGv09XhTvmkDOkCjeFOgnEqeYwp6Ti-h2jPXnl2AbPIFd4TfiIU3uFBHHrpl6rmYRrLid_RpEG5senAewTYoahEN11gOQnfW4Q-V4Q=="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.\" ,\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_2F51dvYjDannP4m8M1mgKlqk", "id": "fc_0b0f4e337a0b72c1006ab48bf6b2c087d290baa7c279eb01e3", "index": 1}]
-{"name": "task", "args": {"description": "Use your echo tool to echo exactly the supplied text: \u201cReAct\u201d. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.", "subagent_type": "isolated-subagent"}, "id": "call_2F51dvYjDannP4m8M1mgKlqk", "type": "tool_call"}</t>
+    <t>[{"id": "rs_001a0a066573c3c3006ab5a3b78c1487d281c258c33e38a742", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaO39HK-Pu-9yad_xiB-k5wb98vVuue-6mevm2ji_VkMpy2ubvVDy48vvDcvsjC4gTcgktoEs4l4t8K0vl6Ahw58c8D48ekFfT3_z4Uc3JubJtUg8h1vSNfdM4MCDs8ApthEHOFwHDx7127vSE3DpNcb3x44i0WyETC85N8xhLdr5XBf5DqinUOxaZcO7rekKb3wqOGRcLvPvxlmED40mnZ-_MlXdoClZrbQxSnLHcU39IfPormBWfPZuCdoaMCSd4gVSe1dx5PoZ-vAyej3opfC4KWesc3U6hkYkhJiXhgJB04TItWPVIVbxoDKX9ByGsZMVHbNPQe0jrUY5xpKzUzPkcmX-XDI7COl-xMBzx3RpO9vWWNbxSkjhUv2sHnFz69pO7b1VDcIh9EsLoa08A5SSOgQOU_D4FurQv7Cu0ZI4o9N2jnBQdhqCCYGsFqJBNIgGddpO8bFrjXLHf8PzC6TSBFLgbK8qC0M2pTPgjlnGS4GWwjdQemU3Le9uu6SE9NBZUZJxtP5quYACAJ6oCThwEB_be9ajhT8V5Uy5kzrM_e0pdQBlJSWiQrlQagGvcqt5JqXxfGewZiuybjiipZY1voPxa2pV2CP2trvDnhf9DR55XpZbN93uBrFf-0W-jVfyfRdRDrsNHwDmZ8VjQnaOlW4s46fEfKB_J5itkK0YZwlpeBkC-4r_HHW3aXTtlPEGHDsgJyr-Te2y4J0LoFnWdQUOFKCsQeSBDw9tmJrcOcRna_9cxqUe6lJ7Se5hI9u2mKO5xeAF2TtS69yQSPC7j7gIFTqrvi-OEGh5SshPH_kgiXdPPH_RBiBN7lQTaPzK9VHjaHf5pg6tFRnp8HC3T3w7Z_eTAtVaXQ50v8nq82-0EW4_rUamC2mrusssLYZgWLD4Mqw9yI7Z0ATHMmVd9pvavHVhMElXg9RQTTcQMmR6I3R5zfav7hNGKFguXpZP0Q_nb6FJ-TOfiZUC6VmCgEdJgyhpppAgzv0JMWl-nTzdXvDcuVqzxb6pXvOVjQs6iyEDX01_rzddBF7EqJ7V0O4LdSNVHClDzRzuUv7j7lPZz4xgci7wQsSmsY33nLgK66kA0IvyIZxf3ykc9SSrITqTVfnZGI5V5GPXZyAVt7vmXfh4rBh8YnuG9Lt--lRq33Rj-icUGCj27pMcvC65rV9-Wn12g1RNoHqgrXdmCiygkQr_l42O0Nz1Iw-oWKACw_Xvb1we5ulzrOO2vxYVqk93YGhj3AOjn7yN3dXXhGLqabelT3hzcAY7frdmuYANR27HhrIZS-O5yB-gbCxeFoENfoOMKEVYKRylK63DgU="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Use your echo tool to echo exactly the text: \\\"ReAct\\\". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.\" ,\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_9WpjMeoociWZb1WXPQZHvDLd", "id": "fc_001a0a066573c3c3006ab5a3b7cfd087d2bff4768967db8122", "index": 1}]
+{"name": "task", "args": {"description": "Use your echo tool to echo exactly the text: \"ReAct\". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.", "subagent_type": "isolated-subagent"}, "id": "call_9WpjMeoociWZb1WXPQZHvDLd", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -361,38 +361,38 @@
     <t>Tool · task</t>
   </si>
   <si>
-    <t>01a0d142-bf27-7823-ad57-670a30c3a8f1</t>
+    <t>01a0d587-8a21-73a1-bfef-b804d74a9901</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'description': 'Use your echo tool to echo exactly the supplied text: “ReAct”. Then report back that the echoed result is returned to the parent agent as your task result/summary, where the parent can use it in its response. Do not add factual claims beyond this process description.', 'subagent_type': 'isolated-subagent'}</t>
+    <t>{'description': 'Use your echo tool to echo exactly the text: "ReAct". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.', 'subagent_type': 'isolated-subagent'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='The echoed result is returned to the parent agent as the task result/summary: “ReAct”.', tool_call_id='call_2F51dvYjDannP4m8M1mgKlqk')]})</t>
+    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='ReAct\n\nThe tool result is returned to the parent agent as the tool’s response, containing the echoed input.', tool_call_id='call_9WpjMeoociWZb1WXPQZHvDLd')]})</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d142-bf30-7c72-93e6-527e44423b76</t>
+    <t>01a0d587-8a2a-72d3-b994-1017bc62cc76</t>
   </si>
   <si>
     <t>You are a workflow teaching specialist. Call echo_tool with the assigned text, then summarize the returned echo for the parent. The echo repeats supplied input and provides no independent factual evidence. Do not delegate further.</t>
   </si>
   <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_ZtmMfMRzgGQF48ppM5b3oeJj", "id": "fc_0c8eb20f1d11b30a006ab48bf8786087d29be9c77d997d91a8", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_ZtmMfMRzgGQF48ppM5b3oeJj", "type": "tool_call"}</t>
+    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_nEdS34lKTFNB3m1cUsUrwKyh", "id": "fc_0e7bbe1ed7254a68006ab5a3b9b6a487d2a58f8dd680c40a44", "index": 0}]
+{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_nEdS34lKTFNB3m1cUsUrwKyh", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · echo_tool</t>
   </si>
   <si>
-    <t>01a0d142-c402-7003-97f2-f06a70c12f41</t>
+    <t>01a0d587-8e6c-7191-8cd5-31fa5e45c08f</t>
   </si>
   <si>
     <t>{'text': 'ReAct'}</t>
@@ -404,25 +404,26 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0d142-c40c-7212-be6f-e0524469d562</t>
+    <t>01a0d587-8e71-7991-a0ed-07bc3b8180ad</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The echoed result is returned to the parent agent as the task result/summary: \u201cReAct\u201d.", "phase": "final_answer", "index": 0, "id": "msg_0c8eb20f1d11b30a006ab48bf98f9087d286f37b9d43a2992a"}]</t>
+    <t>[{"id": "rs_0e7bbe1ed7254a68006ab5a3bac3d087d2bf3d21de94d4f75f", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaO7l89d03i2QN1NUrR8bQHpzRAE3D3o1KWmKjI60pK5TlcJVjXGyCHmPY9Q-b2x2b_z36PfQ1hDdED64u4fl7Ll0EfeWOmnIQAbzLIILUuNygSp-SZsL5B8VY5Sxtd3utaCeEBULTScKSlse1iy6iT6fO12T78hrI8gOPZRKzWNDmigcC7sWEkAVUt4xWFsitKnWc1fCf5zkKo_YpS5wxOUdZyUktXShiqK1k-BpMP2-ekIHEdXbOIRpv1YhKMCMAOLpVyqx_2u0_XSuH-ckaxdOF2PR26RjT7whIltN61kstKt-2g0rzMHEtHYVnC6ifDqqVyk9HPq3oAVazEUI_Hx6grLhu5jLUGiC05rhaYXyfafYv75AayAJHRGpadypWW0wgYEuuFN3KdcG8iNIzqYcZ5ssny6BEmGlgQEZIE88ILdoIKfb9ocSpQGrq5Q6BKfOWeMSczgCFRAxGAwUQlK_kPlg64hAwd9h6hExBOSO4bjqUL2-KC0B7OfVD9QBSmH-5lC6t69-eNj8i29I08C0QlGHRSFsK9_XXgQGLm2U6K_dU7NamiKbTGrH1H3GTQ9FGQjJlDD8dvc_Ur6UYDpKbXaUKhQL_7wjEiHSfq78NUyaOT9KkI1MbylNWnxZWNDlhY6rjMydWqGWKckBgYuNwkS5HlzfOFDABM1IYOx9iT8fRMKvKG_MvpBHm71KyUMBS8RuXUHg_Vy0oHuWkxbp4NTOie8WwR5zsT72kpHoHuRsDH_c9rQPMkr6qNP5evItpK86tAwc0O42tycI0tu4kA09ylQc8oxKhZQFPLkhZNwa2QK4ZoVrH_3wFx5T5c6vzZkuqi71NW3TCrvMFF-Jf23dX1nfdRmvITsI5ZBUOLmfJgsJpVzpDFDsg7d2VjiVGM9bz_6uTDMJ5IooR91xKc1mm7TpAVH_CP0TGyiwZaksWcNsQ1xROwL4zUxqv3PH3NGwdb56qr9nRuwDDeSweFv7RdplJ_AD6i5nG0iNmS3iBQcJJacNYn5198i-gqI1Z1kOAwGo4Sn3i9feWXJL46ZE5lUFloNXNO9pGg42uebTb6yJigPliUO2HyZ1hWz94CQVYSVXcoKJCYd4TvsZjk6zzUt77m2FwSJI2e_E4IV2SB3pZ8-EacyZYdJvJrof-VQSYOHVftF77hqFkMDdrHEBtFhulEbVGwMGaobe_Gg0Oi-Z4FPxf4KFNOxpEoMDE9CtgX8E_K-koWkzGyXevMKb-eXcbXXQexFwdCvaMMIPqOxvcSLcMBNxvyU7IVntdRJWiAV37v_NUBeu9qFU0GIeMoJwvBtH0MeD2FQk_iwruUdYyCUT455f3uWFlLn_MwAUcAYoCcm0Z0u6ZZy52p0tZrXBrim1ZoXWMjBgOpC_5pI2tjdwVKSDN3dCMiRSDuof4rgB7kiQn4ac02VB7YjIEey6qaoluZjhTcK3b9eu__XB-UFzbu-5c75sRFchfOiPzSHlsQFT5JusC92N2iLG1jYCQCpXc7sY474DwEr8ccrZFWfbaJGHD0pvPogbrl5EyxP0n-ciuXA9vOR-2CFtBsbPzFsPun8Xs_vh5OmkoqEk9QFbObzoItYUuRnH4JCZHwIO7NQBpbkSAcfm8OqNHhDuydCztBVEEov0m3LPzz_7d9Jp8Jg8E1TMaCKmCrnbcZzBXt9aN-U78-A4g=="}, {"type": "text", "text": "ReAct\n\nThe tool result is returned to the parent agent as the tool\u2019s response, containing the echoed input.", "phase": "final_answer", "index": 1, "id": "msg_0e7bbe1ed7254a68006ab5a3bb7c4c87d2bca81bc05bd27494"}]</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0d142-c812-7833-9af0-84a4704eb738</t>
-  </si>
-  <si>
-    <t>The echoed result is returned to the parent agent as the task result/summary: “ReAct”.</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The specialist echoed: **\u201cReAct\u201d**.\n\nIts tool result is returned to the parent through the specialist\u2019s task summary, which the parent can then incorporate into its response.", "phase": "final_answer", "index": 0, "id": "msg_0b0f4e337a0b72c1006ab48bfa80d087d2b1859aa25c26069c"}]</t>
+    <t>01a0d587-9603-7490-a940-dd3ee0b70502</t>
+  </si>
+  <si>
+    <t>ReAct
+The tool result is returned to the parent agent as the tool’s response, containing the echoed input.</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "The specialist echoed **\u201cReAct.\u201d**\n\nIts tool result is returned to the parent agent as the tool response, which contains the echoed input and any accompanying summary.", "phase": "final_answer", "index": 0, "id": "msg_001a0a066573c3c3006ab5a3bc95c087d2aa32d3a860b72627"}]</t>
   </si>
   <si>
     <t>delegating_parent</t>
@@ -443,7 +444,7 @@
     <t>Check message history and repair missing tool responses before the agent starts.</t>
   </si>
   <si>
-    <t>01a0d142-b71e-7ab0-b926-2b8b25bf1742</t>
+    <t>01a0d587-81ae-7250-a987-024548c5518d</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -455,7 +456,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d142-b71f-70e2-9e32-05658451738d</t>
+    <t>01a0d587-81af-7132-a9d3-dcd784e7db1a</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -476,7 +477,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d142-bf26-7741-b420-f46b9e717e95</t>
+    <t>01a0d587-8a20-78a3-9486-aa581d19db17</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -504,19 +505,19 @@
     <t>Execute the isolated-subagent workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d142-bf28-7271-86b3-1e331d71c795</t>
+    <t>01a0d587-8a21-73a1-bfef-b811577aec87</t>
   </si>
   <si>
     <t xml:space="preserve">                PatchToolCallsMiddleware.before_agent</t>
   </si>
   <si>
-    <t>01a0d142-bf29-7461-be33-f6953eb29004</t>
+    <t>01a0d587-8a22-7b71-ba48-b65b9f5b7dff</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0d142-bf2b-7952-b975-77f2aa546f40</t>
+    <t>01a0d587-8a24-7f60-b5ab-cd48fc04e488</t>
   </si>
   <si>
     <t xml:space="preserve">                    ChatOpenAI</t>
@@ -525,7 +526,7 @@
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0d142-c401-78f3-8dda-1148024ee64f</t>
+    <t>01a0d587-8e6b-7183-9c1b-2b3dec508828</t>
   </si>
   <si>
     <t xml:space="preserve">                    echo_tool</t>
@@ -534,10 +535,10 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0d142-c406-72a1-8af6-1a63f774d36b</t>
-  </si>
-  <si>
-    <t>01a0d142-c80c-7be0-bd88-a2523a23fd5b</t>
+    <t>01a0d587-8e6e-72e1-8c9e-e86a0aa23fb6</t>
+  </si>
+  <si>
+    <t>01a0d587-95ff-7241-92d0-bdc92bff4c45</t>
   </si>
 </sst>
 </file>
@@ -944,7 +945,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1004,20 +1005,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
-        <v>0.0003896690275</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004824758082</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
-        <v>0.00044465</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00054843</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1028,20 +1029,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
-        <v>0.0003896690275</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004824758082</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
-        <v>0.00044465</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00054843</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1079,7 +1080,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5860242e-05</v>
+        <v>3.59989608e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -1109,7 +1110,7 @@
       </c>
       <c r="E6" s="2">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F6" s="2">
         <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1196,7 +1197,7 @@
         <v>106</v>
       </c>
       <c r="D12" s="4">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -1210,19 +1211,19 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.049698e-05</v>
+        <v>2.4280824e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1240,26 +1241,26 @@
         <v>108</v>
       </c>
       <c r="D14" s="5">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.623284e-05</v>
+        <v>9.7123296e-05</v>
       </c>
       <c r="F14" s="2">
         <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>9.84e-05</v>
+        <v>0.0001104</v>
       </c>
       <c r="G14" s="5">
         <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="5">
         <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="385" customHeight="1">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="398" customHeight="1">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -1307,19 +1308,19 @@
       </c>
       <c r="E18" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
-        <v>0.000153115872</v>
+        <v>0.0001579309248</v>
       </c>
       <c r="F18" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
-        <v>0.00017472</v>
+        <v>0.00017952</v>
       </c>
       <c r="G18" s="5">
         <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="H18" s="5">
         <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>112</v>
@@ -1339,7 +1340,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1">
+    <row r="20" spans="1:13" ht="73" customHeight="1">
       <c r="B20">
         <v>1</v>
       </c>
@@ -1372,7 +1373,7 @@
         <v>94</v>
       </c>
       <c r="D22" s="4">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>95</v>
@@ -1396,7 +1397,7 @@
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9655684e-05</v>
+        <v>2.97704016e-05</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="E24" s="2">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F24" s="2">
         <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1477,15 +1478,15 @@
         <v>104</v>
       </c>
       <c r="D27" s="5">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.29261625e-05</v>
+        <v>1.495558e-05</v>
       </c>
       <c r="F27" s="2">
         <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!D17),D27*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.475e-05</v>
+        <v>1.7e-05</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1493,7 +1494,7 @@
       </c>
       <c r="H27" s="5">
         <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1536,7 +1537,7 @@
       </c>
       <c r="E30" s="2">
         <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.998078e-05</v>
+        <v>2.0058072e-05</v>
       </c>
       <c r="F30" s="2">
         <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!E17),D30*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1599,15 +1600,15 @@
       </c>
       <c r="E34" s="2">
         <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30)=4,SUM('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30),"Unknown")</f>
-        <v>6.30884365e-05</v>
+        <v>6.53118976e-05</v>
       </c>
       <c r="F34" s="2">
         <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30)=4,SUM('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30),"Unknown")</f>
-        <v>7.199e-05</v>
+        <v>7.424e-05</v>
       </c>
       <c r="G34" s="5">
         <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H34" s="5">
         <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1664,7 +1665,7 @@
         <v>94</v>
       </c>
       <c r="D38" s="4">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>95</v>
@@ -1684,15 +1685,15 @@
         <v>97</v>
       </c>
       <c r="D39" s="5">
-        <v>1751</v>
+        <v>1760</v>
       </c>
       <c r="E39" s="2">
         <f>IF(AND(ISNUMBER(F39),ISNUMBER('Reference data'!$B$3)),F39*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0689777e-05</v>
+        <v>3.0966848e-05</v>
       </c>
       <c r="F39" s="2">
         <f>IF(D39=0,0,IF(ISNUMBER('Reference data'!C17),D39*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.502e-05</v>
+        <v>3.52e-05</v>
       </c>
       <c r="G39" s="5">
         <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1718,7 +1719,7 @@
       </c>
       <c r="E40" s="2">
         <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F40" s="2">
         <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!B17),D40*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1762,7 +1763,7 @@
       </c>
       <c r="E42" s="2">
         <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.88715e-06</v>
+        <v>7.91766e-06</v>
       </c>
       <c r="F42" s="2">
         <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!D17),D42*'Reference data'!D17/1000000,"Unknown"))</f>
@@ -1799,7 +1800,7 @@
         <v>106</v>
       </c>
       <c r="D44" s="4">
-        <v>24</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
@@ -1810,29 +1811,29 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D45" s="5">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2">
         <f>IF(AND(ISNUMBER(F45),ISNUMBER('Reference data'!$B$3)),F45*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.523888e-05</v>
+        <v>8.1287976e-05</v>
       </c>
       <c r="F45" s="2">
-        <f>IF(D45=0,0,IF(ISNUMBER('Reference data'!E17),D45*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.88e-05</v>
+        <f>IF(D45=0,0,IF(ISNUMBER('Reference data'!F17),D45*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>9.24e-05</v>
       </c>
       <c r="G45" s="5">
         <f>IF(ISNUMBER(E45),ROUND(E45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="H45" s="5">
         <f>IF(ISNUMBER(F45),ROUND(F45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="47" customHeight="1">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="24" customHeight="1">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -1840,13 +1841,29 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>109</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="D46" s="5">
+        <v>29</v>
+      </c>
+      <c r="E46" s="2">
+        <f>IF(AND(ISNUMBER(F46),ISNUMBER('Reference data'!$B$3)),F46*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.0614952e-05</v>
+      </c>
+      <c r="F46" s="2">
+        <f>IF(D46=0,0,IF(ISNUMBER('Reference data'!E17),D46*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>3.48e-05</v>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="320" customHeight="1">
       <c r="A47" t="s">
         <v>127</v>
       </c>
@@ -1854,7 +1871,10 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
@@ -1865,87 +1885,68 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="24" customHeight="1">
+      <c r="A49" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B49" s="4">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E49" s="2">
-        <f>IF(COUNT('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45)=4,SUM('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45),"Unknown")</f>
-        <v>6.4341617e-05</v>
-      </c>
-      <c r="F49" s="2">
-        <f>IF(COUNT('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45)=4,SUM('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45),"Unknown")</f>
-        <v>7.342e-05</v>
-      </c>
-      <c r="G49" s="5">
-        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
-      </c>
-      <c r="H49" s="5">
-        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A50" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="4">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="2">
+        <f>IF(COUNT('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45,'Turns'!E46)=5,SUM('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45,'Turns'!E46),"Unknown")</f>
+        <v>0.00015131528</v>
+      </c>
+      <c r="F50" s="2">
+        <f>IF(COUNT('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45,'Turns'!F46)=5,SUM('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45,'Turns'!F46),"Unknown")</f>
+        <v>0.000172</v>
+      </c>
+      <c r="G50" s="5">
+        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>15.0</v>
+      </c>
+      <c r="H50" s="5">
+        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>17.0</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A51" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B51" s="4">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="4">
-        <v>2189</v>
-      </c>
-      <c r="J50" s="4" t="s">
+      <c r="D51" s="4">
+        <v>2196</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="M51" s="4" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="24" customHeight="1">
-      <c r="A51" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="5">
-        <v>2046</v>
-      </c>
-      <c r="E51" s="2">
-        <f>IF(AND(ISNUMBER(F51),ISNUMBER('Reference data'!$B$3)),F51*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5860242e-05</v>
-      </c>
-      <c r="F51" s="2">
-        <f>IF(D51=0,0,IF(ISNUMBER('Reference data'!C17),D51*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.092e-05</v>
-      </c>
-      <c r="G51" s="5">
-        <f>IF(ISNUMBER(E51),ROUND(E51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H51" s="5">
-        <f>IF(ISNUMBER(F51),ROUND(F51*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="24" customHeight="1">
@@ -1956,26 +1957,26 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="5">
-        <v>3</v>
+        <v>2046</v>
       </c>
       <c r="E52" s="2">
         <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>3.59989608e-05</v>
       </c>
       <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
+        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!C17),D52*'Reference data'!C17/1000000,"Unknown"))</f>
+        <v>4.092e-05</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H52" s="5">
         <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="24" customHeight="1">
@@ -1986,13 +1987,29 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="24" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3</v>
+      </c>
+      <c r="E53" s="2">
+        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="F53" s="2">
+        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!B17),D53*'Reference data'!B17/1000000,"Unknown"))</f>
+        <v>6e-07</v>
+      </c>
+      <c r="G53" s="5">
+        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H53" s="5">
+        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="60" customHeight="1">
       <c r="A54" t="s">
         <v>131</v>
       </c>
@@ -2000,26 +2017,10 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="5">
-        <v>140</v>
-      </c>
-      <c r="E54" s="2">
-        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.067225e-05</v>
-      </c>
-      <c r="F54" s="2">
-        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!D17),D54*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.5e-05</v>
-      </c>
-      <c r="G54" s="5">
-        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H54" s="5">
-        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>129</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="24" customHeight="1">
@@ -2030,54 +2031,54 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" s="5">
+        <v>147</v>
+      </c>
+      <c r="E55" s="2">
+        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.2330445e-05</v>
+      </c>
+      <c r="F55" s="2">
+        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!D17),D55*'Reference data'!D17/1000000,"Unknown"))</f>
+        <v>3.675e-05</v>
+      </c>
+      <c r="G55" s="5">
+        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H55" s="5">
+        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="24" customHeight="1">
+      <c r="A56" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A56" s="4" t="s">
+    <row r="57" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A57" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B56" s="4">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4" t="s">
+      <c r="B57" s="4">
+        <v>1</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="24" customHeight="1">
-      <c r="A57" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" s="5">
-        <v>40</v>
-      </c>
-      <c r="E57" s="2">
-        <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.20648e-05</v>
-      </c>
-      <c r="F57" s="2">
-        <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.8e-05</v>
-      </c>
-      <c r="G57" s="5">
-        <f>IF(ISNUMBER(E57),ROUND(E57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H57" s="5">
-        <f>IF(ISNUMBER(F57),ROUND(F57*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="60" customHeight="1">
+      <c r="D57" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="24" customHeight="1">
       <c r="A58" t="s">
         <v>131</v>
       </c>
@@ -2085,13 +2086,29 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="24" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="D58" s="5">
+        <v>37</v>
+      </c>
+      <c r="E58" s="2">
+        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.9060456e-05</v>
+      </c>
+      <c r="F58" s="2">
+        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>4.44e-05</v>
+      </c>
+      <c r="G58" s="5">
+        <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+      <c r="H58" s="5">
+        <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="60" customHeight="1">
       <c r="A59" t="s">
         <v>131</v>
       </c>
@@ -2099,7 +2116,10 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="24" customHeight="1">
@@ -2110,41 +2130,52 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="24" customHeight="1">
+      <c r="A61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A61" s="4" t="s">
+    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A62" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B61" s="4">
-        <v>1</v>
-      </c>
-      <c r="C61" s="4" t="s">
+      <c r="B62" s="4">
+        <v>1</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E61" s="2">
-        <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57)=4,SUM('Turns'!E51,'Turns'!E52,'Turns'!E54,'Turns'!E57),"Unknown")</f>
-        <v>0.000109123102</v>
-      </c>
-      <c r="F61" s="2">
-        <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57)=4,SUM('Turns'!F51,'Turns'!F52,'Turns'!F54,'Turns'!F57),"Unknown")</f>
-        <v>0.00012452</v>
-      </c>
-      <c r="G61" s="5">
-        <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="E62" s="2">
+        <f>IF(COUNT('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58)=4,SUM('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58),"Unknown")</f>
+        <v>0.0001079177058</v>
+      </c>
+      <c r="F62" s="2">
+        <f>IF(COUNT('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58)=4,SUM('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58),"Unknown")</f>
+        <v>0.00012267</v>
+      </c>
+      <c r="G62" s="5">
+        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
         <v>11.0</v>
       </c>
-      <c r="H61" s="5">
-        <f>IF(ISNUMBER(F61),ROUND(F61*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H62" s="5">
+        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
         <v>12.0</v>
       </c>
-      <c r="K61" s="4" t="s">
+      <c r="K62" s="4" t="s">
         <v>112</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE61">
+  <conditionalFormatting sqref="A2:AE62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2286,83 +2317,83 @@
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D52)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D53)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D53),"Unknown")</f>
         <v>12.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E52)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E52),"Unknown")</f>
-        <v>2.10324e-06</v>
+        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E53)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E53),"Unknown")</f>
+        <v>2.111376e-06</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F52)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F52),"Unknown")</f>
+        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F53)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F53),"Unknown")</f>
         <v>2.4e-06</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D51)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D51),"Unknown")</f>
-        <v>7535.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D52)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D52),"Unknown")</f>
+        <v>7544.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E51)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E51),"Unknown")</f>
-        <v>0.000132065945</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E52)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E52),"Unknown")</f>
+        <v>0.0001327351712</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F51)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F51),"Unknown")</f>
-        <v>0.0001507</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F52)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F52),"Unknown")</f>
+        <v>0.00015088</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D42,'Turns'!D54)=3,SUM('Turns'!D27,'Turns'!D42,'Turns'!D54),"Unknown")</f>
-        <v>235.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42,'Turns'!D55)=3,SUM('Turns'!D27,'Turns'!D42,'Turns'!D55),"Unknown")</f>
+        <v>251.0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E42,'Turns'!E54)=3,SUM('Turns'!E27,'Turns'!E42,'Turns'!E54),"Unknown")</f>
-        <v>5.14855625e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42,'Turns'!E55)=3,SUM('Turns'!E27,'Turns'!E42,'Turns'!E55),"Unknown")</f>
+        <v>5.5203685e-05</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F42,'Turns'!F54)=3,SUM('Turns'!F27,'Turns'!F42,'Turns'!F54),"Unknown")</f>
-        <v>5.875e-05</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42,'Turns'!F55)=3,SUM('Turns'!F27,'Turns'!F42,'Turns'!F55),"Unknown")</f>
+        <v>6.275e-05</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D14,'Turns'!D30,'Turns'!D45,'Turns'!D57)=4,SUM('Turns'!D14,'Turns'!D30,'Turns'!D45,'Turns'!D57),"Unknown")</f>
-        <v>165.0</v>
+        <f>IF(COUNT('Turns'!D14,'Turns'!D30,'Turns'!D46,'Turns'!D58)=4,SUM('Turns'!D14,'Turns'!D30,'Turns'!D46,'Turns'!D58),"Unknown")</f>
+        <v>177.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E14,'Turns'!E30,'Turns'!E45,'Turns'!E57)=4,SUM('Turns'!E14,'Turns'!E30,'Turns'!E45,'Turns'!E57),"Unknown")</f>
-        <v>0.0001735173</v>
+        <f>IF(COUNT('Turns'!E14,'Turns'!E30,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E14,'Turns'!E30,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.000186856776</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F14,'Turns'!F30,'Turns'!F45,'Turns'!F57)=4,SUM('Turns'!F14,'Turns'!F30,'Turns'!F45,'Turns'!F57),"Unknown")</f>
-        <v>0.000198</v>
+        <f>IF(COUNT('Turns'!F14,'Turns'!F30,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F14,'Turns'!F30,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.0002124</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>29.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D45)=2,SUM('Turns'!D13,'Turns'!D45),"Unknown")</f>
+        <v>100.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.049698e-05</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E45)=2,SUM('Turns'!E13,'Turns'!E45),"Unknown")</f>
+        <v>0.0001055688</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F45)=2,SUM('Turns'!F13,'Turns'!F45),"Unknown")</f>
+        <v>0.00012</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E49,'Turns'!E61),"Unknown")</f>
-        <v>0.0003896690275</v>
+        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
+        <v>0.0004824758082</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F49,'Turns'!F61),"Unknown")</f>
-        <v>0.00044465</v>
+        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
+        <v>0.00054843</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>39.0</v>
+        <v>48.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>44.0</v>
+        <v>55.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>5359.855</v>
+        <v>6318.615</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>138</v>
@@ -2394,7 +2425,7 @@
         <v>49</v>
       </c>
       <c r="AD3" s="1">
-        <v>0.343</v>
+        <v>0.323</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>142</v>
@@ -2431,7 +2462,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -2443,7 +2474,7 @@
       </c>
       <c r="N4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.5860242e-05</v>
+        <v>3.59989608e-05</v>
       </c>
       <c r="O4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2460,46 +2491,46 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>82.0</v>
+        <v>92.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>8.623284e-05</v>
+        <v>9.7123296e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>9.84e-05</v>
+        <v>0.0001104</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.049698e-05</v>
+        <v>2.4280824e-05</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.000153115872</v>
+        <v>0.0001579309248</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017472</v>
+        <v>0.00017952</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2053.755</v>
+        <v>2159.168</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>138</v>
@@ -2539,7 +2570,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
@@ -2551,7 +2582,7 @@
       </c>
       <c r="N5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.5860242e-05</v>
+        <v>3.59989608e-05</v>
       </c>
       <c r="O5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -2568,49 +2599,49 @@
       </c>
       <c r="S5" s="2">
         <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>82.0</v>
+        <v>92.0</v>
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>8.623284e-05</v>
+        <v>9.7123296e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>9.84e-05</v>
+        <v>0.0001104</v>
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.049698e-05</v>
+        <v>2.4280824e-05</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.48e-05</v>
+        <v>2.76e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.000153115872</v>
+        <v>0.0001579309248</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017472</v>
+        <v>0.00017952</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="AC5" s="1" t="s">
         <v>93</v>
       </c>
       <c r="AD5" s="1">
-        <v>2046.721</v>
+        <v>2152.789</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>149</v>
@@ -2647,7 +2678,7 @@
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <v>1.055688e-06</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
@@ -2655,67 +2686,70 @@
       </c>
       <c r="M6" s="2">
         <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3443.0</v>
+        <v>3452.0</v>
       </c>
       <c r="N6" s="2">
         <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.0345461e-05</v>
+        <v>6.07372496e-05</v>
       </c>
       <c r="O6" s="2">
         <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.886e-05</v>
+        <v>6.904e-05</v>
       </c>
       <c r="P6" s="2">
         <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="Q6" s="2">
         <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.08133125e-05</v>
+        <v>2.287324e-05</v>
       </c>
       <c r="R6" s="2">
         <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.375e-05</v>
+        <v>2.6e-05</v>
       </c>
       <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
-        <v>43.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
-        <v>4.521966e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
-        <v>5.16e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V6" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="W6" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
+        <v>8.1287976e-05</v>
       </c>
       <c r="X6" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
+        <v>9.24e-05</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
-        <v>0.0001274300535</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
+        <v>0.0002166271776</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
-        <v>0.00014541</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
+        <v>0.00024624</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>2276.116</v>
+        <v>3038.35</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>138</v>
@@ -2752,7 +2786,7 @@
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <v>1.055688e-06</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
@@ -2760,67 +2794,70 @@
       </c>
       <c r="M7" s="2">
         <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3443.0</v>
+        <v>3452.0</v>
       </c>
       <c r="N7" s="2">
         <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.0345461e-05</v>
+        <v>6.07372496e-05</v>
       </c>
       <c r="O7" s="2">
         <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.886e-05</v>
+        <v>6.904e-05</v>
       </c>
       <c r="P7" s="2">
         <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="Q7" s="2">
         <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.08133125e-05</v>
+        <v>2.287324e-05</v>
       </c>
       <c r="R7" s="2">
         <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.375e-05</v>
+        <v>2.6e-05</v>
       </c>
       <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
-        <v>43.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
-        <v>4.521966e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
-        <v>5.16e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V7" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="W7" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
+        <v>8.1287976e-05</v>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
+        <v>9.24e-05</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
-        <v>0.0001274300535</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
+        <v>0.0002166271776</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
-        <v>0.00014541</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
+        <v>0.00024624</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>2273.475</v>
+        <v>3036.543</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>138</v>
@@ -2857,7 +2894,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.05162e-06</v>
+        <v>1.055688e-06</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
@@ -2865,67 +2902,70 @@
       </c>
       <c r="M8" s="2">
         <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3443.0</v>
+        <v>3452.0</v>
       </c>
       <c r="N8" s="2">
         <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.0345461e-05</v>
+        <v>6.07372496e-05</v>
       </c>
       <c r="O8" s="2">
         <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.886e-05</v>
+        <v>6.904e-05</v>
       </c>
       <c r="P8" s="2">
         <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="Q8" s="2">
         <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.08133125e-05</v>
+        <v>2.287324e-05</v>
       </c>
       <c r="R8" s="2">
         <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.375e-05</v>
+        <v>2.6e-05</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D45)=2,SUM('Turns'!D30,'Turns'!D45),"Unknown")</f>
-        <v>43.0</v>
+        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
+        <v>48.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E45)=2,SUM('Turns'!E30,'Turns'!E45),"Unknown")</f>
-        <v>4.521966e-05</v>
+        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
+        <v>5.0673024e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F45)=2,SUM('Turns'!F30,'Turns'!F45),"Unknown")</f>
-        <v>5.16e-05</v>
+        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
+        <v>5.76e-05</v>
       </c>
       <c r="V8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
+        <v>77.0</v>
       </c>
       <c r="W8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
+        <v>8.1287976e-05</v>
       </c>
       <c r="X8" s="2">
-        <v>0</v>
+        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
+        <v>9.24e-05</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E49)=2,SUM('Turns'!E34,'Turns'!E49),"Unknown")</f>
-        <v>0.0001274300535</v>
+        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
+        <v>0.0002166271776</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F49)=2,SUM('Turns'!F34,'Turns'!F49),"Unknown")</f>
-        <v>0.00014541</v>
+        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
+        <v>0.00024624</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>2271.449</v>
+        <v>3035.199</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>138</v>
@@ -2957,7 +2997,7 @@
         <v>158</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.322</v>
+        <v>1.423</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>142</v>
@@ -2994,7 +3034,7 @@
       </c>
       <c r="K10" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L10" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
@@ -3006,7 +3046,7 @@
       </c>
       <c r="N10" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.9655684e-05</v>
+        <v>2.97704016e-05</v>
       </c>
       <c r="O10" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -3014,15 +3054,15 @@
       </c>
       <c r="P10" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>59.0</v>
+        <v>68.0</v>
       </c>
       <c r="Q10" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.29261625e-05</v>
+        <v>1.495558e-05</v>
       </c>
       <c r="R10" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.475e-05</v>
+        <v>1.7e-05</v>
       </c>
       <c r="S10" s="2">
         <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
@@ -3030,7 +3070,7 @@
       </c>
       <c r="T10" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>1.998078e-05</v>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U10" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
@@ -3047,22 +3087,22 @@
       </c>
       <c r="Y10" s="2">
         <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>6.30884365e-05</v>
+        <v>6.53118976e-05</v>
       </c>
       <c r="Z10" s="2">
         <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>7.199e-05</v>
+        <v>7.424e-05</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB10" s="5">
         <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
         <v>7.0</v>
       </c>
       <c r="AD10" s="1">
-        <v>1236.572</v>
+        <v>1093.913</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>138</v>
@@ -3085,7 +3125,7 @@
         <v>112</v>
       </c>
       <c r="F11" s="1">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>148</v>
@@ -3102,7 +3142,7 @@
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
@@ -3114,7 +3154,7 @@
       </c>
       <c r="N11" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.9655684e-05</v>
+        <v>2.97704016e-05</v>
       </c>
       <c r="O11" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -3122,15 +3162,15 @@
       </c>
       <c r="P11" s="2">
         <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>59.0</v>
+        <v>68.0</v>
       </c>
       <c r="Q11" s="2">
         <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.29261625e-05</v>
+        <v>1.495558e-05</v>
       </c>
       <c r="R11" s="2">
         <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.475e-05</v>
+        <v>1.7e-05</v>
       </c>
       <c r="S11" s="2">
         <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
@@ -3138,7 +3178,7 @@
       </c>
       <c r="T11" s="2">
         <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>1.998078e-05</v>
+        <v>2.0058072e-05</v>
       </c>
       <c r="U11" s="2">
         <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
@@ -3155,15 +3195,15 @@
       </c>
       <c r="Y11" s="2">
         <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>6.30884365e-05</v>
+        <v>6.53118976e-05</v>
       </c>
       <c r="Z11" s="2">
         <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>7.199e-05</v>
+        <v>7.424e-05</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="AB11" s="5">
         <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3173,7 +3213,7 @@
         <v>119</v>
       </c>
       <c r="AD11" s="1">
-        <v>1228.523</v>
+        <v>1087.122</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>149</v>
@@ -3205,7 +3245,7 @@
         <v>158</v>
       </c>
       <c r="AD12" s="1">
-        <v>4.112</v>
+        <v>2.24</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>142</v>
@@ -3237,7 +3277,7 @@
         <v>165</v>
       </c>
       <c r="AD13" s="1">
-        <v>1.036</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>142</v>
@@ -3274,7 +3314,7 @@
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
@@ -3282,15 +3322,15 @@
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
-        <v>1751.0</v>
+        <v>1760.0</v>
       </c>
       <c r="N14" s="2">
         <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>3.0689777e-05</v>
+        <v>3.0966848e-05</v>
       </c>
       <c r="O14" s="2">
         <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>3.502e-05</v>
+        <v>3.52e-05</v>
       </c>
       <c r="P14" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -3298,51 +3338,54 @@
       </c>
       <c r="Q14" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>7.88715e-06</v>
+        <v>7.91766e-06</v>
       </c>
       <c r="R14" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
         <v>9e-06</v>
       </c>
       <c r="S14" s="2">
+        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
+        <v>29.0</v>
+      </c>
+      <c r="T14" s="2">
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>3.0614952e-05</v>
+      </c>
+      <c r="U14" s="2">
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>3.48e-05</v>
+      </c>
+      <c r="V14" s="2">
         <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-      <c r="T14" s="2">
+        <v>77.0</v>
+      </c>
+      <c r="W14" s="2">
         <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>2.523888e-05</v>
-      </c>
-      <c r="U14" s="2">
+        <v>8.1287976e-05</v>
+      </c>
+      <c r="X14" s="2">
         <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>2.88e-05</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2">
-        <v>0</v>
+        <v>9.24e-05</v>
       </c>
       <c r="Y14" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>6.4341617e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>0.00015131528</v>
       </c>
       <c r="Z14" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
-        <v>7.342e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>0.000172</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1023.072</v>
+        <v>1932.661</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>138</v>
@@ -3365,7 +3408,7 @@
         <v>112</v>
       </c>
       <c r="F15" s="1">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>148</v>
@@ -3382,7 +3425,7 @@
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
@@ -3390,15 +3433,15 @@
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
-        <v>1751.0</v>
+        <v>1760.0</v>
       </c>
       <c r="N15" s="2">
         <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>3.0689777e-05</v>
+        <v>3.0966848e-05</v>
       </c>
       <c r="O15" s="2">
         <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>3.502e-05</v>
+        <v>3.52e-05</v>
       </c>
       <c r="P15" s="2">
         <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
@@ -3406,54 +3449,57 @@
       </c>
       <c r="Q15" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>7.88715e-06</v>
+        <v>7.91766e-06</v>
       </c>
       <c r="R15" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
         <v>9e-06</v>
       </c>
       <c r="S15" s="2">
+        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
+        <v>29.0</v>
+      </c>
+      <c r="T15" s="2">
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>3.0614952e-05</v>
+      </c>
+      <c r="U15" s="2">
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>3.48e-05</v>
+      </c>
+      <c r="V15" s="2">
         <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>24.0</v>
-      </c>
-      <c r="T15" s="2">
+        <v>77.0</v>
+      </c>
+      <c r="W15" s="2">
         <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>2.523888e-05</v>
-      </c>
-      <c r="U15" s="2">
+        <v>8.1287976e-05</v>
+      </c>
+      <c r="X15" s="2">
         <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>2.88e-05</v>
-      </c>
-      <c r="V15" s="2">
-        <v>0</v>
-      </c>
-      <c r="W15" s="2">
-        <v>0</v>
-      </c>
-      <c r="X15" s="2">
-        <v>0</v>
+        <v>9.24e-05</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
-        <v>6.4341617e-05</v>
+        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
+        <v>0.00015131528</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
-        <v>7.342e-05</v>
+        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
+        <v>0.000172</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>17.0</v>
       </c>
       <c r="AC15" s="1" t="s">
         <v>127</v>
       </c>
       <c r="AD15" s="1">
-        <v>1015.023</v>
+        <v>1928.636</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>149</v>
@@ -3485,52 +3531,52 @@
         <v>49</v>
       </c>
       <c r="J16" s="2">
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K16" s="2">
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L16" s="2">
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M16" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K16" s="2">
+        <v>2046.0</v>
+      </c>
+      <c r="N16" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L16" s="2">
+        <v>3.59989608e-05</v>
+      </c>
+      <c r="O16" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>3.5860242e-05</v>
-      </c>
-      <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>140.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>147.0</v>
       </c>
       <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>3.067225e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>3.2330445e-05</v>
       </c>
       <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>3.5e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>3.675e-05</v>
       </c>
       <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>37.0</v>
       </c>
       <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>4.20648e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>3.9060456e-05</v>
       </c>
       <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>4.44e-05</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
@@ -3542,12 +3588,12 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.000109123102</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.0001079177058</v>
       </c>
       <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.00012452</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00012267</v>
       </c>
       <c r="AA16" s="5">
         <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3558,7 +3604,7 @@
         <v>12.0</v>
       </c>
       <c r="AD16" s="1">
-        <v>1023.474</v>
+        <v>1114.957</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>138</v>
@@ -3581,7 +3627,7 @@
         <v>112</v>
       </c>
       <c r="F17" s="1">
-        <v>2189</v>
+        <v>2196</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>148</v>
@@ -3593,52 +3639,52 @@
         <v>169</v>
       </c>
       <c r="J17" s="2">
+        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="K17" s="2">
+        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
+        <v>5.27844e-07</v>
+      </c>
+      <c r="L17" s="2">
+        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
+        <v>6e-07</v>
+      </c>
+      <c r="M17" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K17" s="2">
+        <v>2046.0</v>
+      </c>
+      <c r="N17" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>5.2581e-07</v>
-      </c>
-      <c r="L17" s="2">
+        <v>3.59989608e-05</v>
+      </c>
+      <c r="O17" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E51)=1,SUM('Turns'!E51),"Unknown")</f>
-        <v>3.5860242e-05</v>
-      </c>
-      <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F51)=1,SUM('Turns'!F51),"Unknown")</f>
         <v>4.092e-05</v>
       </c>
       <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
-        <v>140.0</v>
+        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
+        <v>147.0</v>
       </c>
       <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
-        <v>3.067225e-05</v>
+        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
+        <v>3.2330445e-05</v>
       </c>
       <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
-        <v>3.5e-05</v>
+        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
+        <v>3.675e-05</v>
       </c>
       <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D57)=1,SUM('Turns'!D57),"Unknown")</f>
-        <v>40.0</v>
+        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
+        <v>37.0</v>
       </c>
       <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>4.20648e-05</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>3.9060456e-05</v>
       </c>
       <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
-        <v>4.8e-05</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>4.44e-05</v>
       </c>
       <c r="V17" s="2">
         <v>0</v>
@@ -3650,12 +3696,12 @@
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.000109123102</v>
+        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
+        <v>0.0001079177058</v>
       </c>
       <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.00012452</v>
+        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
+        <v>0.00012267</v>
       </c>
       <c r="AA17" s="5">
         <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3669,7 +3715,7 @@
         <v>131</v>
       </c>
       <c r="AD17" s="1">
-        <v>1016.334</v>
+        <v>1109.268</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>149</v>
@@ -3727,7 +3773,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/subagent_chat/report.xlsx
+++ b/reports/subagent_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="194">
   <si>
     <t>Request</t>
   </si>
@@ -165,13 +165,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d587-81ab-7592-8676-94fee801eb4b</t>
+    <t>01a1143f-831e-7141-818a-14f77faabd17</t>
   </si>
   <si>
     <t>Recording</t>
   </si>
   <si>
-    <t>Provider trace</t>
+    <t>Offline simulation</t>
   </si>
   <si>
     <t>FX reference date</t>
@@ -216,7 +216,7 @@
     <t>Pricing scope</t>
   </si>
   <si>
-    <t>Standard online token rates. Verify rates and model access before use. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. No batch, regional, long-context, tool, or negotiated pricing adjustments are applied.</t>
+    <t>Published online token rates verified 2026-10-05. Copilot uses GitHub rates, including saved long-context tiers, before plan allowances; these are usage estimates, not subscription invoices. Cache writes with unspecified lifetime use the 5-minute rate unless an explicit cache_write rate is configured. Direct OpenAI and Anthropic entries use standard rates; no batch, regional, tool, negotiated, or unrecorded context-tier adjustments are applied. Model availability and context capacity require separate verification.</t>
   </si>
   <si>
     <t>Model</t>
@@ -252,7 +252,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>2026-09-18</t>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>https://developers.openai.com/api/docs/models/gpt-5.5.md</t>
@@ -291,6 +291,99 @@
     <t>Illustrative demo rates based on openai:gpt-5.6-luna; no provider billing</t>
   </si>
   <si>
+    <t>anthropic:claude-haiku-4-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-haiku-4-5-20251001</t>
+  </si>
+  <si>
+    <t>anthropic:claude-opus-5-5</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-4-6</t>
+  </si>
+  <si>
+    <t>anthropic:claude-sonnet-5-5</t>
+  </si>
+  <si>
+    <t>copilot:claude-haiku-4.5</t>
+  </si>
+  <si>
+    <t>https://docs.github.com/en/copilot/reference/copilot-billing/models-and-pricing</t>
+  </si>
+  <si>
+    <t>copilot:claude-opus-5.5</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-4.6</t>
+  </si>
+  <si>
+    <t>copilot:claude-sonnet-5.5</t>
+  </si>
+  <si>
+    <t>copilot:gemini-3.8-flash</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.3-codex</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-astra</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-astra.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-luna</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-luna.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6-sol.md</t>
+  </si>
+  <si>
+    <t>openai:gpt-6.1-sol</t>
+  </si>
+  <si>
+    <t>https://developers.openai.com/api/docs/models/gpt-6.1-sol.md</t>
+  </si>
+  <si>
+    <t>copilot:gpt-5.4 [long context]</t>
+  </si>
+  <si>
+    <t>Above 272,000 input tokens</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-astra [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-luna [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6-sol [long context]</t>
+  </si>
+  <si>
+    <t>copilot:gpt-6.1-sol [long context]</t>
+  </si>
+  <si>
     <t>Run total</t>
   </si>
   <si>
@@ -303,127 +396,118 @@
     <t>LLM request</t>
   </si>
   <si>
-    <t>gpt-5.6-luna</t>
-  </si>
-  <si>
-    <t>01a0d587-81b4-78a1-9a6c-fac8360c169a</t>
+    <t>scripted-chat</t>
+  </si>
+  <si>
+    <t>01a1143f-8321-79b2-85c0-d160373e18e6</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Tool definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    System prompt</t>
+  </si>
+  <si>
+    <t>Delegate echoing the supplied text to isolated-subagent using task. Provide a self-contained assignment. After its summary returns, answer the user concisely. The specialist uses an echo tool, which supplies no independent factual evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    User prompt</t>
+  </si>
+  <si>
+    <t>Have the specialist echo ReAct and explain how its tool result returns to the parent.</t>
+  </si>
+  <si>
+    <t>Cache write</t>
+  </si>
+  <si>
+    <t>Context · added / total</t>
+  </si>
+  <si>
+    <t>LLM response</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Output content</t>
+  </si>
+  <si>
+    <t>{"name": "task", "args": {"subagent_type": "isolated-subagent", "description": "Call echo_tool with the text ReAct and summarize what it returned."}, "id": "delegate-1", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Call total</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>Tool · task</t>
+  </si>
+  <si>
+    <t>01a1143f-83a1-7520-8dc2-d4d6a652d02d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Arguments</t>
+  </si>
+  <si>
+    <t>{'subagent_type': 'isolated-subagent', 'description': 'Call echo_tool with the text ReAct and summarize what it returned.'}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Result</t>
+  </si>
+  <si>
+    <t>Command(update={'messages': [ToolMessage(content='The echo tool returned Your input was: ReAct. It repeated the supplied text without adding factual evidence.', tool_call_id='delegate-1')]})</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>01a1143f-83a3-7d82-b3d1-8b1bb7bad08e</t>
+  </si>
+  <si>
+    <t>You are a workflow teaching specialist. Call echo_tool with the assigned text, then summarize the returned echo for the parent. The echo repeats supplied input and provides no independent factual evidence. Do not delegate further.</t>
+  </si>
+  <si>
+    <t>{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "specialist-lookup-1", "type": "tool_call"}</t>
+  </si>
+  <si>
+    <t>Tool · echo_tool</t>
+  </si>
+  <si>
+    <t>01a1143f-83a7-7720-bac4-bde63a0cdabd</t>
+  </si>
+  <si>
+    <t>{'text': 'ReAct'}</t>
+  </si>
+  <si>
+    <t>Your input was: ReAct</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>01a1143f-83a8-7422-b1b7-e3e23ebcb479</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
   </si>
   <si>
-    <t>Input at standard rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Tool definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    System prompt</t>
-  </si>
-  <si>
-    <t>Delegate echoing the supplied text to isolated-subagent using task. Provide a self-contained assignment. After its summary returns, answer the user concisely. The specialist uses an echo tool, which supplies no independent factual evidence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    User prompt</t>
-  </si>
-  <si>
-    <t>Have the specialist echo ReAct and explain how its tool result returns to the parent.</t>
-  </si>
-  <si>
-    <t>Cache write</t>
-  </si>
-  <si>
-    <t>Context · added / total</t>
-  </si>
-  <si>
-    <t>LLM response</t>
-  </si>
-  <si>
-    <t>Reasoning</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Output content</t>
-  </si>
-  <si>
-    <t>[{"id": "rs_001a0a066573c3c3006ab5a3b78c1487d281c258c33e38a742", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaO39HK-Pu-9yad_xiB-k5wb98vVuue-6mevm2ji_VkMpy2ubvVDy48vvDcvsjC4gTcgktoEs4l4t8K0vl6Ahw58c8D48ekFfT3_z4Uc3JubJtUg8h1vSNfdM4MCDs8ApthEHOFwHDx7127vSE3DpNcb3x44i0WyETC85N8xhLdr5XBf5DqinUOxaZcO7rekKb3wqOGRcLvPvxlmED40mnZ-_MlXdoClZrbQxSnLHcU39IfPormBWfPZuCdoaMCSd4gVSe1dx5PoZ-vAyej3opfC4KWesc3U6hkYkhJiXhgJB04TItWPVIVbxoDKX9ByGsZMVHbNPQe0jrUY5xpKzUzPkcmX-XDI7COl-xMBzx3RpO9vWWNbxSkjhUv2sHnFz69pO7b1VDcIh9EsLoa08A5SSOgQOU_D4FurQv7Cu0ZI4o9N2jnBQdhqCCYGsFqJBNIgGddpO8bFrjXLHf8PzC6TSBFLgbK8qC0M2pTPgjlnGS4GWwjdQemU3Le9uu6SE9NBZUZJxtP5quYACAJ6oCThwEB_be9ajhT8V5Uy5kzrM_e0pdQBlJSWiQrlQagGvcqt5JqXxfGewZiuybjiipZY1voPxa2pV2CP2trvDnhf9DR55XpZbN93uBrFf-0W-jVfyfRdRDrsNHwDmZ8VjQnaOlW4s46fEfKB_J5itkK0YZwlpeBkC-4r_HHW3aXTtlPEGHDsgJyr-Te2y4J0LoFnWdQUOFKCsQeSBDw9tmJrcOcRna_9cxqUe6lJ7Se5hI9u2mKO5xeAF2TtS69yQSPC7j7gIFTqrvi-OEGh5SshPH_kgiXdPPH_RBiBN7lQTaPzK9VHjaHf5pg6tFRnp8HC3T3w7Z_eTAtVaXQ50v8nq82-0EW4_rUamC2mrusssLYZgWLD4Mqw9yI7Z0ATHMmVd9pvavHVhMElXg9RQTTcQMmR6I3R5zfav7hNGKFguXpZP0Q_nb6FJ-TOfiZUC6VmCgEdJgyhpppAgzv0JMWl-nTzdXvDcuVqzxb6pXvOVjQs6iyEDX01_rzddBF7EqJ7V0O4LdSNVHClDzRzuUv7j7lPZz4xgci7wQsSmsY33nLgK66kA0IvyIZxf3ykc9SSrITqTVfnZGI5V5GPXZyAVt7vmXfh4rBh8YnuG9Lt--lRq33Rj-icUGCj27pMcvC65rV9-Wn12g1RNoHqgrXdmCiygkQr_l42O0Nz1Iw-oWKACw_Xvb1we5ulzrOO2vxYVqk93YGhj3AOjn7yN3dXXhGLqabelT3hzcAY7frdmuYANR27HhrIZS-O5yB-gbCxeFoENfoOMKEVYKRylK63DgU="}, {"type": "function_call", "name": "task", "arguments": "{\"description\":\"Use your echo tool to echo exactly the text: \\\"ReAct\\\". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.\" ,\"subagent_type\":\"isolated-subagent\"}", "call_id": "call_9WpjMeoociWZb1WXPQZHvDLd", "id": "fc_001a0a066573c3c3006ab5a3b7cfd087d2bff4768967db8122", "index": 1}]
-{"name": "task", "args": {"description": "Use your echo tool to echo exactly the text: \"ReAct\". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.", "subagent_type": "isolated-subagent"}, "id": "call_9WpjMeoociWZb1WXPQZHvDLd", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Call total</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Tool · task</t>
-  </si>
-  <si>
-    <t>01a0d587-8a21-73a1-bfef-b804d74a9901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Arguments</t>
-  </si>
-  <si>
-    <t>{'description': 'Use your echo tool to echo exactly the text: "ReAct". Then briefly explain, in general terms, how the result produced by your tool is returned to the parent agent. Return both the exact echoed text and the explanation in your final summary. Do not add independent factual claims beyond describing the tool-result handoff.', 'subagent_type': 'isolated-subagent'}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Result</t>
-  </si>
-  <si>
-    <t>Command(update={'files': {}, 'messages': [ToolMessage(content='ReAct\n\nThe tool result is returned to the parent agent as the tool’s response, containing the echoed input.', tool_call_id='call_9WpjMeoociWZb1WXPQZHvDLd')]})</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>01a0d587-8a2a-72d3-b994-1017bc62cc76</t>
-  </si>
-  <si>
-    <t>You are a workflow teaching specialist. Call echo_tool with the assigned text, then summarize the returned echo for the parent. The echo repeats supplied input and provides no independent factual evidence. Do not delegate further.</t>
-  </si>
-  <si>
-    <t>[{"type": "function_call", "name": "echo_tool", "arguments": "{\"text\":\"ReAct\"}", "call_id": "call_nEdS34lKTFNB3m1cUsUrwKyh", "id": "fc_0e7bbe1ed7254a68006ab5a3b9b6a487d2a58f8dd680c40a44", "index": 0}]
-{"name": "echo_tool", "args": {"text": "ReAct"}, "id": "call_nEdS34lKTFNB3m1cUsUrwKyh", "type": "tool_call"}</t>
-  </si>
-  <si>
-    <t>Tool · echo_tool</t>
-  </si>
-  <si>
-    <t>01a0d587-8e6c-7191-8cd5-31fa5e45c08f</t>
-  </si>
-  <si>
-    <t>{'text': 'ReAct'}</t>
-  </si>
-  <si>
-    <t>Your input was: ReAct</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>01a0d587-8e71-7991-a0ed-07bc3b8180ad</t>
-  </si>
-  <si>
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"id": "rs_0e7bbe1ed7254a68006ab5a3bac3d087d2bf3d21de94d4f75f", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaO7l89d03i2QN1NUrR8bQHpzRAE3D3o1KWmKjI60pK5TlcJVjXGyCHmPY9Q-b2x2b_z36PfQ1hDdED64u4fl7Ll0EfeWOmnIQAbzLIILUuNygSp-SZsL5B8VY5Sxtd3utaCeEBULTScKSlse1iy6iT6fO12T78hrI8gOPZRKzWNDmigcC7sWEkAVUt4xWFsitKnWc1fCf5zkKo_YpS5wxOUdZyUktXShiqK1k-BpMP2-ekIHEdXbOIRpv1YhKMCMAOLpVyqx_2u0_XSuH-ckaxdOF2PR26RjT7whIltN61kstKt-2g0rzMHEtHYVnC6ifDqqVyk9HPq3oAVazEUI_Hx6grLhu5jLUGiC05rhaYXyfafYv75AayAJHRGpadypWW0wgYEuuFN3KdcG8iNIzqYcZ5ssny6BEmGlgQEZIE88ILdoIKfb9ocSpQGrq5Q6BKfOWeMSczgCFRAxGAwUQlK_kPlg64hAwd9h6hExBOSO4bjqUL2-KC0B7OfVD9QBSmH-5lC6t69-eNj8i29I08C0QlGHRSFsK9_XXgQGLm2U6K_dU7NamiKbTGrH1H3GTQ9FGQjJlDD8dvc_Ur6UYDpKbXaUKhQL_7wjEiHSfq78NUyaOT9KkI1MbylNWnxZWNDlhY6rjMydWqGWKckBgYuNwkS5HlzfOFDABM1IYOx9iT8fRMKvKG_MvpBHm71KyUMBS8RuXUHg_Vy0oHuWkxbp4NTOie8WwR5zsT72kpHoHuRsDH_c9rQPMkr6qNP5evItpK86tAwc0O42tycI0tu4kA09ylQc8oxKhZQFPLkhZNwa2QK4ZoVrH_3wFx5T5c6vzZkuqi71NW3TCrvMFF-Jf23dX1nfdRmvITsI5ZBUOLmfJgsJpVzpDFDsg7d2VjiVGM9bz_6uTDMJ5IooR91xKc1mm7TpAVH_CP0TGyiwZaksWcNsQ1xROwL4zUxqv3PH3NGwdb56qr9nRuwDDeSweFv7RdplJ_AD6i5nG0iNmS3iBQcJJacNYn5198i-gqI1Z1kOAwGo4Sn3i9feWXJL46ZE5lUFloNXNO9pGg42uebTb6yJigPliUO2HyZ1hWz94CQVYSVXcoKJCYd4TvsZjk6zzUt77m2FwSJI2e_E4IV2SB3pZ8-EacyZYdJvJrof-VQSYOHVftF77hqFkMDdrHEBtFhulEbVGwMGaobe_Gg0Oi-Z4FPxf4KFNOxpEoMDE9CtgX8E_K-koWkzGyXevMKb-eXcbXXQexFwdCvaMMIPqOxvcSLcMBNxvyU7IVntdRJWiAV37v_NUBeu9qFU0GIeMoJwvBtH0MeD2FQk_iwruUdYyCUT455f3uWFlLn_MwAUcAYoCcm0Z0u6ZZy52p0tZrXBrim1ZoXWMjBgOpC_5pI2tjdwVKSDN3dCMiRSDuof4rgB7kiQn4ac02VB7YjIEey6qaoluZjhTcK3b9eu__XB-UFzbu-5c75sRFchfOiPzSHlsQFT5JusC92N2iLG1jYCQCpXc7sY474DwEr8ccrZFWfbaJGHD0pvPogbrl5EyxP0n-ciuXA9vOR-2CFtBsbPzFsPun8Xs_vh5OmkoqEk9QFbObzoItYUuRnH4JCZHwIO7NQBpbkSAcfm8OqNHhDuydCztBVEEov0m3LPzz_7d9Jp8Jg8E1TMaCKmCrnbcZzBXt9aN-U78-A4g=="}, {"type": "text", "text": "ReAct\n\nThe tool result is returned to the parent agent as the tool\u2019s response, containing the echoed input.", "phase": "final_answer", "index": 1, "id": "msg_0e7bbe1ed7254a68006ab5a3bb7c4c87d2bca81bc05bd27494"}]</t>
+    <t>The echo tool returned Your input was: ReAct. It repeated the supplied text without adding factual evidence.</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>01a0d587-9603-7490-a940-dd3ee0b70502</t>
-  </si>
-  <si>
-    <t>ReAct
-The tool result is returned to the parent agent as the tool’s response, containing the echoed input.</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "The specialist echoed **\u201cReAct.\u201d**\n\nIts tool result is returned to the parent agent as the tool response, which contains the echoed input and any accompanying summary.", "phase": "final_answer", "index": 0, "id": "msg_001a0a066573c3c3006ab5a3bc95c087d2aa32d3a860b72627"}]</t>
+    <t>01a1143f-83ac-7cf1-a37c-45609fd63031</t>
+  </si>
+  <si>
+    <t>The specialist echoed ReAct and received Your input was: ReAct. The parent receives its summary; the specialist's internal tool exchange stays in its own context.</t>
   </si>
   <si>
     <t>delegating_parent</t>
@@ -438,34 +522,22 @@
     <t>Subtree total</t>
   </si>
   <si>
-    <t xml:space="preserve">    PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>Check message history and repair missing tool responses before the agent starts.</t>
-  </si>
-  <si>
-    <t>01a0d587-81ae-7250-a987-024548c5518d</t>
-  </si>
-  <si>
-    <t>No model charge</t>
-  </si>
-  <si>
     <t xml:space="preserve">    model</t>
   </si>
   <si>
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d587-81af-7132-a9d3-dcd784e7db1a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        ChatOpenAI</t>
+    <t>01a1143f-8320-7372-b5ea-fdac72f8bdfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SimulatedModel</t>
   </si>
   <si>
     <t>model</t>
   </si>
   <si>
-    <t>Generate the next assistant message or tool request from the current conversation.</t>
+    <t>A parent agent delegates to a specialist.</t>
   </si>
   <si>
     <t>Own call</t>
@@ -477,7 +549,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d587-8a20-78a3-9486-aa581d19db17</t>
+    <t>01a1143f-83a0-7292-b546-b39421c51891</t>
   </si>
   <si>
     <t xml:space="preserve">        task</t>
@@ -488,7 +560,6 @@
   <si>
     <t>Launch an ephemeral subagent to handle a complex, multi-step task.
 Available agent types and the tools they have access to:
-- general-purpose: General-purpose agent for researching complex questions, searching for files and content, and executing multi-step tasks. When you are searching for a keyword or file and are not confident that you will find the right match in the first few tries use this agent to perform the search for you. This agent has access to all tools as the main agent.
 - isolated-subagent: Echoes assigned text with a local tool and summarizes its result.
 Specify subagent_type to select the agent. Usage notes:
 - Launch multiple agents concurrently when their tasks are independent, using a single message with multiple tool calls.
@@ -505,28 +576,25 @@
     <t>Execute the isolated-subagent workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0d587-8a21-73a1-bfef-b811577aec87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                PatchToolCallsMiddleware.before_agent</t>
-  </si>
-  <si>
-    <t>01a0d587-8a22-7b71-ba48-b65b9f5b7dff</t>
+    <t>01a1143f-83a1-7520-8dc2-d4e9a12dc0c4</t>
   </si>
   <si>
     <t xml:space="preserve">                model</t>
   </si>
   <si>
-    <t>01a0d587-8a24-7f60-b5ab-cd48fc04e488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                    ChatOpenAI</t>
+    <t>01a1143f-83a2-7f61-a440-1209bd5d888c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    SimulatedModel</t>
   </si>
   <si>
     <t xml:space="preserve">                tools</t>
   </si>
   <si>
-    <t>01a0d587-8e6b-7183-9c1b-2b3dec508828</t>
+    <t>01a1143f-83a6-75f1-9b66-69c65f85322e</t>
+  </si>
+  <si>
+    <t>No model charge</t>
   </si>
   <si>
     <t xml:space="preserve">                    echo_tool</t>
@@ -535,10 +603,10 @@
     <t>Return the provided text prefixed with "Your input was: ".</t>
   </si>
   <si>
-    <t>01a0d587-8e6e-72e1-8c9e-e86a0aa23fb6</t>
-  </si>
-  <si>
-    <t>01a0d587-95ff-7241-92d0-bdc92bff4c45</t>
+    <t>01a1143f-83a8-7422-b1b7-e3ddc0922340</t>
+  </si>
+  <si>
+    <t>01a1143f-83ac-7cf1-a37c-455dddb17dd4</t>
   </si>
 </sst>
 </file>
@@ -945,7 +1013,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1002,23 +1070,23 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="C2" s="4" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004824758082</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.00038620586</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00054843</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.000439</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1026,1156 +1094,1072 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004824758082</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.00038620586</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00054843</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.000439</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4">
-        <v>2049</v>
+        <v>468</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
-        <v>2046</v>
+        <v>468</v>
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.59989608e-05</v>
+        <v>8.2343664e-05</v>
       </c>
       <c r="F5" s="2">
-        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!C17),D5*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.092e-05</v>
+        <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B22),D5*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>9.36e-05</v>
       </c>
       <c r="G5" s="5">
         <f>IF(ISNUMBER(E5),ROUND(E5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="5">
         <f>IF(ISNUMBER(F5),ROUND(F5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="5">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER('Reference data'!$B$3)),F6*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(D6=0,0,IF(ISNUMBER('Reference data'!B17),D6*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(ISNUMBER(E6),ROUND(E6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="5">
-        <f>IF(ISNUMBER(F6),ROUND(F6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
+        <v>129</v>
+      </c>
+      <c r="D6" s="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="47" customHeight="1">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="47" customHeight="1">
+        <v>130</v>
+      </c>
+      <c r="D7" s="1">
+        <v>68</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>132</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="D9" s="1">
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="4">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D10" s="1">
+        <v>468</v>
+      </c>
+      <c r="L10" s="1">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="5">
+        <v>75</v>
+      </c>
+      <c r="E12" s="2">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
+        <v>7.91766e-05</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!E22),D12*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>9e-05</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>8.0</v>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(ISNUMBER(F12),ROUND(F12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="47" customHeight="1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="5">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.4280824e-05</v>
-      </c>
-      <c r="F13" s="2">
-        <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!F17),D13*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.76e-05</v>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H13" s="5">
-        <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>138</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="24" customHeight="1">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="5">
-        <v>92</v>
-      </c>
-      <c r="E14" s="2">
-        <f>IF(AND(ISNUMBER(F14),ISNUMBER('Reference data'!$B$3)),F14*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.7123296e-05</v>
-      </c>
-      <c r="F14" s="2">
-        <f>IF(D14=0,0,IF(ISNUMBER('Reference data'!E17),D14*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001104</v>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(ISNUMBER(E14),ROUND(E14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>10.0</v>
-      </c>
-      <c r="H14" s="5">
-        <f>IF(ISNUMBER(F14),ROUND(F14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="398" customHeight="1">
+        <v>134</v>
+      </c>
+      <c r="D14" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="24" customHeight="1">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="24" customHeight="1">
-      <c r="A17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14)=4,SUM('Turns'!E5,'Turns'!E6,'Turns'!E13,'Turns'!E14),"Unknown")</f>
-        <v>0.0001579309248</v>
-      </c>
-      <c r="F18" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14)=4,SUM('Turns'!F5,'Turns'!F6,'Turns'!F13,'Turns'!F14),"Unknown")</f>
-        <v>0.00017952</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(ISNUMBER(E18),ROUND(E18*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>135</v>
+      </c>
+      <c r="D15" s="1">
+        <v>75</v>
+      </c>
+      <c r="L15" s="1">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E16" s="2">
+        <f>IF(COUNT('Turns'!E5,'Turns'!E12)=2,SUM('Turns'!E5,'Turns'!E12),"Unknown")</f>
+        <v>0.000161520264</v>
+      </c>
+      <c r="F16" s="2">
+        <f>IF(COUNT('Turns'!F5,'Turns'!F12)=2,SUM('Turns'!F5,'Turns'!F12),"Unknown")</f>
+        <v>0.0001836</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(ISNUMBER(E16),ROUND(E16*'Reference data'!$B$2,0),"Unknown")</f>
         <v>16.0</v>
       </c>
-      <c r="H18" s="5">
-        <f>IF(ISNUMBER(F18),ROUND(F18*'Reference data'!$B$2,0),"Unknown")</f>
+      <c r="H16" s="5">
+        <f>IF(ISNUMBER(F16),ROUND(F16*'Reference data'!$B$2,0),"Unknown")</f>
         <v>18.0</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="B19" s="4">
-        <v>1</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="73" customHeight="1">
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="47" customHeight="1">
+      <c r="K16" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="34" customHeight="1">
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="47" customHeight="1">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>146</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4">
+        <v>180</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="24" customHeight="1">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1763</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="24" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="D21" s="5">
+        <v>180</v>
+      </c>
+      <c r="E21" s="2">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER('Reference data'!$B$3)),F21*'Reference data'!$B$3,"Unknown")</f>
+        <v>3.167064e-05</v>
+      </c>
+      <c r="F21" s="2">
+        <f>IF(D21=0,0,IF(ISNUMBER('Reference data'!B22),D21*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>3.6e-05</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(ISNUMBER(E21),ROUND(E21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>3.0</v>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(ISNUMBER(F21),ROUND(F21*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="24" customHeight="1">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="47" customHeight="1">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1692</v>
-      </c>
-      <c r="E23" s="2">
-        <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.97704016e-05</v>
-      </c>
-      <c r="F23" s="2">
-        <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!C17),D23*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.384e-05</v>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H23" s="5">
-        <f>IF(ISNUMBER(F23),ROUND(F23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>130</v>
+      </c>
+      <c r="D23" s="1">
+        <v>64</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3</v>
-      </c>
-      <c r="E24" s="2">
-        <f>IF(AND(ISNUMBER(F24),ISNUMBER('Reference data'!$B$3)),F24*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F24" s="2">
-        <f>IF(D24=0,0,IF(ISNUMBER('Reference data'!B17),D24*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(ISNUMBER(E24),ROUND(E24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="5">
-        <f>IF(ISNUMBER(F24),ROUND(F24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
+        <v>134</v>
+      </c>
+      <c r="D24" s="1">
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="47" customHeight="1">
-      <c r="A26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>121</v>
+        <v>135</v>
+      </c>
+      <c r="D25" s="1">
+        <v>180</v>
+      </c>
+      <c r="L25" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4">
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="24" customHeight="1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D27" s="5">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER('Reference data'!$B$3)),F27*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.495558e-05</v>
+        <v>6.0174216e-05</v>
       </c>
       <c r="F27" s="2">
-        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!D17),D27*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>1.7e-05</v>
+        <f>IF(D27=0,0,IF(ISNUMBER('Reference data'!E22),D27*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.84e-05</v>
       </c>
       <c r="G27" s="5">
         <f>IF(ISNUMBER(E27),ROUND(E27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H27" s="5">
         <f>IF(ISNUMBER(F27),ROUND(F27*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="24" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="34" customHeight="1">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="4">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="4">
-        <v>19</v>
+        <v>138</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
+      <c r="A29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="1">
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="5">
-        <v>19</v>
-      </c>
-      <c r="E30" s="2">
-        <f>IF(AND(ISNUMBER(F30),ISNUMBER('Reference data'!$B$3)),F30*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="F30" s="2">
-        <f>IF(D30=0,0,IF(ISNUMBER('Reference data'!E17),D30*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="G30" s="5">
-        <f>IF(ISNUMBER(E30),ROUND(E30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-      <c r="H30" s="5">
-        <f>IF(ISNUMBER(F30),ROUND(F30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="73" customHeight="1">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
+        <v>135</v>
+      </c>
+      <c r="D30" s="1">
+        <v>57</v>
+      </c>
+      <c r="L30" s="1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="2">
+        <f>IF(COUNT('Turns'!E21,'Turns'!E27)=2,SUM('Turns'!E21,'Turns'!E27),"Unknown")</f>
+        <v>9.1844856e-05</v>
+      </c>
+      <c r="F31" s="2">
+        <f>IF(COUNT('Turns'!F21,'Turns'!F27)=2,SUM('Turns'!F21,'Turns'!F27),"Unknown")</f>
+        <v>0.0001044</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(ISNUMBER(E31),ROUND(E31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(ISNUMBER(F31),ROUND(F31*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="24" customHeight="1">
-      <c r="A33" t="s">
-        <v>119</v>
-      </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E34" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30)=4,SUM('Turns'!E23,'Turns'!E24,'Turns'!E27,'Turns'!E30),"Unknown")</f>
-        <v>6.53118976e-05</v>
-      </c>
-      <c r="F34" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30)=4,SUM('Turns'!F23,'Turns'!F24,'Turns'!F27,'Turns'!F30),"Unknown")</f>
-        <v>7.424e-05</v>
-      </c>
-      <c r="G34" s="5">
-        <f>IF(ISNUMBER(E34),ROUND(E34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="H34" s="5">
-        <f>IF(ISNUMBER(F34),ROUND(F34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>112</v>
+        <v>144</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1">
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="B35" s="4">
         <v>1</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="D35" s="4">
+        <v>273</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="24" customHeight="1">
+      <c r="A36" t="s">
+        <v>156</v>
+      </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>125</v>
+        <v>158</v>
+      </c>
+      <c r="D36" s="5">
+        <v>237</v>
+      </c>
+      <c r="E36" s="2">
+        <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
+        <v>4.1699676e-06</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!C22),D36*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>4.74e-06</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(ISNUMBER(F36),ROUND(F36*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="24" customHeight="1">
+      <c r="A37" t="s">
+        <v>156</v>
+      </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A38" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="4">
-        <v>1799</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M38" s="4" t="s">
         <v>128</v>
+      </c>
+      <c r="D37" s="5">
+        <v>36</v>
+      </c>
+      <c r="E37" s="2">
+        <f>IF(AND(ISNUMBER(F37),ISNUMBER('Reference data'!$B$3)),F37*'Reference data'!$B$3,"Unknown")</f>
+        <v>6.334128e-06</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(D37=0,0,IF(ISNUMBER('Reference data'!B22),D37*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(ISNUMBER(E37),ROUND(E37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="5">
+        <f>IF(ISNUMBER(F37),ROUND(F37*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="24" customHeight="1">
+      <c r="A38" t="s">
+        <v>156</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="1">
+        <v>36</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="24" customHeight="1">
       <c r="A39" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="5">
-        <v>1760</v>
-      </c>
-      <c r="E39" s="2">
-        <f>IF(AND(ISNUMBER(F39),ISNUMBER('Reference data'!$B$3)),F39*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0966848e-05</v>
-      </c>
-      <c r="F39" s="2">
-        <f>IF(D39=0,0,IF(ISNUMBER('Reference data'!C17),D39*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>3.52e-05</v>
-      </c>
-      <c r="G39" s="5">
-        <f>IF(ISNUMBER(E39),ROUND(E39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H39" s="5">
-        <f>IF(ISNUMBER(F39),ROUND(F39*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>134</v>
+      </c>
+      <c r="D39" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="24" customHeight="1">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="5">
-        <v>3</v>
-      </c>
-      <c r="E40" s="2">
-        <f>IF(AND(ISNUMBER(F40),ISNUMBER('Reference data'!$B$3)),F40*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F40" s="2">
-        <f>IF(D40=0,0,IF(ISNUMBER('Reference data'!B17),D40*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G40" s="5">
-        <f>IF(ISNUMBER(E40),ROUND(E40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H40" s="5">
-        <f>IF(ISNUMBER(F40),ROUND(F40*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="24" customHeight="1">
-      <c r="A41" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>129</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>126</v>
+        <v>135</v>
+      </c>
+      <c r="D40" s="1">
+        <v>36</v>
+      </c>
+      <c r="L40" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="4">
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="24" customHeight="1">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D42" s="5">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E42" s="2">
         <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.91766e-06</v>
+        <v>4.6450272e-05</v>
       </c>
       <c r="F42" s="2">
-        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!D17),D42*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>9e-06</v>
+        <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E22),D42*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>5.28e-05</v>
       </c>
       <c r="G42" s="5">
         <f>IF(ISNUMBER(E42),ROUND(E42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H42" s="5">
         <f>IF(ISNUMBER(F42),ROUND(F42*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="24" customHeight="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="34" customHeight="1">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A44" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B44" s="4">
-        <v>1</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="4">
-        <v>106</v>
+        <v>138</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1">
+      <c r="A44" t="s">
+        <v>156</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="1">
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="24" customHeight="1">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="5">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2">
-        <f>IF(AND(ISNUMBER(F45),ISNUMBER('Reference data'!$B$3)),F45*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.1287976e-05</v>
-      </c>
-      <c r="F45" s="2">
-        <f>IF(D45=0,0,IF(ISNUMBER('Reference data'!F17),D45*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>9.24e-05</v>
-      </c>
-      <c r="G45" s="5">
-        <f>IF(ISNUMBER(E45),ROUND(E45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>8.0</v>
-      </c>
-      <c r="H45" s="5">
-        <f>IF(ISNUMBER(F45),ROUND(F45*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="24" customHeight="1">
-      <c r="A46" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="5">
-        <v>29</v>
+        <v>135</v>
+      </c>
+      <c r="D45" s="1">
+        <v>44</v>
+      </c>
+      <c r="L45" s="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="E46" s="2">
-        <f>IF(AND(ISNUMBER(F46),ISNUMBER('Reference data'!$B$3)),F46*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0614952e-05</v>
+        <f>IF(COUNT('Turns'!E36,'Turns'!E37,'Turns'!E42)=3,SUM('Turns'!E36,'Turns'!E37,'Turns'!E42),"Unknown")</f>
+        <v>5.69543676e-05</v>
       </c>
       <c r="F46" s="2">
-        <f>IF(D46=0,0,IF(ISNUMBER('Reference data'!E17),D46*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F36,'Turns'!F37,'Turns'!F42)=3,SUM('Turns'!F36,'Turns'!F37,'Turns'!F42),"Unknown")</f>
+        <v>6.474e-05</v>
       </c>
       <c r="G46" s="5">
         <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H46" s="5">
         <f>IF(ISNUMBER(F46),ROUND(F46*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="320" customHeight="1">
-      <c r="A47" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>109</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>130</v>
+        <v>6.0</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="4">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="4">
+        <v>590</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="24" customHeight="1">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="24" customHeight="1">
+        <v>158</v>
+      </c>
+      <c r="D48" s="5">
+        <v>543</v>
+      </c>
+      <c r="E48" s="2">
+        <f>IF(AND(ISNUMBER(F48),ISNUMBER('Reference data'!$B$3)),F48*'Reference data'!$B$3,"Unknown")</f>
+        <v>9.5539764e-06</v>
+      </c>
+      <c r="F48" s="2">
+        <f>IF(D48=0,0,IF(ISNUMBER('Reference data'!C22),D48*'Reference data'!C22/1000000,"Unknown"))</f>
+        <v>1.086e-05</v>
+      </c>
+      <c r="G48" s="5">
+        <f>IF(ISNUMBER(E48),ROUND(E48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H48" s="5">
+        <f>IF(ISNUMBER(F48),ROUND(F48*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="24" customHeight="1">
       <c r="A49" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="2">
-        <f>IF(COUNT('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45,'Turns'!E46)=5,SUM('Turns'!E39,'Turns'!E40,'Turns'!E42,'Turns'!E45,'Turns'!E46),"Unknown")</f>
-        <v>0.00015131528</v>
-      </c>
-      <c r="F50" s="2">
-        <f>IF(COUNT('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45,'Turns'!F46)=5,SUM('Turns'!F39,'Turns'!F40,'Turns'!F42,'Turns'!F45,'Turns'!F46),"Unknown")</f>
-        <v>0.000172</v>
-      </c>
-      <c r="G50" s="5">
-        <f>IF(ISNUMBER(E50),ROUND(E50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
-      </c>
-      <c r="H50" s="5">
-        <f>IF(ISNUMBER(F50),ROUND(F50*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A51" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" s="4">
-        <v>2196</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24" customHeight="1">
+        <v>128</v>
+      </c>
+      <c r="D49" s="5">
+        <v>47</v>
+      </c>
+      <c r="E49" s="2">
+        <f>IF(AND(ISNUMBER(F49),ISNUMBER('Reference data'!$B$3)),F49*'Reference data'!$B$3,"Unknown")</f>
+        <v>8.269556e-06</v>
+      </c>
+      <c r="F49" s="2">
+        <f>IF(D49=0,0,IF(ISNUMBER('Reference data'!B22),D49*'Reference data'!B22/1000000,"Unknown"))</f>
+        <v>9.4e-06</v>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(ISNUMBER(E49),ROUND(E49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(ISNUMBER(F49),ROUND(F49*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="34" customHeight="1">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="1">
+        <v>47</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="24" customHeight="1">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="24" customHeight="1">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="5">
-        <v>2046</v>
-      </c>
-      <c r="E52" s="2">
-        <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.59989608e-05</v>
-      </c>
-      <c r="F52" s="2">
-        <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!C17),D52*'Reference data'!C17/1000000,"Unknown"))</f>
-        <v>4.092e-05</v>
-      </c>
-      <c r="G52" s="5">
-        <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-      <c r="H52" s="5">
-        <f>IF(ISNUMBER(F52),ROUND(F52*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="24" customHeight="1">
-      <c r="A53" t="s">
-        <v>131</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3</v>
-      </c>
-      <c r="E53" s="2">
-        <f>IF(AND(ISNUMBER(F53),ISNUMBER('Reference data'!$B$3)),F53*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="F53" s="2">
-        <f>IF(D53=0,0,IF(ISNUMBER('Reference data'!B17),D53*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>6e-07</v>
-      </c>
-      <c r="G53" s="5">
-        <f>IF(ISNUMBER(E53),ROUND(E53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-      <c r="H53" s="5">
-        <f>IF(ISNUMBER(F53),ROUND(F53*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="60" customHeight="1">
+        <v>135</v>
+      </c>
+      <c r="D52" s="1">
+        <v>47</v>
+      </c>
+      <c r="L52" s="1">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="4">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="24" customHeight="1">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="24" customHeight="1">
+        <v>137</v>
+      </c>
+      <c r="D54" s="5">
+        <v>55</v>
+      </c>
+      <c r="E54" s="2">
+        <f>IF(AND(ISNUMBER(F54),ISNUMBER('Reference data'!$B$3)),F54*'Reference data'!$B$3,"Unknown")</f>
+        <v>5.806284e-05</v>
+      </c>
+      <c r="F54" s="2">
+        <f>IF(D54=0,0,IF(ISNUMBER('Reference data'!E22),D54*'Reference data'!E22/1000000,"Unknown"))</f>
+        <v>6.6e-05</v>
+      </c>
+      <c r="G54" s="5">
+        <f>IF(ISNUMBER(E54),ROUND(E54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="H54" s="5">
+        <f>IF(ISNUMBER(F54),ROUND(F54*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="34" customHeight="1">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" s="5">
-        <v>147</v>
-      </c>
-      <c r="E55" s="2">
-        <f>IF(AND(ISNUMBER(F55),ISNUMBER('Reference data'!$B$3)),F55*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2330445e-05</v>
-      </c>
-      <c r="F55" s="2">
-        <f>IF(D55=0,0,IF(ISNUMBER('Reference data'!D17),D55*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>3.675e-05</v>
-      </c>
-      <c r="G55" s="5">
-        <f>IF(ISNUMBER(E55),ROUND(E55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="H55" s="5">
-        <f>IF(ISNUMBER(F55),ROUND(F55*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="24" customHeight="1">
+        <v>138</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="24" customHeight="1">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="4">
-        <v>1</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D57" s="4">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="24" customHeight="1">
-      <c r="A58" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="5">
-        <v>37</v>
+        <v>134</v>
+      </c>
+      <c r="D56" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="24" customHeight="1">
+      <c r="A57" t="s">
+        <v>161</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" s="1">
+        <v>55</v>
+      </c>
+      <c r="L57" s="1">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A58" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="4">
+        <v>1</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="E58" s="2">
-        <f>IF(AND(ISNUMBER(F58),ISNUMBER('Reference data'!$B$3)),F58*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.9060456e-05</v>
+        <f>IF(COUNT('Turns'!E48,'Turns'!E49,'Turns'!E54)=3,SUM('Turns'!E48,'Turns'!E49,'Turns'!E54),"Unknown")</f>
+        <v>7.58863724e-05</v>
       </c>
       <c r="F58" s="2">
-        <f>IF(D58=0,0,IF(ISNUMBER('Reference data'!E17),D58*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.44e-05</v>
+        <f>IF(COUNT('Turns'!F48,'Turns'!F49,'Turns'!F54)=3,SUM('Turns'!F48,'Turns'!F49,'Turns'!F54),"Unknown")</f>
+        <v>8.626e-05</v>
       </c>
       <c r="G58" s="5">
         <f>IF(ISNUMBER(E58),ROUND(E58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" s="5">
         <f>IF(ISNUMBER(F58),ROUND(F58*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="60" customHeight="1">
-      <c r="A59" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>109</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="24" customHeight="1">
-      <c r="A60" t="s">
-        <v>131</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="24" customHeight="1">
-      <c r="A61" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A62" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E62" s="2">
-        <f>IF(COUNT('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58)=4,SUM('Turns'!E52,'Turns'!E53,'Turns'!E55,'Turns'!E58),"Unknown")</f>
-        <v>0.0001079177058</v>
-      </c>
-      <c r="F62" s="2">
-        <f>IF(COUNT('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58)=4,SUM('Turns'!F52,'Turns'!F53,'Turns'!F55,'Turns'!F58),"Unknown")</f>
-        <v>0.00012267</v>
-      </c>
-      <c r="G62" s="5">
-        <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="H62" s="5">
-        <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>112</v>
+        <v>9.0</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE62">
+  <conditionalFormatting sqref="A2:AE58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -2189,7 +2173,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -2296,189 +2280,250 @@
     </row>
     <row r="2" spans="1:31" ht="54" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
         <v>49</v>
       </c>
       <c r="J2" s="2">
-        <f>IF(COUNT('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D53)=4,SUM('Turns'!D6,'Turns'!D24,'Turns'!D40,'Turns'!D53),"Unknown")</f>
-        <v>12.0</v>
+        <f>IF(COUNT('Turns'!D5,'Turns'!D21,'Turns'!D37,'Turns'!D49)=4,SUM('Turns'!D5,'Turns'!D21,'Turns'!D37,'Turns'!D49),"Unknown")</f>
+        <v>731.0</v>
       </c>
       <c r="K2" s="2">
-        <f>IF(COUNT('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E53)=4,SUM('Turns'!E6,'Turns'!E24,'Turns'!E40,'Turns'!E53),"Unknown")</f>
-        <v>2.111376e-06</v>
+        <f>IF(COUNT('Turns'!E5,'Turns'!E21,'Turns'!E37,'Turns'!E49)=4,SUM('Turns'!E5,'Turns'!E21,'Turns'!E37,'Turns'!E49),"Unknown")</f>
+        <v>0.000128617988</v>
       </c>
       <c r="L2" s="2">
-        <f>IF(COUNT('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F53)=4,SUM('Turns'!F6,'Turns'!F24,'Turns'!F40,'Turns'!F53),"Unknown")</f>
-        <v>2.4e-06</v>
+        <f>IF(COUNT('Turns'!F5,'Turns'!F21,'Turns'!F37,'Turns'!F49)=4,SUM('Turns'!F5,'Turns'!F21,'Turns'!F37,'Turns'!F49),"Unknown")</f>
+        <v>0.0001462</v>
       </c>
       <c r="M2" s="2">
-        <f>IF(COUNT('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D52)=4,SUM('Turns'!D5,'Turns'!D23,'Turns'!D39,'Turns'!D52),"Unknown")</f>
-        <v>7544.0</v>
+        <f>IF(COUNT('Turns'!D36,'Turns'!D48)=2,SUM('Turns'!D36,'Turns'!D48),"Unknown")</f>
+        <v>780.0</v>
       </c>
       <c r="N2" s="2">
-        <f>IF(COUNT('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E52)=4,SUM('Turns'!E5,'Turns'!E23,'Turns'!E39,'Turns'!E52),"Unknown")</f>
-        <v>0.0001327351712</v>
+        <f>IF(COUNT('Turns'!E36,'Turns'!E48)=2,SUM('Turns'!E36,'Turns'!E48),"Unknown")</f>
+        <v>1.3723944e-05</v>
       </c>
       <c r="O2" s="2">
-        <f>IF(COUNT('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F52)=4,SUM('Turns'!F5,'Turns'!F23,'Turns'!F39,'Turns'!F52),"Unknown")</f>
-        <v>0.00015088</v>
+        <f>IF(COUNT('Turns'!F36,'Turns'!F48)=2,SUM('Turns'!F36,'Turns'!F48),"Unknown")</f>
+        <v>1.56e-05</v>
       </c>
       <c r="P2" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D42,'Turns'!D55)=3,SUM('Turns'!D27,'Turns'!D42,'Turns'!D55),"Unknown")</f>
-        <v>251.0</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E42,'Turns'!E55)=3,SUM('Turns'!E27,'Turns'!E42,'Turns'!E55),"Unknown")</f>
-        <v>5.5203685e-05</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F42,'Turns'!F55)=3,SUM('Turns'!F27,'Turns'!F42,'Turns'!F55),"Unknown")</f>
-        <v>6.275e-05</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D14,'Turns'!D30,'Turns'!D46,'Turns'!D58)=4,SUM('Turns'!D14,'Turns'!D30,'Turns'!D46,'Turns'!D58),"Unknown")</f>
-        <v>177.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D54)=4,SUM('Turns'!D12,'Turns'!D27,'Turns'!D42,'Turns'!D54),"Unknown")</f>
+        <v>231.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E14,'Turns'!E30,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E14,'Turns'!E30,'Turns'!E46,'Turns'!E58),"Unknown")</f>
-        <v>0.000186856776</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E54)=4,SUM('Turns'!E12,'Turns'!E27,'Turns'!E42,'Turns'!E54),"Unknown")</f>
+        <v>0.000243863928</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F14,'Turns'!F30,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F14,'Turns'!F30,'Turns'!F46,'Turns'!F58),"Unknown")</f>
-        <v>0.0002124</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F54)=4,SUM('Turns'!F12,'Turns'!F27,'Turns'!F42,'Turns'!F54),"Unknown")</f>
+        <v>0.0002772</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D45)=2,SUM('Turns'!D13,'Turns'!D45),"Unknown")</f>
-        <v>100.0</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E45)=2,SUM('Turns'!E13,'Turns'!E45),"Unknown")</f>
-        <v>0.0001055688</v>
+        <v>0</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F45)=2,SUM('Turns'!F13,'Turns'!F45),"Unknown")</f>
-        <v>0.00012</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62)=4,SUM('Turns'!E18,'Turns'!E34,'Turns'!E50,'Turns'!E62),"Unknown")</f>
-        <v>0.0004824758082</v>
+        <f>IF(COUNT('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58)=4,SUM('Turns'!E16,'Turns'!E31,'Turns'!E46,'Turns'!E58),"Unknown")</f>
+        <v>0.00038620586</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62)=4,SUM('Turns'!F18,'Turns'!F34,'Turns'!F50,'Turns'!F62),"Unknown")</f>
-        <v>0.00054843</v>
+        <f>IF(COUNT('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58)=4,SUM('Turns'!F16,'Turns'!F31,'Turns'!F46,'Turns'!F58),"Unknown")</f>
+        <v>0.000439</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>55.0</v>
+        <v>44.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>6318.615</v>
+        <v>143.492</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="54" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="I3" t="s">
         <v>49</v>
       </c>
+      <c r="J3" s="2">
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>468.0</v>
+      </c>
+      <c r="K3" s="2">
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>8.2343664e-05</v>
+      </c>
+      <c r="L3" s="2">
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>9.36e-05</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>75.0</v>
+      </c>
+      <c r="T3" s="2">
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>7.91766e-05</v>
+      </c>
+      <c r="U3" s="2">
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>9e-05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000161520264</v>
+      </c>
+      <c r="Z3" s="2">
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.0001836</v>
+      </c>
+      <c r="AA3" s="5">
+        <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>16.0</v>
+      </c>
+      <c r="AB3" s="5">
+        <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>18.0</v>
+      </c>
       <c r="AD3" s="1">
-        <v>0.323</v>
+        <v>127.488</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
+      </c>
+      <c r="F4" s="1">
+        <v>468</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="J4" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
+        <v>468.0</v>
       </c>
       <c r="K4" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
+        <v>8.2343664e-05</v>
       </c>
       <c r="L4" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
+        <v>9.36e-05</v>
       </c>
       <c r="M4" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>2046.0</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.59989608e-05</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.092e-05</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2">
         <v>0</v>
@@ -2490,36 +2535,33 @@
         <v>0</v>
       </c>
       <c r="S4" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>92.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>75.0</v>
       </c>
       <c r="T4" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>9.7123296e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>7.91766e-05</v>
       </c>
       <c r="U4" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>0.0001104</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>9e-05</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W4" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.4280824e-05</v>
+        <v>0</v>
       </c>
       <c r="X4" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.0001579309248</v>
+        <f>IF(COUNT('Turns'!E16)=1,SUM('Turns'!E16),"Unknown")</f>
+        <v>0.000161520264</v>
       </c>
       <c r="Z4" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017952</v>
+        <f>IF(COUNT('Turns'!F16)=1,SUM('Turns'!F16),"Unknown")</f>
+        <v>0.0001836</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2529,64 +2571,64 @@
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
         <v>18.0</v>
       </c>
+      <c r="AC4" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="AD4" s="1">
-        <v>2159.168</v>
+        <v>125.611</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="54" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2049</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="I5" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2">
-        <f>IF(COUNT('Turns'!D6)=1,SUM('Turns'!D6),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>216.0</v>
       </c>
       <c r="K5" s="2">
-        <f>IF(COUNT('Turns'!E6)=1,SUM('Turns'!E6),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>3.8004768e-05</v>
       </c>
       <c r="L5" s="2">
-        <f>IF(COUNT('Turns'!F6)=1,SUM('Turns'!F6),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>4.32e-05</v>
       </c>
       <c r="M5" s="2">
-        <f>IF(COUNT('Turns'!D5)=1,SUM('Turns'!D5),"Unknown")</f>
-        <v>2046.0</v>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>237.0</v>
       </c>
       <c r="N5" s="2">
-        <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.59989608e-05</v>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>4.1699676e-06</v>
       </c>
       <c r="O5" s="2">
-        <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
-        <v>4.092e-05</v>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>4.74e-06</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
@@ -2598,1131 +2640,943 @@
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <f>IF(COUNT('Turns'!D14)=1,SUM('Turns'!D14),"Unknown")</f>
-        <v>92.0</v>
+        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
+        <v>101.0</v>
       </c>
       <c r="T5" s="2">
-        <f>IF(COUNT('Turns'!E14)=1,SUM('Turns'!E14),"Unknown")</f>
-        <v>9.7123296e-05</v>
+        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
+        <v>0.000106624488</v>
       </c>
       <c r="U5" s="2">
-        <f>IF(COUNT('Turns'!F14)=1,SUM('Turns'!F14),"Unknown")</f>
-        <v>0.0001104</v>
+        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
+        <v>0.0001212</v>
       </c>
       <c r="V5" s="2">
-        <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>23.0</v>
+        <v>0</v>
       </c>
       <c r="W5" s="2">
-        <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>2.4280824e-05</v>
+        <v>0</v>
       </c>
       <c r="X5" s="2">
-        <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>2.76e-05</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f>IF(COUNT('Turns'!E18)=1,SUM('Turns'!E18),"Unknown")</f>
-        <v>0.0001579309248</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.0001487992236</v>
       </c>
       <c r="Z5" s="2">
-        <f>IF(COUNT('Turns'!F18)=1,SUM('Turns'!F18),"Unknown")</f>
-        <v>0.00017952</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.00016914</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>93</v>
+        <v>17.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>2152.789</v>
+        <v>10.78</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="54" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="J6" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>216.0</v>
       </c>
       <c r="K6" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>3.8004768e-05</v>
       </c>
       <c r="L6" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>4.32e-05</v>
       </c>
       <c r="M6" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3452.0</v>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>237.0</v>
       </c>
       <c r="N6" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.07372496e-05</v>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>4.1699676e-06</v>
       </c>
       <c r="O6" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.904e-05</v>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>4.74e-06</v>
       </c>
       <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
         <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="Q6" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.287324e-05</v>
-      </c>
-      <c r="R6" s="2">
+        <v>0.000106624488</v>
+      </c>
+      <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.6e-05</v>
-      </c>
-      <c r="S6" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="T6" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
-        <v>5.0673024e-05</v>
-      </c>
-      <c r="U6" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>0.0001212</v>
       </c>
       <c r="V6" s="2">
-        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>77.0</v>
+        <v>0</v>
       </c>
       <c r="W6" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.1287976e-05</v>
+        <v>0</v>
       </c>
       <c r="X6" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.24e-05</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
-        <v>0.0002166271776</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.0001487992236</v>
       </c>
       <c r="Z6" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
-        <v>0.00024624</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.00016914</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD6" s="1">
-        <v>3038.35</v>
+        <v>9.879</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="54" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="I7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="J7" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D21,'Turns'!D37)=2,SUM('Turns'!D21,'Turns'!D37),"Unknown")</f>
+        <v>216.0</v>
       </c>
       <c r="K7" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <f>IF(COUNT('Turns'!E21,'Turns'!E37)=2,SUM('Turns'!E21,'Turns'!E37),"Unknown")</f>
+        <v>3.8004768e-05</v>
       </c>
       <c r="L7" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F21,'Turns'!F37)=2,SUM('Turns'!F21,'Turns'!F37),"Unknown")</f>
+        <v>4.32e-05</v>
       </c>
       <c r="M7" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3452.0</v>
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>237.0</v>
       </c>
       <c r="N7" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.07372496e-05</v>
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>4.1699676e-06</v>
       </c>
       <c r="O7" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.904e-05</v>
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>4.74e-06</v>
       </c>
       <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>104.0</v>
-      </c>
-      <c r="Q7" s="2">
+        <v>101.0</v>
+      </c>
+      <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.287324e-05</v>
-      </c>
-      <c r="R7" s="2">
+        <v>0.000106624488</v>
+      </c>
+      <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.6e-05</v>
-      </c>
-      <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
-        <v>48.0</v>
-      </c>
-      <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
-        <v>5.0673024e-05</v>
-      </c>
-      <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
-        <v>5.76e-05</v>
+        <v>0.0001212</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>77.0</v>
+        <v>0</v>
       </c>
       <c r="W7" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.1287976e-05</v>
+        <v>0</v>
       </c>
       <c r="X7" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.24e-05</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
-        <v>0.0002166271776</v>
+        <f>IF(COUNT('Turns'!E31,'Turns'!E46)=2,SUM('Turns'!E31,'Turns'!E46),"Unknown")</f>
+        <v>0.0001487992236</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
-        <v>0.00024624</v>
+        <f>IF(COUNT('Turns'!F31,'Turns'!F46)=2,SUM('Turns'!F31,'Turns'!F46),"Unknown")</f>
+        <v>0.00016914</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3036.543</v>
+        <v>9.098000000000001</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="54" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="B8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="I8" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="J8" s="2">
-        <f>IF(COUNT('Turns'!D24,'Turns'!D40)=2,SUM('Turns'!D24,'Turns'!D40),"Unknown")</f>
-        <v>6.0</v>
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>180.0</v>
       </c>
       <c r="K8" s="2">
-        <f>IF(COUNT('Turns'!E24,'Turns'!E40)=2,SUM('Turns'!E24,'Turns'!E40),"Unknown")</f>
-        <v>1.055688e-06</v>
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.167064e-05</v>
       </c>
       <c r="L8" s="2">
-        <f>IF(COUNT('Turns'!F24,'Turns'!F40)=2,SUM('Turns'!F24,'Turns'!F40),"Unknown")</f>
-        <v>1.2e-06</v>
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>3.6e-05</v>
       </c>
       <c r="M8" s="2">
-        <f>IF(COUNT('Turns'!D23,'Turns'!D39)=2,SUM('Turns'!D23,'Turns'!D39),"Unknown")</f>
-        <v>3452.0</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2">
-        <f>IF(COUNT('Turns'!E23,'Turns'!E39)=2,SUM('Turns'!E23,'Turns'!E39),"Unknown")</f>
-        <v>6.07372496e-05</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2">
-        <f>IF(COUNT('Turns'!F23,'Turns'!F39)=2,SUM('Turns'!F23,'Turns'!F39),"Unknown")</f>
-        <v>6.904e-05</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2">
-        <f>IF(COUNT('Turns'!D27,'Turns'!D42)=2,SUM('Turns'!D27,'Turns'!D42),"Unknown")</f>
-        <v>104.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2">
-        <f>IF(COUNT('Turns'!E27,'Turns'!E42)=2,SUM('Turns'!E27,'Turns'!E42),"Unknown")</f>
-        <v>2.287324e-05</v>
+        <v>0</v>
       </c>
       <c r="R8" s="2">
-        <f>IF(COUNT('Turns'!F27,'Turns'!F42)=2,SUM('Turns'!F27,'Turns'!F42),"Unknown")</f>
-        <v>2.6e-05</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D30,'Turns'!D46)=2,SUM('Turns'!D30,'Turns'!D46),"Unknown")</f>
-        <v>48.0</v>
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>57.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E30,'Turns'!E46)=2,SUM('Turns'!E30,'Turns'!E46),"Unknown")</f>
-        <v>5.0673024e-05</v>
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.0174216e-05</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F30,'Turns'!F46)=2,SUM('Turns'!F30,'Turns'!F46),"Unknown")</f>
-        <v>5.76e-05</v>
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>6.84e-05</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>77.0</v>
+        <v>0</v>
       </c>
       <c r="W8" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.1287976e-05</v>
+        <v>0</v>
       </c>
       <c r="X8" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.24e-05</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E34,'Turns'!E50)=2,SUM('Turns'!E34,'Turns'!E50),"Unknown")</f>
-        <v>0.0002166271776</v>
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>9.1844856e-05</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F34,'Turns'!F50)=2,SUM('Turns'!F34,'Turns'!F50),"Unknown")</f>
-        <v>0.00024624</v>
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0001044</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="AD8" s="1">
-        <v>3035.199</v>
+        <v>3.53</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="54" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="B9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
+      </c>
+      <c r="F9" s="1">
+        <v>180</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="H9" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I9" t="s">
-        <v>158</v>
+        <v>185</v>
+      </c>
+      <c r="J9" s="2">
+        <f>IF(COUNT('Turns'!D21)=1,SUM('Turns'!D21),"Unknown")</f>
+        <v>180.0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>IF(COUNT('Turns'!E21)=1,SUM('Turns'!E21),"Unknown")</f>
+        <v>3.167064e-05</v>
+      </c>
+      <c r="L9" s="2">
+        <f>IF(COUNT('Turns'!F21)=1,SUM('Turns'!F21),"Unknown")</f>
+        <v>3.6e-05</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
+        <v>57.0</v>
+      </c>
+      <c r="T9" s="2">
+        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
+        <v>6.0174216e-05</v>
+      </c>
+      <c r="U9" s="2">
+        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
+        <v>6.84e-05</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>IF(COUNT('Turns'!E31)=1,SUM('Turns'!E31),"Unknown")</f>
+        <v>9.1844856e-05</v>
+      </c>
+      <c r="Z9" s="2">
+        <f>IF(COUNT('Turns'!F31)=1,SUM('Turns'!F31),"Unknown")</f>
+        <v>0.0001044</v>
+      </c>
+      <c r="AA9" s="5">
+        <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>9.0</v>
+      </c>
+      <c r="AB9" s="5">
+        <f>IF(ISNUMBER(Z9),ROUND(Z9*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>10.0</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.423</v>
+        <v>1.935</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="54" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="B10" s="1">
         <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="H10" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J10" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K10" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L10" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M10" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>1692.0</v>
-      </c>
-      <c r="N10" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.97704016e-05</v>
-      </c>
-      <c r="O10" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>3.384e-05</v>
-      </c>
-      <c r="P10" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>68.0</v>
-      </c>
-      <c r="Q10" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.495558e-05</v>
-      </c>
-      <c r="R10" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.7e-05</v>
-      </c>
-      <c r="S10" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-      <c r="T10" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="U10" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="V10" s="2">
-        <v>0</v>
-      </c>
-      <c r="W10" s="2">
-        <v>0</v>
-      </c>
-      <c r="X10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>6.53118976e-05</v>
-      </c>
-      <c r="Z10" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>7.424e-05</v>
-      </c>
-      <c r="AA10" s="5">
-        <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AB10" s="5">
-        <f>IF(ISNUMBER(Z10),ROUND(Z10*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>183</v>
       </c>
       <c r="AD10" s="1">
-        <v>1093.913</v>
+        <v>1.283</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="54" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="B11" s="1">
         <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1763</v>
+        <v>141</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="I11" t="s">
-        <v>162</v>
-      </c>
-      <c r="J11" s="2">
-        <f>IF(COUNT('Turns'!D24)=1,SUM('Turns'!D24),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K11" s="2">
-        <f>IF(COUNT('Turns'!E24)=1,SUM('Turns'!E24),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L11" s="2">
-        <f>IF(COUNT('Turns'!F24)=1,SUM('Turns'!F24),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M11" s="2">
-        <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>1692.0</v>
-      </c>
-      <c r="N11" s="2">
-        <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>2.97704016e-05</v>
-      </c>
-      <c r="O11" s="2">
-        <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>3.384e-05</v>
-      </c>
-      <c r="P11" s="2">
-        <f>IF(COUNT('Turns'!D27)=1,SUM('Turns'!D27),"Unknown")</f>
-        <v>68.0</v>
-      </c>
-      <c r="Q11" s="2">
-        <f>IF(COUNT('Turns'!E27)=1,SUM('Turns'!E27),"Unknown")</f>
-        <v>1.495558e-05</v>
-      </c>
-      <c r="R11" s="2">
-        <f>IF(COUNT('Turns'!F27)=1,SUM('Turns'!F27),"Unknown")</f>
-        <v>1.7e-05</v>
-      </c>
-      <c r="S11" s="2">
-        <f>IF(COUNT('Turns'!D30)=1,SUM('Turns'!D30),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-      <c r="T11" s="2">
-        <f>IF(COUNT('Turns'!E30)=1,SUM('Turns'!E30),"Unknown")</f>
-        <v>2.0058072e-05</v>
-      </c>
-      <c r="U11" s="2">
-        <f>IF(COUNT('Turns'!F30)=1,SUM('Turns'!F30),"Unknown")</f>
-        <v>2.28e-05</v>
-      </c>
-      <c r="V11" s="2">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2">
-        <v>0</v>
-      </c>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2">
-        <f>IF(COUNT('Turns'!E34)=1,SUM('Turns'!E34),"Unknown")</f>
-        <v>6.53118976e-05</v>
-      </c>
-      <c r="Z11" s="2">
-        <f>IF(COUNT('Turns'!F34)=1,SUM('Turns'!F34),"Unknown")</f>
-        <v>7.424e-05</v>
-      </c>
-      <c r="AA11" s="5">
-        <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AB11" s="5">
-        <f>IF(ISNUMBER(Z11),ROUND(Z11*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="AD11" s="1">
-        <v>1087.122</v>
+        <v>0.397</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="54" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="I12" t="s">
-        <v>158</v>
+        <v>183</v>
+      </c>
+      <c r="J12" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>36.0</v>
+      </c>
+      <c r="K12" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>6.334128e-06</v>
+      </c>
+      <c r="L12" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="M12" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>237.0</v>
+      </c>
+      <c r="N12" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>4.1699676e-06</v>
+      </c>
+      <c r="O12" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>4.74e-06</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>44.0</v>
+      </c>
+      <c r="T12" s="2">
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>4.6450272e-05</v>
+      </c>
+      <c r="U12" s="2">
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>5.28e-05</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>5.69543676e-05</v>
+      </c>
+      <c r="Z12" s="2">
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>6.474e-05</v>
+      </c>
+      <c r="AA12" s="5">
+        <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="AB12" s="5">
+        <f>IF(ISNUMBER(Z12),ROUND(Z12*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2.24</v>
+        <v>2.028</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="54" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
+      </c>
+      <c r="F13" s="1">
+        <v>273</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="I13" t="s">
-        <v>165</v>
+        <v>192</v>
+      </c>
+      <c r="J13" s="2">
+        <f>IF(COUNT('Turns'!D37)=1,SUM('Turns'!D37),"Unknown")</f>
+        <v>36.0</v>
+      </c>
+      <c r="K13" s="2">
+        <f>IF(COUNT('Turns'!E37)=1,SUM('Turns'!E37),"Unknown")</f>
+        <v>6.334128e-06</v>
+      </c>
+      <c r="L13" s="2">
+        <f>IF(COUNT('Turns'!F37)=1,SUM('Turns'!F37),"Unknown")</f>
+        <v>7.2e-06</v>
+      </c>
+      <c r="M13" s="2">
+        <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
+        <v>237.0</v>
+      </c>
+      <c r="N13" s="2">
+        <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
+        <v>4.1699676e-06</v>
+      </c>
+      <c r="O13" s="2">
+        <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
+        <v>4.74e-06</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
+        <v>44.0</v>
+      </c>
+      <c r="T13" s="2">
+        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
+        <v>4.6450272e-05</v>
+      </c>
+      <c r="U13" s="2">
+        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
+        <v>5.28e-05</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
+        <v>5.69543676e-05</v>
+      </c>
+      <c r="Z13" s="2">
+        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
+        <v>6.474e-05</v>
+      </c>
+      <c r="AA13" s="5">
+        <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="AB13" s="5">
+        <f>IF(ISNUMBER(Z13),ROUND(Z13*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>6.0</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="AD13" s="1">
-        <v>0.5570000000000001</v>
+        <v>1.239</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="54" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B14" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="J14" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>47.0</v>
       </c>
       <c r="K14" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>8.269556e-06</v>
       </c>
       <c r="L14" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>9.4e-06</v>
       </c>
       <c r="M14" s="2">
-        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
-        <v>1760.0</v>
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
+        <v>543.0</v>
       </c>
       <c r="N14" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>3.0966848e-05</v>
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
+        <v>9.5539764e-06</v>
       </c>
       <c r="O14" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>3.52e-05</v>
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
+        <v>1.086e-05</v>
       </c>
       <c r="P14" s="2">
-        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="2">
-        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>7.91766e-06</v>
+        <v>0</v>
       </c>
       <c r="R14" s="2">
-        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2">
-        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
-        <v>29.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>55.0</v>
       </c>
       <c r="T14" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>3.0614952e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>5.806284e-05</v>
       </c>
       <c r="U14" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>6.6e-05</v>
       </c>
       <c r="V14" s="2">
-        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>77.0</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.1287976e-05</v>
+        <v>0</v>
       </c>
       <c r="X14" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.24e-05</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>0.00015131528</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>7.58863724e-05</v>
       </c>
       <c r="Z14" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>0.000172</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>8.626e-05</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB14" s="5">
         <f>IF(ISNUMBER(Z14),ROUND(Z14*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1932.661</v>
+        <v>2.186</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="54" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B15" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="F15" s="1">
-        <v>1799</v>
+        <v>590</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="I15" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="J15" s="2">
-        <f>IF(COUNT('Turns'!D40)=1,SUM('Turns'!D40),"Unknown")</f>
-        <v>3.0</v>
+        <f>IF(COUNT('Turns'!D49)=1,SUM('Turns'!D49),"Unknown")</f>
+        <v>47.0</v>
       </c>
       <c r="K15" s="2">
-        <f>IF(COUNT('Turns'!E40)=1,SUM('Turns'!E40),"Unknown")</f>
-        <v>5.27844e-07</v>
+        <f>IF(COUNT('Turns'!E49)=1,SUM('Turns'!E49),"Unknown")</f>
+        <v>8.269556e-06</v>
       </c>
       <c r="L15" s="2">
-        <f>IF(COUNT('Turns'!F40)=1,SUM('Turns'!F40),"Unknown")</f>
-        <v>6e-07</v>
+        <f>IF(COUNT('Turns'!F49)=1,SUM('Turns'!F49),"Unknown")</f>
+        <v>9.4e-06</v>
       </c>
       <c r="M15" s="2">
-        <f>IF(COUNT('Turns'!D39)=1,SUM('Turns'!D39),"Unknown")</f>
-        <v>1760.0</v>
+        <f>IF(COUNT('Turns'!D48)=1,SUM('Turns'!D48),"Unknown")</f>
+        <v>543.0</v>
       </c>
       <c r="N15" s="2">
-        <f>IF(COUNT('Turns'!E39)=1,SUM('Turns'!E39),"Unknown")</f>
-        <v>3.0966848e-05</v>
+        <f>IF(COUNT('Turns'!E48)=1,SUM('Turns'!E48),"Unknown")</f>
+        <v>9.5539764e-06</v>
       </c>
       <c r="O15" s="2">
-        <f>IF(COUNT('Turns'!F39)=1,SUM('Turns'!F39),"Unknown")</f>
-        <v>3.52e-05</v>
+        <f>IF(COUNT('Turns'!F48)=1,SUM('Turns'!F48),"Unknown")</f>
+        <v>1.086e-05</v>
       </c>
       <c r="P15" s="2">
-        <f>IF(COUNT('Turns'!D42)=1,SUM('Turns'!D42),"Unknown")</f>
-        <v>36.0</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="2">
-        <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>7.91766e-06</v>
+        <v>0</v>
       </c>
       <c r="R15" s="2">
-        <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
-        <v>9e-06</v>
+        <v>0</v>
       </c>
       <c r="S15" s="2">
-        <f>IF(COUNT('Turns'!D46)=1,SUM('Turns'!D46),"Unknown")</f>
-        <v>29.0</v>
+        <f>IF(COUNT('Turns'!D54)=1,SUM('Turns'!D54),"Unknown")</f>
+        <v>55.0</v>
       </c>
       <c r="T15" s="2">
-        <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>3.0614952e-05</v>
+        <f>IF(COUNT('Turns'!E54)=1,SUM('Turns'!E54),"Unknown")</f>
+        <v>5.806284e-05</v>
       </c>
       <c r="U15" s="2">
-        <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>3.48e-05</v>
+        <f>IF(COUNT('Turns'!F54)=1,SUM('Turns'!F54),"Unknown")</f>
+        <v>6.6e-05</v>
       </c>
       <c r="V15" s="2">
-        <f>IF(COUNT('Turns'!D45)=1,SUM('Turns'!D45),"Unknown")</f>
-        <v>77.0</v>
+        <v>0</v>
       </c>
       <c r="W15" s="2">
-        <f>IF(COUNT('Turns'!E45)=1,SUM('Turns'!E45),"Unknown")</f>
-        <v>8.1287976e-05</v>
+        <v>0</v>
       </c>
       <c r="X15" s="2">
-        <f>IF(COUNT('Turns'!F45)=1,SUM('Turns'!F45),"Unknown")</f>
-        <v>9.24e-05</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <f>IF(COUNT('Turns'!E50)=1,SUM('Turns'!E50),"Unknown")</f>
-        <v>0.00015131528</v>
+        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
+        <v>7.58863724e-05</v>
       </c>
       <c r="Z15" s="2">
-        <f>IF(COUNT('Turns'!F50)=1,SUM('Turns'!F50),"Unknown")</f>
-        <v>0.000172</v>
+        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
+        <v>8.626e-05</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB15" s="5">
         <f>IF(ISNUMBER(Z15),ROUND(Z15*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="AD15" s="1">
-        <v>1928.636</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="54" customHeight="1">
-      <c r="A16" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H16" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K16" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L16" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M16" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="N16" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>3.59989608e-05</v>
-      </c>
-      <c r="O16" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>4.092e-05</v>
-      </c>
-      <c r="P16" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>147.0</v>
-      </c>
-      <c r="Q16" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>3.2330445e-05</v>
-      </c>
-      <c r="R16" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>3.675e-05</v>
-      </c>
-      <c r="S16" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>37.0</v>
-      </c>
-      <c r="T16" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>3.9060456e-05</v>
-      </c>
-      <c r="U16" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>4.44e-05</v>
-      </c>
-      <c r="V16" s="2">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.0001079177058</v>
-      </c>
-      <c r="Z16" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00012267</v>
-      </c>
-      <c r="AA16" s="5">
-        <f>IF(ISNUMBER(Y16),ROUND(Y16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="AB16" s="5">
-        <f>IF(ISNUMBER(Z16),ROUND(Z16*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>1114.957</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="54" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2196</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="H17" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" t="s">
-        <v>169</v>
-      </c>
-      <c r="J17" s="2">
-        <f>IF(COUNT('Turns'!D53)=1,SUM('Turns'!D53),"Unknown")</f>
-        <v>3.0</v>
-      </c>
-      <c r="K17" s="2">
-        <f>IF(COUNT('Turns'!E53)=1,SUM('Turns'!E53),"Unknown")</f>
-        <v>5.27844e-07</v>
-      </c>
-      <c r="L17" s="2">
-        <f>IF(COUNT('Turns'!F53)=1,SUM('Turns'!F53),"Unknown")</f>
-        <v>6e-07</v>
-      </c>
-      <c r="M17" s="2">
-        <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>2046.0</v>
-      </c>
-      <c r="N17" s="2">
-        <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>3.59989608e-05</v>
-      </c>
-      <c r="O17" s="2">
-        <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>4.092e-05</v>
-      </c>
-      <c r="P17" s="2">
-        <f>IF(COUNT('Turns'!D55)=1,SUM('Turns'!D55),"Unknown")</f>
-        <v>147.0</v>
-      </c>
-      <c r="Q17" s="2">
-        <f>IF(COUNT('Turns'!E55)=1,SUM('Turns'!E55),"Unknown")</f>
-        <v>3.2330445e-05</v>
-      </c>
-      <c r="R17" s="2">
-        <f>IF(COUNT('Turns'!F55)=1,SUM('Turns'!F55),"Unknown")</f>
-        <v>3.675e-05</v>
-      </c>
-      <c r="S17" s="2">
-        <f>IF(COUNT('Turns'!D58)=1,SUM('Turns'!D58),"Unknown")</f>
-        <v>37.0</v>
-      </c>
-      <c r="T17" s="2">
-        <f>IF(COUNT('Turns'!E58)=1,SUM('Turns'!E58),"Unknown")</f>
-        <v>3.9060456e-05</v>
-      </c>
-      <c r="U17" s="2">
-        <f>IF(COUNT('Turns'!F58)=1,SUM('Turns'!F58),"Unknown")</f>
-        <v>4.44e-05</v>
-      </c>
-      <c r="V17" s="2">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2">
-        <f>IF(COUNT('Turns'!E62)=1,SUM('Turns'!E62),"Unknown")</f>
-        <v>0.0001079177058</v>
-      </c>
-      <c r="Z17" s="2">
-        <f>IF(COUNT('Turns'!F62)=1,SUM('Turns'!F62),"Unknown")</f>
-        <v>0.00012267</v>
-      </c>
-      <c r="AA17" s="5">
-        <f>IF(ISNUMBER(Y17),ROUND(Y17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>11.0</v>
-      </c>
-      <c r="AB17" s="5">
-        <f>IF(ISNUMBER(Z17),ROUND(Z17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>12.0</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>1109.268</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE17">
+  <conditionalFormatting sqref="A2:AE15">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$E2="error"</formula>
     </cfRule>
@@ -3736,7 +3590,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -4121,6 +3975,731 @@
         <v>80</v>
       </c>
     </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E23" s="2">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="72" customHeight="1">
+      <c r="A24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="72" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="72" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E26" s="2">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="72" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="72" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="72" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="F29" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="72" customHeight="1">
+      <c r="A30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.00</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F30" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="72" customHeight="1">
+      <c r="A32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.075</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="72" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="F33" s="2">
+        <v>14.00</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F34" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="72" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1.00</v>
+      </c>
+      <c r="D35" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="F35" s="2">
+        <v>50.00</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="72" customHeight="1">
+      <c r="A36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="72" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="72" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.00</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="72" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="2">
+        <v>10</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>12.50</v>
+      </c>
+      <c r="E39" s="2">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2">
+        <v>50</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="72" customHeight="1">
+      <c r="A40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="72" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E41" s="2">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="72" customHeight="1">
+      <c r="A42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2.50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="72" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="F43" s="2">
+        <v>22.50</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="72" customHeight="1">
+      <c r="A44" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="2">
+        <v>20.00</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2.00</v>
+      </c>
+      <c r="D44" s="2">
+        <v>25.00</v>
+      </c>
+      <c r="E44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="F44" s="2">
+        <v>75.00</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="72" customHeight="1">
+      <c r="A45" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="72" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.40</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="72" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4.00</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.20</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5.00</v>
+      </c>
+      <c r="E47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="F47" s="2">
+        <v>15.00</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
